--- a/artfynd/A 61943-2024 artfynd.xlsx
+++ b/artfynd/A 61943-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122567126</v>
+        <v>122567133</v>
       </c>
       <c r="B2" t="n">
         <v>78656</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>441344</v>
+        <v>441321</v>
       </c>
       <c r="R2" t="n">
-        <v>6753362</v>
+        <v>6753447</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122567117</v>
+        <v>122567126</v>
       </c>
       <c r="B3" t="n">
         <v>78656</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>441193</v>
+        <v>441344</v>
       </c>
       <c r="R3" t="n">
-        <v>6753577</v>
+        <v>6753362</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122567035</v>
+        <v>122567120</v>
       </c>
       <c r="B4" t="n">
-        <v>79274</v>
+        <v>78656</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>441158</v>
+        <v>441289</v>
       </c>
       <c r="R4" t="n">
-        <v>6753553</v>
+        <v>6753324</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122567069</v>
+        <v>122567067</v>
       </c>
       <c r="B5" t="n">
         <v>8441</v>
@@ -1026,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>441119</v>
+        <v>441231</v>
       </c>
       <c r="R5" t="n">
-        <v>6753677</v>
+        <v>6753537</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122567038</v>
+        <v>122567072</v>
       </c>
       <c r="B6" t="n">
-        <v>79274</v>
+        <v>8441</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1100,38 +1100,43 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>441336</v>
+        <v>441255</v>
       </c>
       <c r="R6" t="n">
-        <v>6753344</v>
+        <v>6753382</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1190,10 +1195,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122567067</v>
+        <v>122567047</v>
       </c>
       <c r="B7" t="n">
-        <v>8441</v>
+        <v>74757</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1202,43 +1207,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106545</v>
+        <v>6440</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>441231</v>
+        <v>441304</v>
       </c>
       <c r="R7" t="n">
-        <v>6753537</v>
+        <v>6753377</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1297,10 +1297,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122567066</v>
+        <v>122567056</v>
       </c>
       <c r="B8" t="n">
-        <v>8441</v>
+        <v>57399</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1309,31 +1309,31 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1342,10 +1342,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>441258</v>
+        <v>441305</v>
       </c>
       <c r="R8" t="n">
-        <v>6753406</v>
+        <v>6753366</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1404,10 +1404,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122567133</v>
+        <v>122567075</v>
       </c>
       <c r="B9" t="n">
-        <v>78656</v>
+        <v>8441</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1416,38 +1416,43 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>441321</v>
+        <v>441291</v>
       </c>
       <c r="R9" t="n">
-        <v>6753447</v>
+        <v>6753289</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1506,10 +1511,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122567041</v>
+        <v>122567066</v>
       </c>
       <c r="B10" t="n">
-        <v>79274</v>
+        <v>8441</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1518,38 +1523,43 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>441357</v>
+        <v>441258</v>
       </c>
       <c r="R10" t="n">
-        <v>6753361</v>
+        <v>6753406</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1608,10 +1618,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122567053</v>
+        <v>122567035</v>
       </c>
       <c r="B11" t="n">
-        <v>78690</v>
+        <v>79274</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1624,21 +1634,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1648,10 +1658,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>441420</v>
+        <v>441158</v>
       </c>
       <c r="R11" t="n">
-        <v>6753456</v>
+        <v>6753553</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1710,7 +1720,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122567121</v>
+        <v>122567099</v>
       </c>
       <c r="B12" t="n">
         <v>78656</v>
@@ -1750,10 +1760,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>441306</v>
+        <v>441323</v>
       </c>
       <c r="R12" t="n">
-        <v>6753338</v>
+        <v>6753416</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1812,10 +1822,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122567081</v>
+        <v>122567088</v>
       </c>
       <c r="B13" t="n">
-        <v>78393</v>
+        <v>56593</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1824,38 +1834,43 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>441344</v>
+        <v>441262</v>
       </c>
       <c r="R13" t="n">
-        <v>6753341</v>
+        <v>6753412</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1914,10 +1929,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122567056</v>
+        <v>122567051</v>
       </c>
       <c r="B14" t="n">
-        <v>57399</v>
+        <v>74757</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1930,39 +1945,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>6440</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>441305</v>
+        <v>441352</v>
       </c>
       <c r="R14" t="n">
-        <v>6753366</v>
+        <v>6753455</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2021,10 +2031,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122567070</v>
+        <v>122567098</v>
       </c>
       <c r="B15" t="n">
-        <v>8441</v>
+        <v>78656</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2033,43 +2043,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>441158</v>
+        <v>441329</v>
       </c>
       <c r="R15" t="n">
-        <v>6753533</v>
+        <v>6753411</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2128,10 +2133,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122567048</v>
+        <v>122567101</v>
       </c>
       <c r="B16" t="n">
-        <v>74757</v>
+        <v>78656</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2144,21 +2149,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2168,10 +2173,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>441302</v>
+        <v>441301</v>
       </c>
       <c r="R16" t="n">
-        <v>6753380</v>
+        <v>6753376</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2230,10 +2235,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122567047</v>
+        <v>122567117</v>
       </c>
       <c r="B17" t="n">
-        <v>74757</v>
+        <v>78656</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2246,21 +2251,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2270,10 +2275,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>441304</v>
+        <v>441193</v>
       </c>
       <c r="R17" t="n">
-        <v>6753377</v>
+        <v>6753577</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2332,7 +2337,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122567102</v>
+        <v>122567104</v>
       </c>
       <c r="B18" t="n">
         <v>78656</v>
@@ -2372,10 +2377,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>441305</v>
+        <v>441277</v>
       </c>
       <c r="R18" t="n">
-        <v>6753384</v>
+        <v>6753396</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2434,10 +2439,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122567051</v>
+        <v>122567077</v>
       </c>
       <c r="B19" t="n">
-        <v>74757</v>
+        <v>8441</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2446,38 +2451,43 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6440</v>
+        <v>106545</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>441352</v>
+        <v>441381</v>
       </c>
       <c r="R19" t="n">
-        <v>6753455</v>
+        <v>6753451</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2536,7 +2546,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122567039</v>
+        <v>122567038</v>
       </c>
       <c r="B20" t="n">
         <v>79274</v>
@@ -2576,10 +2586,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>441344</v>
+        <v>441336</v>
       </c>
       <c r="R20" t="n">
-        <v>6753341</v>
+        <v>6753344</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2638,7 +2648,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122567105</v>
+        <v>122567109</v>
       </c>
       <c r="B21" t="n">
         <v>78656</v>
@@ -2678,10 +2688,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>441269</v>
+        <v>441223</v>
       </c>
       <c r="R21" t="n">
-        <v>6753398</v>
+        <v>6753536</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2740,7 +2750,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122567128</v>
+        <v>122567127</v>
       </c>
       <c r="B22" t="n">
         <v>78656</v>
@@ -2780,10 +2790,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>441350</v>
+        <v>441338</v>
       </c>
       <c r="R22" t="n">
-        <v>6753388</v>
+        <v>6753386</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2842,7 +2852,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122567097</v>
+        <v>122567108</v>
       </c>
       <c r="B23" t="n">
         <v>78656</v>
@@ -2882,10 +2892,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>441320</v>
+        <v>441273</v>
       </c>
       <c r="R23" t="n">
-        <v>6753429</v>
+        <v>6753425</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2944,10 +2954,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122567071</v>
+        <v>122567125</v>
       </c>
       <c r="B24" t="n">
-        <v>8441</v>
+        <v>78656</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2956,43 +2966,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>441172</v>
+        <v>441356</v>
       </c>
       <c r="R24" t="n">
-        <v>6753515</v>
+        <v>6753361</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3051,10 +3056,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122567049</v>
+        <v>122567122</v>
       </c>
       <c r="B25" t="n">
-        <v>74757</v>
+        <v>78656</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3067,21 +3072,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3091,10 +3096,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>441299</v>
+        <v>441315</v>
       </c>
       <c r="R25" t="n">
-        <v>6753387</v>
+        <v>6753342</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3153,10 +3158,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122567109</v>
+        <v>122567068</v>
       </c>
       <c r="B26" t="n">
-        <v>78656</v>
+        <v>8441</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3165,38 +3170,43 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>441223</v>
+        <v>441150</v>
       </c>
       <c r="R26" t="n">
-        <v>6753536</v>
+        <v>6753623</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3255,7 +3265,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122567098</v>
+        <v>122567091</v>
       </c>
       <c r="B27" t="n">
         <v>78656</v>
@@ -3295,10 +3305,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>441329</v>
+        <v>441420</v>
       </c>
       <c r="R27" t="n">
-        <v>6753411</v>
+        <v>6753456</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3357,7 +3367,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122567134</v>
+        <v>122567116</v>
       </c>
       <c r="B28" t="n">
         <v>78656</v>
@@ -3397,10 +3407,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>441320</v>
+        <v>441199</v>
       </c>
       <c r="R28" t="n">
-        <v>6753453</v>
+        <v>6753562</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3459,10 +3469,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122567122</v>
+        <v>122567050</v>
       </c>
       <c r="B29" t="n">
-        <v>78656</v>
+        <v>74757</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3475,21 +3485,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3499,7 +3509,7 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>441315</v>
+        <v>441314</v>
       </c>
       <c r="R29" t="n">
         <v>6753342</v>
@@ -3561,7 +3571,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122567042</v>
+        <v>122567044</v>
       </c>
       <c r="B30" t="n">
         <v>79274</v>
@@ -3601,10 +3611,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>441336</v>
+        <v>441348</v>
       </c>
       <c r="R30" t="n">
-        <v>6753370</v>
+        <v>6753445</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3663,7 +3673,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122567127</v>
+        <v>122567118</v>
       </c>
       <c r="B31" t="n">
         <v>78656</v>
@@ -3703,10 +3713,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>441338</v>
+        <v>441277</v>
       </c>
       <c r="R31" t="n">
-        <v>6753386</v>
+        <v>6753324</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3765,10 +3775,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122567104</v>
+        <v>122567064</v>
       </c>
       <c r="B32" t="n">
-        <v>78656</v>
+        <v>8441</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3777,38 +3787,43 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>441277</v>
+        <v>441389</v>
       </c>
       <c r="R32" t="n">
-        <v>6753396</v>
+        <v>6753439</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3867,10 +3882,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122567138</v>
+        <v>122567081</v>
       </c>
       <c r="B33" t="n">
-        <v>78656</v>
+        <v>78393</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3883,21 +3898,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3907,10 +3922,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>441383</v>
+        <v>441344</v>
       </c>
       <c r="R33" t="n">
-        <v>6753450</v>
+        <v>6753341</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3969,10 +3984,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122567125</v>
+        <v>122567083</v>
       </c>
       <c r="B34" t="n">
-        <v>78656</v>
+        <v>78393</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3985,21 +4000,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4009,10 +4024,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>441356</v>
+        <v>441348</v>
       </c>
       <c r="R34" t="n">
-        <v>6753361</v>
+        <v>6753422</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4071,10 +4086,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122567046</v>
+        <v>122567139</v>
       </c>
       <c r="B35" t="n">
-        <v>74757</v>
+        <v>78656</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4087,21 +4102,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4111,10 +4126,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>441304</v>
+        <v>441430</v>
       </c>
       <c r="R35" t="n">
-        <v>6753366</v>
+        <v>6753445</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4173,7 +4188,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122567106</v>
+        <v>122567111</v>
       </c>
       <c r="B36" t="n">
         <v>78656</v>
@@ -4213,10 +4228,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>441266</v>
+        <v>441221</v>
       </c>
       <c r="R36" t="n">
-        <v>6753401</v>
+        <v>6753553</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4275,7 +4290,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122567103</v>
+        <v>122567137</v>
       </c>
       <c r="B37" t="n">
         <v>78656</v>
@@ -4315,10 +4330,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>441287</v>
+        <v>441348</v>
       </c>
       <c r="R37" t="n">
-        <v>6753389</v>
+        <v>6753444</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4377,10 +4392,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122567064</v>
+        <v>122567095</v>
       </c>
       <c r="B38" t="n">
-        <v>8441</v>
+        <v>78656</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4389,40 +4404,35 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>441389</v>
+        <v>441406</v>
       </c>
       <c r="R38" t="n">
         <v>6753439</v>
@@ -4484,10 +4494,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122567083</v>
+        <v>122567042</v>
       </c>
       <c r="B39" t="n">
-        <v>78393</v>
+        <v>79274</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4500,21 +4510,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4524,10 +4534,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>441348</v>
+        <v>441336</v>
       </c>
       <c r="R39" t="n">
-        <v>6753422</v>
+        <v>6753370</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4586,7 +4596,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122567068</v>
+        <v>122567059</v>
       </c>
       <c r="B40" t="n">
         <v>8441</v>
@@ -4622,7 +4632,7 @@
       <c r="I40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -4631,10 +4641,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>441150</v>
+        <v>441302</v>
       </c>
       <c r="R40" t="n">
-        <v>6753623</v>
+        <v>6753294</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4693,7 +4703,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122567112</v>
+        <v>122567106</v>
       </c>
       <c r="B41" t="n">
         <v>78656</v>
@@ -4733,10 +4743,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>441217</v>
+        <v>441266</v>
       </c>
       <c r="R41" t="n">
-        <v>6753556</v>
+        <v>6753401</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4795,10 +4805,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122567089</v>
+        <v>122567041</v>
       </c>
       <c r="B42" t="n">
-        <v>56593</v>
+        <v>79274</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4807,43 +4817,38 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>441283</v>
+        <v>441357</v>
       </c>
       <c r="R42" t="n">
-        <v>6753349</v>
+        <v>6753361</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4902,7 +4907,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122567111</v>
+        <v>122567114</v>
       </c>
       <c r="B43" t="n">
         <v>78656</v>
@@ -4942,10 +4947,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>441221</v>
+        <v>441206</v>
       </c>
       <c r="R43" t="n">
-        <v>6753553</v>
+        <v>6753562</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5004,7 +5009,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122567095</v>
+        <v>122567096</v>
       </c>
       <c r="B44" t="n">
         <v>78656</v>
@@ -5044,10 +5049,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>441406</v>
+        <v>441319</v>
       </c>
       <c r="R44" t="n">
-        <v>6753439</v>
+        <v>6753442</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5106,10 +5111,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122567099</v>
+        <v>122567089</v>
       </c>
       <c r="B45" t="n">
-        <v>78656</v>
+        <v>56593</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5118,38 +5123,43 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>441323</v>
+        <v>441283</v>
       </c>
       <c r="R45" t="n">
-        <v>6753416</v>
+        <v>6753349</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5208,10 +5218,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122567077</v>
+        <v>122567119</v>
       </c>
       <c r="B46" t="n">
-        <v>8441</v>
+        <v>78656</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5220,43 +5230,38 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>441381</v>
+        <v>441291</v>
       </c>
       <c r="R46" t="n">
-        <v>6753451</v>
+        <v>6753289</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5315,7 +5320,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122567091</v>
+        <v>122567103</v>
       </c>
       <c r="B47" t="n">
         <v>78656</v>
@@ -5355,10 +5360,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>441420</v>
+        <v>441287</v>
       </c>
       <c r="R47" t="n">
-        <v>6753456</v>
+        <v>6753389</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5417,7 +5422,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122567136</v>
+        <v>122567123</v>
       </c>
       <c r="B48" t="n">
         <v>78656</v>
@@ -5457,10 +5462,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>441345</v>
+        <v>441334</v>
       </c>
       <c r="R48" t="n">
-        <v>6753451</v>
+        <v>6753341</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5519,7 +5524,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122567120</v>
+        <v>122567100</v>
       </c>
       <c r="B49" t="n">
         <v>78656</v>
@@ -5559,10 +5564,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>441289</v>
+        <v>441332</v>
       </c>
       <c r="R49" t="n">
-        <v>6753324</v>
+        <v>6753382</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5723,10 +5728,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122567043</v>
+        <v>122567105</v>
       </c>
       <c r="B51" t="n">
-        <v>79274</v>
+        <v>78656</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5739,21 +5744,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5763,10 +5768,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>441348</v>
+        <v>441269</v>
       </c>
       <c r="R51" t="n">
-        <v>6753422</v>
+        <v>6753398</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5825,7 +5830,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122567072</v>
+        <v>122567070</v>
       </c>
       <c r="B52" t="n">
         <v>8441</v>
@@ -5870,10 +5875,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>441255</v>
+        <v>441158</v>
       </c>
       <c r="R52" t="n">
-        <v>6753382</v>
+        <v>6753533</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5932,10 +5937,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122567119</v>
+        <v>122567158</v>
       </c>
       <c r="B53" t="n">
-        <v>78656</v>
+        <v>78301</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5948,21 +5953,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5972,10 +5977,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>441291</v>
+        <v>441248</v>
       </c>
       <c r="R53" t="n">
-        <v>6753289</v>
+        <v>6753389</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6034,10 +6039,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122567036</v>
+        <v>122567136</v>
       </c>
       <c r="B54" t="n">
-        <v>79274</v>
+        <v>78656</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6050,21 +6055,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6074,10 +6079,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>441283</v>
+        <v>441345</v>
       </c>
       <c r="R54" t="n">
-        <v>6753350</v>
+        <v>6753451</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6136,10 +6141,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122567075</v>
+        <v>122567107</v>
       </c>
       <c r="B55" t="n">
-        <v>8441</v>
+        <v>78656</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6148,43 +6153,38 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>441291</v>
+        <v>441262</v>
       </c>
       <c r="R55" t="n">
-        <v>6753289</v>
+        <v>6753417</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6243,10 +6243,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122567118</v>
+        <v>122567071</v>
       </c>
       <c r="B56" t="n">
-        <v>78656</v>
+        <v>8441</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6255,38 +6255,43 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>441277</v>
+        <v>441172</v>
       </c>
       <c r="R56" t="n">
-        <v>6753324</v>
+        <v>6753515</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6345,10 +6350,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122567135</v>
+        <v>122567069</v>
       </c>
       <c r="B57" t="n">
-        <v>78656</v>
+        <v>8441</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6357,38 +6362,43 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>441322</v>
+        <v>441119</v>
       </c>
       <c r="R57" t="n">
-        <v>6753459</v>
+        <v>6753677</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6447,7 +6457,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122567132</v>
+        <v>122567112</v>
       </c>
       <c r="B58" t="n">
         <v>78656</v>
@@ -6487,10 +6497,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>441329</v>
+        <v>441217</v>
       </c>
       <c r="R58" t="n">
-        <v>6753438</v>
+        <v>6753556</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6549,7 +6559,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122567033</v>
+        <v>122567036</v>
       </c>
       <c r="B59" t="n">
         <v>79274</v>
@@ -6589,10 +6599,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>441194</v>
+        <v>441283</v>
       </c>
       <c r="R59" t="n">
-        <v>6753576</v>
+        <v>6753350</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6651,10 +6661,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122567074</v>
+        <v>122567134</v>
       </c>
       <c r="B60" t="n">
-        <v>8441</v>
+        <v>78656</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6663,43 +6673,38 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>441284</v>
+        <v>441320</v>
       </c>
       <c r="R60" t="n">
-        <v>6753286</v>
+        <v>6753453</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6758,10 +6763,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122567088</v>
+        <v>122567033</v>
       </c>
       <c r="B61" t="n">
-        <v>56593</v>
+        <v>79274</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6770,43 +6775,38 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>441262</v>
+        <v>441194</v>
       </c>
       <c r="R61" t="n">
-        <v>6753412</v>
+        <v>6753576</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6865,10 +6865,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122567034</v>
+        <v>122567121</v>
       </c>
       <c r="B62" t="n">
-        <v>79274</v>
+        <v>78656</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6881,21 +6881,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6905,10 +6905,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>441152</v>
+        <v>441306</v>
       </c>
       <c r="R62" t="n">
-        <v>6753562</v>
+        <v>6753338</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6967,10 +6967,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122567073</v>
+        <v>122567102</v>
       </c>
       <c r="B63" t="n">
-        <v>8441</v>
+        <v>78656</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -6979,43 +6979,38 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>441269</v>
+        <v>441305</v>
       </c>
       <c r="R63" t="n">
-        <v>6753365</v>
+        <v>6753384</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7074,7 +7069,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122567096</v>
+        <v>122567132</v>
       </c>
       <c r="B64" t="n">
         <v>78656</v>
@@ -7114,10 +7109,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>441319</v>
+        <v>441329</v>
       </c>
       <c r="R64" t="n">
-        <v>6753442</v>
+        <v>6753438</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7176,10 +7171,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122567050</v>
+        <v>122567034</v>
       </c>
       <c r="B65" t="n">
-        <v>74757</v>
+        <v>79274</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7192,21 +7187,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6440</v>
+        <v>6453</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7216,10 +7211,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>441314</v>
+        <v>441152</v>
       </c>
       <c r="R65" t="n">
-        <v>6753342</v>
+        <v>6753562</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7278,10 +7273,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122567158</v>
+        <v>122567128</v>
       </c>
       <c r="B66" t="n">
-        <v>78301</v>
+        <v>78656</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7294,21 +7289,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7318,10 +7313,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>441248</v>
+        <v>441350</v>
       </c>
       <c r="R66" t="n">
-        <v>6753389</v>
+        <v>6753388</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7380,7 +7375,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122567137</v>
+        <v>122567097</v>
       </c>
       <c r="B67" t="n">
         <v>78656</v>
@@ -7420,10 +7415,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>441348</v>
+        <v>441320</v>
       </c>
       <c r="R67" t="n">
-        <v>6753444</v>
+        <v>6753429</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7482,7 +7477,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122567123</v>
+        <v>122567113</v>
       </c>
       <c r="B68" t="n">
         <v>78656</v>
@@ -7522,10 +7517,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>441334</v>
+        <v>441207</v>
       </c>
       <c r="R68" t="n">
-        <v>6753341</v>
+        <v>6753568</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7584,10 +7579,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122567114</v>
+        <v>122567048</v>
       </c>
       <c r="B69" t="n">
-        <v>78656</v>
+        <v>74757</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7600,21 +7595,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7624,10 +7619,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>441206</v>
+        <v>441302</v>
       </c>
       <c r="R69" t="n">
-        <v>6753562</v>
+        <v>6753380</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7686,10 +7681,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122567100</v>
+        <v>122567046</v>
       </c>
       <c r="B70" t="n">
-        <v>78656</v>
+        <v>74757</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7702,21 +7697,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7726,10 +7721,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>441332</v>
+        <v>441304</v>
       </c>
       <c r="R70" t="n">
-        <v>6753382</v>
+        <v>6753366</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7788,10 +7783,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122567101</v>
+        <v>122567074</v>
       </c>
       <c r="B71" t="n">
-        <v>78656</v>
+        <v>8441</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7800,38 +7795,43 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>441301</v>
+        <v>441284</v>
       </c>
       <c r="R71" t="n">
-        <v>6753376</v>
+        <v>6753286</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7890,10 +7890,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122567116</v>
+        <v>122567049</v>
       </c>
       <c r="B72" t="n">
-        <v>78656</v>
+        <v>74757</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -7906,21 +7906,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7930,10 +7930,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>441199</v>
+        <v>441299</v>
       </c>
       <c r="R72" t="n">
-        <v>6753562</v>
+        <v>6753387</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7992,10 +7992,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>122567044</v>
+        <v>122567138</v>
       </c>
       <c r="B73" t="n">
-        <v>79274</v>
+        <v>78656</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8008,21 +8008,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8032,10 +8032,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>441348</v>
+        <v>441383</v>
       </c>
       <c r="R73" t="n">
-        <v>6753445</v>
+        <v>6753450</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8094,7 +8094,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>122567108</v>
+        <v>122567135</v>
       </c>
       <c r="B74" t="n">
         <v>78656</v>
@@ -8134,10 +8134,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>441273</v>
+        <v>441322</v>
       </c>
       <c r="R74" t="n">
-        <v>6753425</v>
+        <v>6753459</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8196,10 +8196,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>122567139</v>
+        <v>122567043</v>
       </c>
       <c r="B75" t="n">
-        <v>78656</v>
+        <v>79274</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8212,21 +8212,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8236,10 +8236,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>441430</v>
+        <v>441348</v>
       </c>
       <c r="R75" t="n">
-        <v>6753445</v>
+        <v>6753422</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8298,10 +8298,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>122567113</v>
+        <v>122567053</v>
       </c>
       <c r="B76" t="n">
-        <v>78656</v>
+        <v>78690</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8314,21 +8314,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8338,10 +8338,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>441207</v>
+        <v>441420</v>
       </c>
       <c r="R76" t="n">
-        <v>6753568</v>
+        <v>6753456</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8400,10 +8400,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>122567107</v>
+        <v>122567039</v>
       </c>
       <c r="B77" t="n">
-        <v>78656</v>
+        <v>79274</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8416,21 +8416,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8440,10 +8440,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>441262</v>
+        <v>441344</v>
       </c>
       <c r="R77" t="n">
-        <v>6753417</v>
+        <v>6753341</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8502,7 +8502,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>122567059</v>
+        <v>122567073</v>
       </c>
       <c r="B78" t="n">
         <v>8441</v>
@@ -8538,7 +8538,7 @@
       <c r="I78" t="inlineStr"/>
       <c r="M78" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
@@ -8547,10 +8547,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>441302</v>
+        <v>441269</v>
       </c>
       <c r="R78" t="n">
-        <v>6753294</v>
+        <v>6753365</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>

--- a/artfynd/A 61943-2024 artfynd.xlsx
+++ b/artfynd/A 61943-2024 artfynd.xlsx
@@ -1511,10 +1511,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122567066</v>
+        <v>122567035</v>
       </c>
       <c r="B10" t="n">
-        <v>8441</v>
+        <v>79274</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1523,43 +1523,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>441258</v>
+        <v>441158</v>
       </c>
       <c r="R10" t="n">
-        <v>6753406</v>
+        <v>6753553</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1618,10 +1613,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122567035</v>
+        <v>122567099</v>
       </c>
       <c r="B11" t="n">
-        <v>79274</v>
+        <v>78656</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1634,21 +1629,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1658,10 +1653,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>441158</v>
+        <v>441323</v>
       </c>
       <c r="R11" t="n">
-        <v>6753553</v>
+        <v>6753416</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1720,10 +1715,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122567099</v>
+        <v>122567088</v>
       </c>
       <c r="B12" t="n">
-        <v>78656</v>
+        <v>56593</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1732,38 +1727,43 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>441323</v>
+        <v>441262</v>
       </c>
       <c r="R12" t="n">
-        <v>6753416</v>
+        <v>6753412</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1822,10 +1822,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122567088</v>
+        <v>122567066</v>
       </c>
       <c r="B13" t="n">
-        <v>56593</v>
+        <v>8441</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1838,27 +1838,27 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100138</v>
+        <v>106545</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1867,10 +1867,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>441262</v>
+        <v>441258</v>
       </c>
       <c r="R13" t="n">
-        <v>6753412</v>
+        <v>6753406</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>

--- a/artfynd/A 61943-2024 artfynd.xlsx
+++ b/artfynd/A 61943-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122567133</v>
+        <v>122567111</v>
       </c>
       <c r="B2" t="n">
         <v>78656</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>441321</v>
+        <v>441221</v>
       </c>
       <c r="R2" t="n">
-        <v>6753447</v>
+        <v>6753553</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122567126</v>
+        <v>122567044</v>
       </c>
       <c r="B3" t="n">
-        <v>78656</v>
+        <v>79274</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>441344</v>
+        <v>441348</v>
       </c>
       <c r="R3" t="n">
-        <v>6753362</v>
+        <v>6753445</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122567120</v>
+        <v>122567039</v>
       </c>
       <c r="B4" t="n">
-        <v>78656</v>
+        <v>79274</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>441289</v>
+        <v>441344</v>
       </c>
       <c r="R4" t="n">
-        <v>6753324</v>
+        <v>6753341</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122567067</v>
+        <v>122567133</v>
       </c>
       <c r="B5" t="n">
-        <v>8441</v>
+        <v>78656</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,43 +993,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>441231</v>
+        <v>441321</v>
       </c>
       <c r="R5" t="n">
-        <v>6753537</v>
+        <v>6753447</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122567072</v>
+        <v>122567098</v>
       </c>
       <c r="B6" t="n">
-        <v>8441</v>
+        <v>78656</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1100,43 +1095,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>441255</v>
+        <v>441329</v>
       </c>
       <c r="R6" t="n">
-        <v>6753382</v>
+        <v>6753411</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1195,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122567047</v>
+        <v>122567100</v>
       </c>
       <c r="B7" t="n">
-        <v>74757</v>
+        <v>78656</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1211,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1235,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>441304</v>
+        <v>441332</v>
       </c>
       <c r="R7" t="n">
-        <v>6753377</v>
+        <v>6753382</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1297,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122567056</v>
+        <v>122567046</v>
       </c>
       <c r="B8" t="n">
-        <v>57399</v>
+        <v>74757</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1313,36 +1303,31 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>6440</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>441305</v>
+        <v>441304</v>
       </c>
       <c r="R8" t="n">
         <v>6753366</v>
@@ -1404,7 +1389,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122567075</v>
+        <v>122567066</v>
       </c>
       <c r="B9" t="n">
         <v>8441</v>
@@ -1449,10 +1434,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>441291</v>
+        <v>441258</v>
       </c>
       <c r="R9" t="n">
-        <v>6753289</v>
+        <v>6753406</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1511,7 +1496,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122567035</v>
+        <v>122567042</v>
       </c>
       <c r="B10" t="n">
         <v>79274</v>
@@ -1551,10 +1536,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>441158</v>
+        <v>441336</v>
       </c>
       <c r="R10" t="n">
-        <v>6753553</v>
+        <v>6753370</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1613,7 +1598,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122567099</v>
+        <v>122567112</v>
       </c>
       <c r="B11" t="n">
         <v>78656</v>
@@ -1653,10 +1638,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>441323</v>
+        <v>441217</v>
       </c>
       <c r="R11" t="n">
-        <v>6753416</v>
+        <v>6753556</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1715,10 +1700,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122567088</v>
+        <v>122567132</v>
       </c>
       <c r="B12" t="n">
-        <v>56593</v>
+        <v>78656</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1727,43 +1712,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>441262</v>
+        <v>441329</v>
       </c>
       <c r="R12" t="n">
-        <v>6753412</v>
+        <v>6753438</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1822,10 +1802,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122567066</v>
+        <v>122567136</v>
       </c>
       <c r="B13" t="n">
-        <v>8441</v>
+        <v>78656</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1834,43 +1814,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>441258</v>
+        <v>441345</v>
       </c>
       <c r="R13" t="n">
-        <v>6753406</v>
+        <v>6753451</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1929,10 +1904,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122567051</v>
+        <v>122567104</v>
       </c>
       <c r="B14" t="n">
-        <v>74757</v>
+        <v>78656</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1945,21 +1920,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1969,10 +1944,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>441352</v>
+        <v>441277</v>
       </c>
       <c r="R14" t="n">
-        <v>6753455</v>
+        <v>6753396</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2031,7 +2006,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122567098</v>
+        <v>122567102</v>
       </c>
       <c r="B15" t="n">
         <v>78656</v>
@@ -2071,10 +2046,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>441329</v>
+        <v>441305</v>
       </c>
       <c r="R15" t="n">
-        <v>6753411</v>
+        <v>6753384</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2133,10 +2108,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122567101</v>
+        <v>122567072</v>
       </c>
       <c r="B16" t="n">
-        <v>78656</v>
+        <v>8441</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2145,38 +2120,43 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>441301</v>
+        <v>441255</v>
       </c>
       <c r="R16" t="n">
-        <v>6753376</v>
+        <v>6753382</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2235,7 +2215,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122567117</v>
+        <v>122567103</v>
       </c>
       <c r="B17" t="n">
         <v>78656</v>
@@ -2275,10 +2255,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>441193</v>
+        <v>441287</v>
       </c>
       <c r="R17" t="n">
-        <v>6753577</v>
+        <v>6753389</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2337,7 +2317,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122567104</v>
+        <v>122567121</v>
       </c>
       <c r="B18" t="n">
         <v>78656</v>
@@ -2377,10 +2357,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>441277</v>
+        <v>441306</v>
       </c>
       <c r="R18" t="n">
-        <v>6753396</v>
+        <v>6753338</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2439,10 +2419,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122567077</v>
+        <v>122567128</v>
       </c>
       <c r="B19" t="n">
-        <v>8441</v>
+        <v>78656</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2451,43 +2431,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>441381</v>
+        <v>441350</v>
       </c>
       <c r="R19" t="n">
-        <v>6753451</v>
+        <v>6753388</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2546,10 +2521,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122567038</v>
+        <v>122567118</v>
       </c>
       <c r="B20" t="n">
-        <v>79274</v>
+        <v>78656</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2562,21 +2537,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2586,10 +2561,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>441336</v>
+        <v>441277</v>
       </c>
       <c r="R20" t="n">
-        <v>6753344</v>
+        <v>6753324</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2648,7 +2623,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122567109</v>
+        <v>122567127</v>
       </c>
       <c r="B21" t="n">
         <v>78656</v>
@@ -2688,10 +2663,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>441223</v>
+        <v>441338</v>
       </c>
       <c r="R21" t="n">
-        <v>6753536</v>
+        <v>6753386</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2750,10 +2725,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122567127</v>
+        <v>122567043</v>
       </c>
       <c r="B22" t="n">
-        <v>78656</v>
+        <v>79274</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2766,21 +2741,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2790,10 +2765,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>441338</v>
+        <v>441348</v>
       </c>
       <c r="R22" t="n">
-        <v>6753386</v>
+        <v>6753422</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2852,7 +2827,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122567108</v>
+        <v>122567117</v>
       </c>
       <c r="B23" t="n">
         <v>78656</v>
@@ -2892,10 +2867,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>441273</v>
+        <v>441193</v>
       </c>
       <c r="R23" t="n">
-        <v>6753425</v>
+        <v>6753577</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2954,7 +2929,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122567125</v>
+        <v>122567109</v>
       </c>
       <c r="B24" t="n">
         <v>78656</v>
@@ -2994,10 +2969,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>441356</v>
+        <v>441223</v>
       </c>
       <c r="R24" t="n">
-        <v>6753361</v>
+        <v>6753536</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3056,7 +3031,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122567122</v>
+        <v>122567097</v>
       </c>
       <c r="B25" t="n">
         <v>78656</v>
@@ -3096,10 +3071,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>441315</v>
+        <v>441320</v>
       </c>
       <c r="R25" t="n">
-        <v>6753342</v>
+        <v>6753429</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3158,10 +3133,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122567068</v>
+        <v>122567035</v>
       </c>
       <c r="B26" t="n">
-        <v>8441</v>
+        <v>79274</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3170,43 +3145,38 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>441150</v>
+        <v>441158</v>
       </c>
       <c r="R26" t="n">
-        <v>6753623</v>
+        <v>6753553</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3265,7 +3235,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122567091</v>
+        <v>122567116</v>
       </c>
       <c r="B27" t="n">
         <v>78656</v>
@@ -3305,10 +3275,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>441420</v>
+        <v>441199</v>
       </c>
       <c r="R27" t="n">
-        <v>6753456</v>
+        <v>6753562</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3367,7 +3337,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122567116</v>
+        <v>122567113</v>
       </c>
       <c r="B28" t="n">
         <v>78656</v>
@@ -3407,10 +3377,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>441199</v>
+        <v>441207</v>
       </c>
       <c r="R28" t="n">
-        <v>6753562</v>
+        <v>6753568</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3469,10 +3439,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122567050</v>
+        <v>122567137</v>
       </c>
       <c r="B29" t="n">
-        <v>74757</v>
+        <v>78656</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3485,21 +3455,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3509,10 +3479,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>441314</v>
+        <v>441348</v>
       </c>
       <c r="R29" t="n">
-        <v>6753342</v>
+        <v>6753444</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3571,10 +3541,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122567044</v>
+        <v>122567095</v>
       </c>
       <c r="B30" t="n">
-        <v>79274</v>
+        <v>78656</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3587,21 +3557,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3611,10 +3581,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>441348</v>
+        <v>441406</v>
       </c>
       <c r="R30" t="n">
-        <v>6753445</v>
+        <v>6753439</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3673,10 +3643,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122567118</v>
+        <v>122567048</v>
       </c>
       <c r="B31" t="n">
-        <v>78656</v>
+        <v>74757</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3689,21 +3659,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3713,10 +3683,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>441277</v>
+        <v>441302</v>
       </c>
       <c r="R31" t="n">
-        <v>6753324</v>
+        <v>6753380</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3775,10 +3745,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122567064</v>
+        <v>122567049</v>
       </c>
       <c r="B32" t="n">
-        <v>8441</v>
+        <v>74757</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3787,43 +3757,38 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>106545</v>
+        <v>6440</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>441389</v>
+        <v>441299</v>
       </c>
       <c r="R32" t="n">
-        <v>6753439</v>
+        <v>6753387</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3882,10 +3847,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122567081</v>
+        <v>122567138</v>
       </c>
       <c r="B33" t="n">
-        <v>78393</v>
+        <v>78656</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3898,21 +3863,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3922,10 +3887,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>441344</v>
+        <v>441383</v>
       </c>
       <c r="R33" t="n">
-        <v>6753341</v>
+        <v>6753450</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3984,10 +3949,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122567083</v>
+        <v>122567056</v>
       </c>
       <c r="B34" t="n">
-        <v>78393</v>
+        <v>57399</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4000,34 +3965,39 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>441348</v>
+        <v>441305</v>
       </c>
       <c r="R34" t="n">
-        <v>6753422</v>
+        <v>6753366</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4086,10 +4056,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122567139</v>
+        <v>122567073</v>
       </c>
       <c r="B35" t="n">
-        <v>78656</v>
+        <v>8441</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4098,38 +4068,43 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>441430</v>
+        <v>441269</v>
       </c>
       <c r="R35" t="n">
-        <v>6753445</v>
+        <v>6753365</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4188,10 +4163,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122567111</v>
+        <v>122567067</v>
       </c>
       <c r="B36" t="n">
-        <v>78656</v>
+        <v>8441</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4200,38 +4175,43 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>441221</v>
+        <v>441231</v>
       </c>
       <c r="R36" t="n">
-        <v>6753553</v>
+        <v>6753537</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4290,7 +4270,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122567137</v>
+        <v>122567105</v>
       </c>
       <c r="B37" t="n">
         <v>78656</v>
@@ -4330,10 +4310,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>441348</v>
+        <v>441269</v>
       </c>
       <c r="R37" t="n">
-        <v>6753444</v>
+        <v>6753398</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4392,10 +4372,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122567095</v>
+        <v>122567036</v>
       </c>
       <c r="B38" t="n">
-        <v>78656</v>
+        <v>79274</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4408,21 +4388,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4432,10 +4412,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>441406</v>
+        <v>441283</v>
       </c>
       <c r="R38" t="n">
-        <v>6753439</v>
+        <v>6753350</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4494,10 +4474,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122567042</v>
+        <v>122567119</v>
       </c>
       <c r="B39" t="n">
-        <v>79274</v>
+        <v>78656</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4510,21 +4490,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4534,10 +4514,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>441336</v>
+        <v>441291</v>
       </c>
       <c r="R39" t="n">
-        <v>6753370</v>
+        <v>6753289</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4596,10 +4576,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122567059</v>
+        <v>122567122</v>
       </c>
       <c r="B40" t="n">
-        <v>8441</v>
+        <v>78656</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4608,43 +4588,38 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>441302</v>
+        <v>441315</v>
       </c>
       <c r="R40" t="n">
-        <v>6753294</v>
+        <v>6753342</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4703,10 +4678,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122567106</v>
+        <v>122567041</v>
       </c>
       <c r="B41" t="n">
-        <v>78656</v>
+        <v>79274</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4719,21 +4694,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4743,10 +4718,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>441266</v>
+        <v>441357</v>
       </c>
       <c r="R41" t="n">
-        <v>6753401</v>
+        <v>6753361</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4805,10 +4780,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122567041</v>
+        <v>122567114</v>
       </c>
       <c r="B42" t="n">
-        <v>79274</v>
+        <v>78656</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4821,21 +4796,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4845,10 +4820,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>441357</v>
+        <v>441206</v>
       </c>
       <c r="R42" t="n">
-        <v>6753361</v>
+        <v>6753562</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4907,7 +4882,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122567114</v>
+        <v>122567096</v>
       </c>
       <c r="B43" t="n">
         <v>78656</v>
@@ -4947,10 +4922,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>441206</v>
+        <v>441319</v>
       </c>
       <c r="R43" t="n">
-        <v>6753562</v>
+        <v>6753442</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5009,10 +4984,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122567096</v>
+        <v>122567051</v>
       </c>
       <c r="B44" t="n">
-        <v>78656</v>
+        <v>74757</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5025,21 +5000,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5049,10 +5024,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>441319</v>
+        <v>441352</v>
       </c>
       <c r="R44" t="n">
-        <v>6753442</v>
+        <v>6753455</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5111,10 +5086,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122567089</v>
+        <v>122567101</v>
       </c>
       <c r="B45" t="n">
-        <v>56593</v>
+        <v>78656</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5123,43 +5098,38 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>441283</v>
+        <v>441301</v>
       </c>
       <c r="R45" t="n">
-        <v>6753349</v>
+        <v>6753376</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5218,7 +5188,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122567119</v>
+        <v>122567131</v>
       </c>
       <c r="B46" t="n">
         <v>78656</v>
@@ -5258,10 +5228,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>441291</v>
+        <v>441347</v>
       </c>
       <c r="R46" t="n">
-        <v>6753289</v>
+        <v>6753407</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5320,10 +5290,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122567103</v>
+        <v>122567034</v>
       </c>
       <c r="B47" t="n">
-        <v>78656</v>
+        <v>79274</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5336,21 +5306,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5360,10 +5330,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>441287</v>
+        <v>441152</v>
       </c>
       <c r="R47" t="n">
-        <v>6753389</v>
+        <v>6753562</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5422,7 +5392,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122567123</v>
+        <v>122567135</v>
       </c>
       <c r="B48" t="n">
         <v>78656</v>
@@ -5462,10 +5432,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>441334</v>
+        <v>441322</v>
       </c>
       <c r="R48" t="n">
-        <v>6753341</v>
+        <v>6753459</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5524,7 +5494,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122567100</v>
+        <v>122567134</v>
       </c>
       <c r="B49" t="n">
         <v>78656</v>
@@ -5564,10 +5534,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>441332</v>
+        <v>441320</v>
       </c>
       <c r="R49" t="n">
-        <v>6753382</v>
+        <v>6753453</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5626,10 +5596,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122567131</v>
+        <v>122567033</v>
       </c>
       <c r="B50" t="n">
-        <v>78656</v>
+        <v>79274</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5642,21 +5612,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5666,10 +5636,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>441347</v>
+        <v>441194</v>
       </c>
       <c r="R50" t="n">
-        <v>6753407</v>
+        <v>6753576</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5728,10 +5698,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122567105</v>
+        <v>122567071</v>
       </c>
       <c r="B51" t="n">
-        <v>78656</v>
+        <v>8441</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5740,38 +5710,43 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>441269</v>
+        <v>441172</v>
       </c>
       <c r="R51" t="n">
-        <v>6753398</v>
+        <v>6753515</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5830,10 +5805,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122567070</v>
+        <v>122567125</v>
       </c>
       <c r="B52" t="n">
-        <v>8441</v>
+        <v>78656</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5842,43 +5817,38 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>441158</v>
+        <v>441356</v>
       </c>
       <c r="R52" t="n">
-        <v>6753533</v>
+        <v>6753361</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5937,10 +5907,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122567158</v>
+        <v>122567070</v>
       </c>
       <c r="B53" t="n">
-        <v>78301</v>
+        <v>8441</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5949,38 +5919,43 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>353</v>
+        <v>106545</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>441248</v>
+        <v>441158</v>
       </c>
       <c r="R53" t="n">
-        <v>6753389</v>
+        <v>6753533</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6039,10 +6014,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122567136</v>
+        <v>122567069</v>
       </c>
       <c r="B54" t="n">
-        <v>78656</v>
+        <v>8441</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6051,38 +6026,43 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>441345</v>
+        <v>441119</v>
       </c>
       <c r="R54" t="n">
-        <v>6753451</v>
+        <v>6753677</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6141,7 +6121,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122567107</v>
+        <v>122567126</v>
       </c>
       <c r="B55" t="n">
         <v>78656</v>
@@ -6181,10 +6161,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>441262</v>
+        <v>441344</v>
       </c>
       <c r="R55" t="n">
-        <v>6753417</v>
+        <v>6753362</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6243,10 +6223,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122567071</v>
+        <v>122567091</v>
       </c>
       <c r="B56" t="n">
-        <v>8441</v>
+        <v>78656</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6255,43 +6235,38 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>441172</v>
+        <v>441420</v>
       </c>
       <c r="R56" t="n">
-        <v>6753515</v>
+        <v>6753456</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6350,10 +6325,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122567069</v>
+        <v>122567050</v>
       </c>
       <c r="B57" t="n">
-        <v>8441</v>
+        <v>74757</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6362,43 +6337,38 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>106545</v>
+        <v>6440</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>441119</v>
+        <v>441314</v>
       </c>
       <c r="R57" t="n">
-        <v>6753677</v>
+        <v>6753342</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6457,7 +6427,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122567112</v>
+        <v>122567099</v>
       </c>
       <c r="B58" t="n">
         <v>78656</v>
@@ -6497,10 +6467,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>441217</v>
+        <v>441323</v>
       </c>
       <c r="R58" t="n">
-        <v>6753556</v>
+        <v>6753416</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6559,10 +6529,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122567036</v>
+        <v>122567074</v>
       </c>
       <c r="B59" t="n">
-        <v>79274</v>
+        <v>8441</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6571,38 +6541,43 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>441283</v>
+        <v>441284</v>
       </c>
       <c r="R59" t="n">
-        <v>6753350</v>
+        <v>6753286</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6661,10 +6636,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122567134</v>
+        <v>122567064</v>
       </c>
       <c r="B60" t="n">
-        <v>78656</v>
+        <v>8441</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6673,38 +6648,43 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>441320</v>
+        <v>441389</v>
       </c>
       <c r="R60" t="n">
-        <v>6753453</v>
+        <v>6753439</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6763,10 +6743,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122567033</v>
+        <v>122567068</v>
       </c>
       <c r="B61" t="n">
-        <v>79274</v>
+        <v>8441</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6775,38 +6755,43 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>441194</v>
+        <v>441150</v>
       </c>
       <c r="R61" t="n">
-        <v>6753576</v>
+        <v>6753623</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6865,10 +6850,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122567121</v>
+        <v>122567077</v>
       </c>
       <c r="B62" t="n">
-        <v>78656</v>
+        <v>8441</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6877,38 +6862,43 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>441306</v>
+        <v>441381</v>
       </c>
       <c r="R62" t="n">
-        <v>6753338</v>
+        <v>6753451</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6967,10 +6957,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122567102</v>
+        <v>122567088</v>
       </c>
       <c r="B63" t="n">
-        <v>78656</v>
+        <v>56593</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -6979,38 +6969,43 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>441305</v>
+        <v>441262</v>
       </c>
       <c r="R63" t="n">
-        <v>6753384</v>
+        <v>6753412</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7069,7 +7064,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122567132</v>
+        <v>122567108</v>
       </c>
       <c r="B64" t="n">
         <v>78656</v>
@@ -7109,10 +7104,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>441329</v>
+        <v>441273</v>
       </c>
       <c r="R64" t="n">
-        <v>6753438</v>
+        <v>6753425</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7171,10 +7166,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122567034</v>
+        <v>122567139</v>
       </c>
       <c r="B65" t="n">
-        <v>79274</v>
+        <v>78656</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7187,21 +7182,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7211,10 +7206,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>441152</v>
+        <v>441430</v>
       </c>
       <c r="R65" t="n">
-        <v>6753562</v>
+        <v>6753445</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7273,10 +7268,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122567128</v>
+        <v>122567059</v>
       </c>
       <c r="B66" t="n">
-        <v>78656</v>
+        <v>8441</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7285,38 +7280,43 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>441350</v>
+        <v>441302</v>
       </c>
       <c r="R66" t="n">
-        <v>6753388</v>
+        <v>6753294</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7375,10 +7375,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122567097</v>
+        <v>122567053</v>
       </c>
       <c r="B67" t="n">
-        <v>78656</v>
+        <v>78690</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7391,21 +7391,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7415,10 +7415,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>441320</v>
+        <v>441420</v>
       </c>
       <c r="R67" t="n">
-        <v>6753429</v>
+        <v>6753456</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7477,10 +7477,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122567113</v>
+        <v>122567158</v>
       </c>
       <c r="B68" t="n">
-        <v>78656</v>
+        <v>78301</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7493,21 +7493,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7517,10 +7517,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>441207</v>
+        <v>441248</v>
       </c>
       <c r="R68" t="n">
-        <v>6753568</v>
+        <v>6753389</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7579,10 +7579,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122567048</v>
+        <v>122567106</v>
       </c>
       <c r="B69" t="n">
-        <v>74757</v>
+        <v>78656</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7595,21 +7595,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7619,10 +7619,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>441302</v>
+        <v>441266</v>
       </c>
       <c r="R69" t="n">
-        <v>6753380</v>
+        <v>6753401</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7681,10 +7681,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122567046</v>
+        <v>122567123</v>
       </c>
       <c r="B70" t="n">
-        <v>74757</v>
+        <v>78656</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7697,21 +7697,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7721,10 +7721,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>441304</v>
+        <v>441334</v>
       </c>
       <c r="R70" t="n">
-        <v>6753366</v>
+        <v>6753341</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7783,10 +7783,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122567074</v>
+        <v>122567038</v>
       </c>
       <c r="B71" t="n">
-        <v>8441</v>
+        <v>79274</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7795,43 +7795,38 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>441284</v>
+        <v>441336</v>
       </c>
       <c r="R71" t="n">
-        <v>6753286</v>
+        <v>6753344</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7890,10 +7885,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122567049</v>
+        <v>122567120</v>
       </c>
       <c r="B72" t="n">
-        <v>74757</v>
+        <v>78656</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -7906,21 +7901,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7930,10 +7925,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>441299</v>
+        <v>441289</v>
       </c>
       <c r="R72" t="n">
-        <v>6753387</v>
+        <v>6753324</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7992,10 +7987,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>122567138</v>
+        <v>122567089</v>
       </c>
       <c r="B73" t="n">
-        <v>78656</v>
+        <v>56593</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8004,38 +7999,43 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>441383</v>
+        <v>441283</v>
       </c>
       <c r="R73" t="n">
-        <v>6753450</v>
+        <v>6753349</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8094,10 +8094,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>122567135</v>
+        <v>122567075</v>
       </c>
       <c r="B74" t="n">
-        <v>78656</v>
+        <v>8441</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8106,38 +8106,43 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>441322</v>
+        <v>441291</v>
       </c>
       <c r="R74" t="n">
-        <v>6753459</v>
+        <v>6753289</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8196,10 +8201,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>122567043</v>
+        <v>122567107</v>
       </c>
       <c r="B75" t="n">
-        <v>79274</v>
+        <v>78656</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8212,21 +8217,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8236,10 +8241,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>441348</v>
+        <v>441262</v>
       </c>
       <c r="R75" t="n">
-        <v>6753422</v>
+        <v>6753417</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8298,10 +8303,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>122567053</v>
+        <v>122567047</v>
       </c>
       <c r="B76" t="n">
-        <v>78690</v>
+        <v>74757</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8314,21 +8319,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>185</v>
+        <v>6440</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8338,10 +8343,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>441420</v>
+        <v>441304</v>
       </c>
       <c r="R76" t="n">
-        <v>6753456</v>
+        <v>6753377</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8400,10 +8405,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>122567039</v>
+        <v>122567081</v>
       </c>
       <c r="B77" t="n">
-        <v>79274</v>
+        <v>78393</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8416,21 +8421,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8502,10 +8507,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>122567073</v>
+        <v>122567083</v>
       </c>
       <c r="B78" t="n">
-        <v>8441</v>
+        <v>78393</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8514,43 +8519,38 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>441269</v>
+        <v>441348</v>
       </c>
       <c r="R78" t="n">
-        <v>6753365</v>
+        <v>6753422</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>

--- a/artfynd/A 61943-2024 artfynd.xlsx
+++ b/artfynd/A 61943-2024 artfynd.xlsx
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122567066</v>
+        <v>122567112</v>
       </c>
       <c r="B9" t="n">
-        <v>8441</v>
+        <v>78656</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1401,43 +1401,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>441258</v>
+        <v>441217</v>
       </c>
       <c r="R9" t="n">
-        <v>6753406</v>
+        <v>6753556</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1496,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122567042</v>
+        <v>122567132</v>
       </c>
       <c r="B10" t="n">
-        <v>79274</v>
+        <v>78656</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1512,21 +1507,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1536,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>441336</v>
+        <v>441329</v>
       </c>
       <c r="R10" t="n">
-        <v>6753370</v>
+        <v>6753438</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1598,7 +1593,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122567112</v>
+        <v>122567136</v>
       </c>
       <c r="B11" t="n">
         <v>78656</v>
@@ -1638,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>441217</v>
+        <v>441345</v>
       </c>
       <c r="R11" t="n">
-        <v>6753556</v>
+        <v>6753451</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1700,7 +1695,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122567132</v>
+        <v>122567104</v>
       </c>
       <c r="B12" t="n">
         <v>78656</v>
@@ -1740,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>441329</v>
+        <v>441277</v>
       </c>
       <c r="R12" t="n">
-        <v>6753438</v>
+        <v>6753396</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1802,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122567136</v>
+        <v>122567042</v>
       </c>
       <c r="B13" t="n">
-        <v>78656</v>
+        <v>79274</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1818,21 +1813,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1842,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>441345</v>
+        <v>441336</v>
       </c>
       <c r="R13" t="n">
-        <v>6753451</v>
+        <v>6753370</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1904,10 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122567104</v>
+        <v>122567066</v>
       </c>
       <c r="B14" t="n">
-        <v>78656</v>
+        <v>8441</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1916,38 +1911,43 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>441277</v>
+        <v>441258</v>
       </c>
       <c r="R14" t="n">
-        <v>6753396</v>
+        <v>6753406</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2006,7 +2006,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122567102</v>
+        <v>122567121</v>
       </c>
       <c r="B15" t="n">
         <v>78656</v>
@@ -2046,10 +2046,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>441305</v>
+        <v>441306</v>
       </c>
       <c r="R15" t="n">
-        <v>6753384</v>
+        <v>6753338</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2108,10 +2108,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122567072</v>
+        <v>122567128</v>
       </c>
       <c r="B16" t="n">
-        <v>8441</v>
+        <v>78656</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2120,43 +2120,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>441255</v>
+        <v>441350</v>
       </c>
       <c r="R16" t="n">
-        <v>6753382</v>
+        <v>6753388</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2215,7 +2210,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122567103</v>
+        <v>122567102</v>
       </c>
       <c r="B17" t="n">
         <v>78656</v>
@@ -2255,10 +2250,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>441287</v>
+        <v>441305</v>
       </c>
       <c r="R17" t="n">
-        <v>6753389</v>
+        <v>6753384</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2317,7 +2312,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122567121</v>
+        <v>122567103</v>
       </c>
       <c r="B18" t="n">
         <v>78656</v>
@@ -2357,10 +2352,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>441306</v>
+        <v>441287</v>
       </c>
       <c r="R18" t="n">
-        <v>6753338</v>
+        <v>6753389</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2419,7 +2414,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122567128</v>
+        <v>122567118</v>
       </c>
       <c r="B19" t="n">
         <v>78656</v>
@@ -2459,10 +2454,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>441350</v>
+        <v>441277</v>
       </c>
       <c r="R19" t="n">
-        <v>6753388</v>
+        <v>6753324</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2521,10 +2516,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122567118</v>
+        <v>122567072</v>
       </c>
       <c r="B20" t="n">
-        <v>78656</v>
+        <v>8441</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2533,38 +2528,43 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>441277</v>
+        <v>441255</v>
       </c>
       <c r="R20" t="n">
-        <v>6753324</v>
+        <v>6753382</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3133,10 +3133,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122567035</v>
+        <v>122567095</v>
       </c>
       <c r="B26" t="n">
-        <v>79274</v>
+        <v>78656</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3149,21 +3149,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3173,10 +3173,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>441158</v>
+        <v>441406</v>
       </c>
       <c r="R26" t="n">
-        <v>6753553</v>
+        <v>6753439</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3541,10 +3541,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122567095</v>
+        <v>122567048</v>
       </c>
       <c r="B30" t="n">
-        <v>78656</v>
+        <v>74757</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3557,21 +3557,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3581,10 +3581,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>441406</v>
+        <v>441302</v>
       </c>
       <c r="R30" t="n">
-        <v>6753439</v>
+        <v>6753380</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3643,10 +3643,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122567048</v>
+        <v>122567035</v>
       </c>
       <c r="B31" t="n">
-        <v>74757</v>
+        <v>79274</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3659,21 +3659,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6440</v>
+        <v>6453</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3683,10 +3683,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>441302</v>
+        <v>441158</v>
       </c>
       <c r="R31" t="n">
-        <v>6753380</v>
+        <v>6753553</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4163,10 +4163,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122567067</v>
+        <v>122567105</v>
       </c>
       <c r="B36" t="n">
-        <v>8441</v>
+        <v>78656</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4175,43 +4175,38 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>441231</v>
+        <v>441269</v>
       </c>
       <c r="R36" t="n">
-        <v>6753537</v>
+        <v>6753398</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4270,10 +4265,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122567105</v>
+        <v>122567036</v>
       </c>
       <c r="B37" t="n">
-        <v>78656</v>
+        <v>79274</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4286,21 +4281,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4310,10 +4305,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>441269</v>
+        <v>441283</v>
       </c>
       <c r="R37" t="n">
-        <v>6753398</v>
+        <v>6753350</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4372,10 +4367,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122567036</v>
+        <v>122567067</v>
       </c>
       <c r="B38" t="n">
-        <v>79274</v>
+        <v>8441</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4384,38 +4379,43 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>441283</v>
+        <v>441231</v>
       </c>
       <c r="R38" t="n">
-        <v>6753350</v>
+        <v>6753537</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5392,10 +5392,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122567135</v>
+        <v>122567033</v>
       </c>
       <c r="B48" t="n">
-        <v>78656</v>
+        <v>79274</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5408,21 +5408,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>441322</v>
+        <v>441194</v>
       </c>
       <c r="R48" t="n">
-        <v>6753459</v>
+        <v>6753576</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5596,10 +5596,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122567033</v>
+        <v>122567135</v>
       </c>
       <c r="B50" t="n">
-        <v>79274</v>
+        <v>78656</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5612,21 +5612,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5636,10 +5636,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>441194</v>
+        <v>441322</v>
       </c>
       <c r="R50" t="n">
-        <v>6753576</v>
+        <v>6753459</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>

--- a/artfynd/A 61943-2024 artfynd.xlsx
+++ b/artfynd/A 61943-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122567111</v>
+        <v>122567117</v>
       </c>
       <c r="B2" t="n">
         <v>78656</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>441221</v>
+        <v>441193</v>
       </c>
       <c r="R2" t="n">
-        <v>6753553</v>
+        <v>6753577</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122567044</v>
+        <v>122567064</v>
       </c>
       <c r="B3" t="n">
-        <v>79274</v>
+        <v>8441</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,38 +789,43 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>441348</v>
+        <v>441389</v>
       </c>
       <c r="R3" t="n">
-        <v>6753445</v>
+        <v>6753439</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,7 +884,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122567039</v>
+        <v>122567041</v>
       </c>
       <c r="B4" t="n">
         <v>79274</v>
@@ -919,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>441344</v>
+        <v>441357</v>
       </c>
       <c r="R4" t="n">
-        <v>6753341</v>
+        <v>6753361</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122567133</v>
+        <v>122567039</v>
       </c>
       <c r="B5" t="n">
-        <v>78656</v>
+        <v>79274</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +1002,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>441321</v>
+        <v>441344</v>
       </c>
       <c r="R5" t="n">
-        <v>6753447</v>
+        <v>6753341</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122567098</v>
+        <v>122567048</v>
       </c>
       <c r="B6" t="n">
-        <v>78656</v>
+        <v>74757</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1104,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>441329</v>
+        <v>441302</v>
       </c>
       <c r="R6" t="n">
-        <v>6753411</v>
+        <v>6753380</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,7 +1190,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122567100</v>
+        <v>122567128</v>
       </c>
       <c r="B7" t="n">
         <v>78656</v>
@@ -1225,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>441332</v>
+        <v>441350</v>
       </c>
       <c r="R7" t="n">
-        <v>6753382</v>
+        <v>6753388</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1292,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122567046</v>
+        <v>122567095</v>
       </c>
       <c r="B8" t="n">
-        <v>74757</v>
+        <v>78656</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,21 +1308,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1332,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>441304</v>
+        <v>441406</v>
       </c>
       <c r="R8" t="n">
-        <v>6753366</v>
+        <v>6753439</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,7 +1394,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122567112</v>
+        <v>122567099</v>
       </c>
       <c r="B9" t="n">
         <v>78656</v>
@@ -1429,10 +1434,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>441217</v>
+        <v>441323</v>
       </c>
       <c r="R9" t="n">
-        <v>6753556</v>
+        <v>6753416</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,7 +1496,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122567132</v>
+        <v>122567108</v>
       </c>
       <c r="B10" t="n">
         <v>78656</v>
@@ -1531,10 +1536,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>441329</v>
+        <v>441273</v>
       </c>
       <c r="R10" t="n">
-        <v>6753438</v>
+        <v>6753425</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,10 +1598,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122567136</v>
+        <v>122567043</v>
       </c>
       <c r="B11" t="n">
-        <v>78656</v>
+        <v>79274</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1609,21 +1614,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1638,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>441345</v>
+        <v>441348</v>
       </c>
       <c r="R11" t="n">
-        <v>6753451</v>
+        <v>6753422</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,7 +1700,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122567104</v>
+        <v>122567116</v>
       </c>
       <c r="B12" t="n">
         <v>78656</v>
@@ -1735,10 +1740,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>441277</v>
+        <v>441199</v>
       </c>
       <c r="R12" t="n">
-        <v>6753396</v>
+        <v>6753562</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1797,10 +1802,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122567042</v>
+        <v>122567073</v>
       </c>
       <c r="B13" t="n">
-        <v>79274</v>
+        <v>8441</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1809,38 +1814,43 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>441336</v>
+        <v>441269</v>
       </c>
       <c r="R13" t="n">
-        <v>6753370</v>
+        <v>6753365</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1899,7 +1909,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122567066</v>
+        <v>122567074</v>
       </c>
       <c r="B14" t="n">
         <v>8441</v>
@@ -1944,10 +1954,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>441258</v>
+        <v>441284</v>
       </c>
       <c r="R14" t="n">
-        <v>6753406</v>
+        <v>6753286</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2006,10 +2016,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122567121</v>
+        <v>122567069</v>
       </c>
       <c r="B15" t="n">
-        <v>78656</v>
+        <v>8441</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2018,38 +2028,43 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>441306</v>
+        <v>441119</v>
       </c>
       <c r="R15" t="n">
-        <v>6753338</v>
+        <v>6753677</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2108,10 +2123,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122567128</v>
+        <v>122567051</v>
       </c>
       <c r="B16" t="n">
-        <v>78656</v>
+        <v>74757</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2124,21 +2139,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2148,10 +2163,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>441350</v>
+        <v>441352</v>
       </c>
       <c r="R16" t="n">
-        <v>6753388</v>
+        <v>6753455</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2210,7 +2225,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122567102</v>
+        <v>122567126</v>
       </c>
       <c r="B17" t="n">
         <v>78656</v>
@@ -2250,10 +2265,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>441305</v>
+        <v>441344</v>
       </c>
       <c r="R17" t="n">
-        <v>6753384</v>
+        <v>6753362</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2312,10 +2327,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122567103</v>
+        <v>122567081</v>
       </c>
       <c r="B18" t="n">
-        <v>78656</v>
+        <v>78393</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2328,21 +2343,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2352,10 +2367,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>441287</v>
+        <v>441344</v>
       </c>
       <c r="R18" t="n">
-        <v>6753389</v>
+        <v>6753341</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2414,7 +2429,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122567118</v>
+        <v>122567103</v>
       </c>
       <c r="B19" t="n">
         <v>78656</v>
@@ -2454,10 +2469,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>441277</v>
+        <v>441287</v>
       </c>
       <c r="R19" t="n">
-        <v>6753324</v>
+        <v>6753389</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2516,10 +2531,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122567072</v>
+        <v>122567125</v>
       </c>
       <c r="B20" t="n">
-        <v>8441</v>
+        <v>78656</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2528,43 +2543,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>441255</v>
+        <v>441356</v>
       </c>
       <c r="R20" t="n">
-        <v>6753382</v>
+        <v>6753361</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2623,10 +2633,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122567127</v>
+        <v>122567072</v>
       </c>
       <c r="B21" t="n">
-        <v>78656</v>
+        <v>8441</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2635,38 +2645,43 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>441338</v>
+        <v>441255</v>
       </c>
       <c r="R21" t="n">
-        <v>6753386</v>
+        <v>6753382</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2725,10 +2740,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122567043</v>
+        <v>122567112</v>
       </c>
       <c r="B22" t="n">
-        <v>79274</v>
+        <v>78656</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2741,21 +2756,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2765,10 +2780,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>441348</v>
+        <v>441217</v>
       </c>
       <c r="R22" t="n">
-        <v>6753422</v>
+        <v>6753556</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2827,7 +2842,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122567117</v>
+        <v>122567132</v>
       </c>
       <c r="B23" t="n">
         <v>78656</v>
@@ -2867,10 +2882,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>441193</v>
+        <v>441329</v>
       </c>
       <c r="R23" t="n">
-        <v>6753577</v>
+        <v>6753438</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2929,7 +2944,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122567109</v>
+        <v>122567121</v>
       </c>
       <c r="B24" t="n">
         <v>78656</v>
@@ -2969,10 +2984,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>441223</v>
+        <v>441306</v>
       </c>
       <c r="R24" t="n">
-        <v>6753536</v>
+        <v>6753338</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3031,10 +3046,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122567097</v>
+        <v>122567036</v>
       </c>
       <c r="B25" t="n">
-        <v>78656</v>
+        <v>79274</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3047,21 +3062,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3071,10 +3086,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>441320</v>
+        <v>441283</v>
       </c>
       <c r="R25" t="n">
-        <v>6753429</v>
+        <v>6753350</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3133,7 +3148,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122567095</v>
+        <v>122567123</v>
       </c>
       <c r="B26" t="n">
         <v>78656</v>
@@ -3173,10 +3188,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>441406</v>
+        <v>441334</v>
       </c>
       <c r="R26" t="n">
-        <v>6753439</v>
+        <v>6753341</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3235,7 +3250,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122567116</v>
+        <v>122567109</v>
       </c>
       <c r="B27" t="n">
         <v>78656</v>
@@ -3275,10 +3290,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>441199</v>
+        <v>441223</v>
       </c>
       <c r="R27" t="n">
-        <v>6753562</v>
+        <v>6753536</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3337,10 +3352,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122567113</v>
+        <v>122567089</v>
       </c>
       <c r="B28" t="n">
-        <v>78656</v>
+        <v>56593</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3349,38 +3364,43 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>441207</v>
+        <v>441283</v>
       </c>
       <c r="R28" t="n">
-        <v>6753568</v>
+        <v>6753349</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3439,10 +3459,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122567137</v>
+        <v>122567083</v>
       </c>
       <c r="B29" t="n">
-        <v>78656</v>
+        <v>78393</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3455,21 +3475,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3482,7 +3502,7 @@
         <v>441348</v>
       </c>
       <c r="R29" t="n">
-        <v>6753444</v>
+        <v>6753422</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3541,10 +3561,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122567048</v>
+        <v>122567059</v>
       </c>
       <c r="B30" t="n">
-        <v>74757</v>
+        <v>8441</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3553,28 +3573,33 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6440</v>
+        <v>106545</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
@@ -3584,7 +3609,7 @@
         <v>441302</v>
       </c>
       <c r="R30" t="n">
-        <v>6753380</v>
+        <v>6753294</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3643,10 +3668,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122567035</v>
+        <v>122567068</v>
       </c>
       <c r="B31" t="n">
-        <v>79274</v>
+        <v>8441</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3655,38 +3680,43 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>441158</v>
+        <v>441150</v>
       </c>
       <c r="R31" t="n">
-        <v>6753553</v>
+        <v>6753623</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3745,10 +3775,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122567049</v>
+        <v>122567137</v>
       </c>
       <c r="B32" t="n">
-        <v>74757</v>
+        <v>78656</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3761,21 +3791,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3785,10 +3815,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>441299</v>
+        <v>441348</v>
       </c>
       <c r="R32" t="n">
-        <v>6753387</v>
+        <v>6753444</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3847,7 +3877,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122567138</v>
+        <v>122567098</v>
       </c>
       <c r="B33" t="n">
         <v>78656</v>
@@ -3887,10 +3917,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>441383</v>
+        <v>441329</v>
       </c>
       <c r="R33" t="n">
-        <v>6753450</v>
+        <v>6753411</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3949,10 +3979,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122567056</v>
+        <v>122567034</v>
       </c>
       <c r="B34" t="n">
-        <v>57399</v>
+        <v>79274</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3965,39 +3995,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>441305</v>
+        <v>441152</v>
       </c>
       <c r="R34" t="n">
-        <v>6753366</v>
+        <v>6753562</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4056,10 +4081,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122567073</v>
+        <v>122567127</v>
       </c>
       <c r="B35" t="n">
-        <v>8441</v>
+        <v>78656</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4068,43 +4093,38 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>441269</v>
+        <v>441338</v>
       </c>
       <c r="R35" t="n">
-        <v>6753365</v>
+        <v>6753386</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4163,7 +4183,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122567105</v>
+        <v>122567101</v>
       </c>
       <c r="B36" t="n">
         <v>78656</v>
@@ -4203,10 +4223,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>441269</v>
+        <v>441301</v>
       </c>
       <c r="R36" t="n">
-        <v>6753398</v>
+        <v>6753376</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4265,10 +4285,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122567036</v>
+        <v>122567113</v>
       </c>
       <c r="B37" t="n">
-        <v>79274</v>
+        <v>78656</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4281,21 +4301,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4305,10 +4325,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>441283</v>
+        <v>441207</v>
       </c>
       <c r="R37" t="n">
-        <v>6753350</v>
+        <v>6753568</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4367,10 +4387,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122567067</v>
+        <v>122567100</v>
       </c>
       <c r="B38" t="n">
-        <v>8441</v>
+        <v>78656</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4379,43 +4399,38 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>441231</v>
+        <v>441332</v>
       </c>
       <c r="R38" t="n">
-        <v>6753537</v>
+        <v>6753382</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4474,10 +4489,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122567119</v>
+        <v>122567075</v>
       </c>
       <c r="B39" t="n">
-        <v>78656</v>
+        <v>8441</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4486,28 +4501,33 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
@@ -4576,10 +4596,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122567122</v>
+        <v>122567070</v>
       </c>
       <c r="B40" t="n">
-        <v>78656</v>
+        <v>8441</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4588,38 +4608,43 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>441315</v>
+        <v>441158</v>
       </c>
       <c r="R40" t="n">
-        <v>6753342</v>
+        <v>6753533</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4678,10 +4703,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122567041</v>
+        <v>122567120</v>
       </c>
       <c r="B41" t="n">
-        <v>79274</v>
+        <v>78656</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4694,21 +4719,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4718,10 +4743,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>441357</v>
+        <v>441289</v>
       </c>
       <c r="R41" t="n">
-        <v>6753361</v>
+        <v>6753324</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4780,10 +4805,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122567114</v>
+        <v>122567035</v>
       </c>
       <c r="B42" t="n">
-        <v>78656</v>
+        <v>79274</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4796,21 +4821,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4820,10 +4845,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>441206</v>
+        <v>441158</v>
       </c>
       <c r="R42" t="n">
-        <v>6753562</v>
+        <v>6753553</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4882,7 +4907,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122567096</v>
+        <v>122567118</v>
       </c>
       <c r="B43" t="n">
         <v>78656</v>
@@ -4922,10 +4947,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>441319</v>
+        <v>441277</v>
       </c>
       <c r="R43" t="n">
-        <v>6753442</v>
+        <v>6753324</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4984,10 +5009,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122567051</v>
+        <v>122567135</v>
       </c>
       <c r="B44" t="n">
-        <v>74757</v>
+        <v>78656</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5000,21 +5025,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5024,10 +5049,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>441352</v>
+        <v>441322</v>
       </c>
       <c r="R44" t="n">
-        <v>6753455</v>
+        <v>6753459</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5086,7 +5111,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122567101</v>
+        <v>122567096</v>
       </c>
       <c r="B45" t="n">
         <v>78656</v>
@@ -5126,10 +5151,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>441301</v>
+        <v>441319</v>
       </c>
       <c r="R45" t="n">
-        <v>6753376</v>
+        <v>6753442</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5188,7 +5213,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122567131</v>
+        <v>122567114</v>
       </c>
       <c r="B46" t="n">
         <v>78656</v>
@@ -5228,10 +5253,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>441347</v>
+        <v>441206</v>
       </c>
       <c r="R46" t="n">
-        <v>6753407</v>
+        <v>6753562</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5290,10 +5315,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122567034</v>
+        <v>122567107</v>
       </c>
       <c r="B47" t="n">
-        <v>79274</v>
+        <v>78656</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5306,21 +5331,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5330,10 +5355,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>441152</v>
+        <v>441262</v>
       </c>
       <c r="R47" t="n">
-        <v>6753562</v>
+        <v>6753417</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5392,10 +5417,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122567033</v>
+        <v>122567119</v>
       </c>
       <c r="B48" t="n">
-        <v>79274</v>
+        <v>78656</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5408,21 +5433,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5432,10 +5457,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>441194</v>
+        <v>441291</v>
       </c>
       <c r="R48" t="n">
-        <v>6753576</v>
+        <v>6753289</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5494,10 +5519,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122567134</v>
+        <v>122567046</v>
       </c>
       <c r="B49" t="n">
-        <v>78656</v>
+        <v>74757</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5510,21 +5535,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5534,10 +5559,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>441320</v>
+        <v>441304</v>
       </c>
       <c r="R49" t="n">
-        <v>6753453</v>
+        <v>6753366</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5596,7 +5621,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122567135</v>
+        <v>122567091</v>
       </c>
       <c r="B50" t="n">
         <v>78656</v>
@@ -5636,10 +5661,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>441322</v>
+        <v>441420</v>
       </c>
       <c r="R50" t="n">
-        <v>6753459</v>
+        <v>6753456</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5698,10 +5723,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122567071</v>
+        <v>122567038</v>
       </c>
       <c r="B51" t="n">
-        <v>8441</v>
+        <v>79274</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5710,43 +5735,38 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>441172</v>
+        <v>441336</v>
       </c>
       <c r="R51" t="n">
-        <v>6753515</v>
+        <v>6753344</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5805,10 +5825,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122567125</v>
+        <v>122567033</v>
       </c>
       <c r="B52" t="n">
-        <v>78656</v>
+        <v>79274</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5821,21 +5841,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5845,10 +5865,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>441356</v>
+        <v>441194</v>
       </c>
       <c r="R52" t="n">
-        <v>6753361</v>
+        <v>6753576</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5907,10 +5927,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122567070</v>
+        <v>122567133</v>
       </c>
       <c r="B53" t="n">
-        <v>8441</v>
+        <v>78656</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5919,43 +5939,38 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>441158</v>
+        <v>441321</v>
       </c>
       <c r="R53" t="n">
-        <v>6753533</v>
+        <v>6753447</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6014,10 +6029,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122567069</v>
+        <v>122567158</v>
       </c>
       <c r="B54" t="n">
-        <v>8441</v>
+        <v>78301</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6026,43 +6041,38 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>106545</v>
+        <v>353</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>441119</v>
+        <v>441248</v>
       </c>
       <c r="R54" t="n">
-        <v>6753677</v>
+        <v>6753389</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6121,7 +6131,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122567126</v>
+        <v>122567136</v>
       </c>
       <c r="B55" t="n">
         <v>78656</v>
@@ -6161,10 +6171,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>441344</v>
+        <v>441345</v>
       </c>
       <c r="R55" t="n">
-        <v>6753362</v>
+        <v>6753451</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6223,7 +6233,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122567091</v>
+        <v>122567097</v>
       </c>
       <c r="B56" t="n">
         <v>78656</v>
@@ -6263,10 +6273,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>441420</v>
+        <v>441320</v>
       </c>
       <c r="R56" t="n">
-        <v>6753456</v>
+        <v>6753429</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6325,10 +6335,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122567050</v>
+        <v>122567111</v>
       </c>
       <c r="B57" t="n">
-        <v>74757</v>
+        <v>78656</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6341,21 +6351,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6365,10 +6375,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>441314</v>
+        <v>441221</v>
       </c>
       <c r="R57" t="n">
-        <v>6753342</v>
+        <v>6753553</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6427,10 +6437,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122567099</v>
+        <v>122567071</v>
       </c>
       <c r="B58" t="n">
-        <v>78656</v>
+        <v>8441</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6439,38 +6449,43 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>441323</v>
+        <v>441172</v>
       </c>
       <c r="R58" t="n">
-        <v>6753416</v>
+        <v>6753515</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6529,10 +6544,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122567074</v>
+        <v>122567049</v>
       </c>
       <c r="B59" t="n">
-        <v>8441</v>
+        <v>74757</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6541,43 +6556,38 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>106545</v>
+        <v>6440</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>441284</v>
+        <v>441299</v>
       </c>
       <c r="R59" t="n">
-        <v>6753286</v>
+        <v>6753387</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6636,10 +6646,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122567064</v>
+        <v>122567134</v>
       </c>
       <c r="B60" t="n">
-        <v>8441</v>
+        <v>78656</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6648,43 +6658,38 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>441389</v>
+        <v>441320</v>
       </c>
       <c r="R60" t="n">
-        <v>6753439</v>
+        <v>6753453</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6743,10 +6748,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122567068</v>
+        <v>122567042</v>
       </c>
       <c r="B61" t="n">
-        <v>8441</v>
+        <v>79274</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6755,43 +6760,38 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>441150</v>
+        <v>441336</v>
       </c>
       <c r="R61" t="n">
-        <v>6753623</v>
+        <v>6753370</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6850,10 +6850,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122567077</v>
+        <v>122567122</v>
       </c>
       <c r="B62" t="n">
-        <v>8441</v>
+        <v>78656</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6862,43 +6862,38 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>441381</v>
+        <v>441315</v>
       </c>
       <c r="R62" t="n">
-        <v>6753451</v>
+        <v>6753342</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6957,10 +6952,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122567088</v>
+        <v>122567066</v>
       </c>
       <c r="B63" t="n">
-        <v>56593</v>
+        <v>8441</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -6973,27 +6968,27 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100138</v>
+        <v>106545</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="M63" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
@@ -7002,10 +6997,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>441262</v>
+        <v>441258</v>
       </c>
       <c r="R63" t="n">
-        <v>6753412</v>
+        <v>6753406</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7064,10 +7059,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122567108</v>
+        <v>122567050</v>
       </c>
       <c r="B64" t="n">
-        <v>78656</v>
+        <v>74757</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7080,21 +7075,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7104,10 +7099,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>441273</v>
+        <v>441314</v>
       </c>
       <c r="R64" t="n">
-        <v>6753425</v>
+        <v>6753342</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7166,10 +7161,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122567139</v>
+        <v>122567047</v>
       </c>
       <c r="B65" t="n">
-        <v>78656</v>
+        <v>74757</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7182,21 +7177,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7206,10 +7201,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>441430</v>
+        <v>441304</v>
       </c>
       <c r="R65" t="n">
-        <v>6753445</v>
+        <v>6753377</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7268,10 +7263,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122567059</v>
+        <v>122567106</v>
       </c>
       <c r="B66" t="n">
-        <v>8441</v>
+        <v>78656</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7280,43 +7275,38 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>441302</v>
+        <v>441266</v>
       </c>
       <c r="R66" t="n">
-        <v>6753294</v>
+        <v>6753401</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7375,10 +7365,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122567053</v>
+        <v>122567104</v>
       </c>
       <c r="B67" t="n">
-        <v>78690</v>
+        <v>78656</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7391,21 +7381,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7415,10 +7405,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>441420</v>
+        <v>441277</v>
       </c>
       <c r="R67" t="n">
-        <v>6753456</v>
+        <v>6753396</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7477,10 +7467,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122567158</v>
+        <v>122567105</v>
       </c>
       <c r="B68" t="n">
-        <v>78301</v>
+        <v>78656</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7493,21 +7483,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7517,10 +7507,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>441248</v>
+        <v>441269</v>
       </c>
       <c r="R68" t="n">
-        <v>6753389</v>
+        <v>6753398</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7579,10 +7569,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122567106</v>
+        <v>122567056</v>
       </c>
       <c r="B69" t="n">
-        <v>78656</v>
+        <v>57399</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7595,34 +7585,39 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>441266</v>
+        <v>441305</v>
       </c>
       <c r="R69" t="n">
-        <v>6753401</v>
+        <v>6753366</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7681,10 +7676,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122567123</v>
+        <v>122567077</v>
       </c>
       <c r="B70" t="n">
-        <v>78656</v>
+        <v>8441</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7693,38 +7688,43 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>441334</v>
+        <v>441381</v>
       </c>
       <c r="R70" t="n">
-        <v>6753341</v>
+        <v>6753451</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7783,7 +7783,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122567038</v>
+        <v>122567044</v>
       </c>
       <c r="B71" t="n">
         <v>79274</v>
@@ -7823,10 +7823,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>441336</v>
+        <v>441348</v>
       </c>
       <c r="R71" t="n">
-        <v>6753344</v>
+        <v>6753445</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7885,7 +7885,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122567120</v>
+        <v>122567131</v>
       </c>
       <c r="B72" t="n">
         <v>78656</v>
@@ -7925,10 +7925,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>441289</v>
+        <v>441347</v>
       </c>
       <c r="R72" t="n">
-        <v>6753324</v>
+        <v>6753407</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7987,10 +7987,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>122567089</v>
+        <v>122567102</v>
       </c>
       <c r="B73" t="n">
-        <v>56593</v>
+        <v>78656</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -7999,43 +7999,38 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>441283</v>
+        <v>441305</v>
       </c>
       <c r="R73" t="n">
-        <v>6753349</v>
+        <v>6753384</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8094,10 +8089,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>122567075</v>
+        <v>122567138</v>
       </c>
       <c r="B74" t="n">
-        <v>8441</v>
+        <v>78656</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8106,43 +8101,38 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>441291</v>
+        <v>441383</v>
       </c>
       <c r="R74" t="n">
-        <v>6753289</v>
+        <v>6753450</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8201,7 +8191,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>122567107</v>
+        <v>122567139</v>
       </c>
       <c r="B75" t="n">
         <v>78656</v>
@@ -8241,10 +8231,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>441262</v>
+        <v>441430</v>
       </c>
       <c r="R75" t="n">
-        <v>6753417</v>
+        <v>6753445</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8303,10 +8293,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>122567047</v>
+        <v>122567053</v>
       </c>
       <c r="B76" t="n">
-        <v>74757</v>
+        <v>78690</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8319,21 +8309,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6440</v>
+        <v>185</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8343,10 +8333,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>441304</v>
+        <v>441420</v>
       </c>
       <c r="R76" t="n">
-        <v>6753377</v>
+        <v>6753456</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8405,10 +8395,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>122567081</v>
+        <v>122567088</v>
       </c>
       <c r="B77" t="n">
-        <v>78393</v>
+        <v>56593</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8417,38 +8407,43 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>441344</v>
+        <v>441262</v>
       </c>
       <c r="R77" t="n">
-        <v>6753341</v>
+        <v>6753412</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8507,10 +8502,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>122567083</v>
+        <v>122567067</v>
       </c>
       <c r="B78" t="n">
-        <v>78393</v>
+        <v>8441</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8519,38 +8514,43 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>441348</v>
+        <v>441231</v>
       </c>
       <c r="R78" t="n">
-        <v>6753422</v>
+        <v>6753537</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>

--- a/artfynd/A 61943-2024 artfynd.xlsx
+++ b/artfynd/A 61943-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122567117</v>
+        <v>122567067</v>
       </c>
       <c r="B2" t="n">
-        <v>78656</v>
+        <v>8441</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,43 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>441193</v>
+        <v>441231</v>
       </c>
       <c r="R2" t="n">
-        <v>6753577</v>
+        <v>6753537</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122567064</v>
+        <v>122567097</v>
       </c>
       <c r="B3" t="n">
-        <v>8441</v>
+        <v>78656</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,43 +794,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>441389</v>
+        <v>441320</v>
       </c>
       <c r="R3" t="n">
-        <v>6753439</v>
+        <v>6753429</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,7 +884,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122567041</v>
+        <v>122567033</v>
       </c>
       <c r="B4" t="n">
         <v>79274</v>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>441357</v>
+        <v>441194</v>
       </c>
       <c r="R4" t="n">
-        <v>6753361</v>
+        <v>6753576</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,7 +986,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122567039</v>
+        <v>122567042</v>
       </c>
       <c r="B5" t="n">
         <v>79274</v>
@@ -1026,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>441344</v>
+        <v>441336</v>
       </c>
       <c r="R5" t="n">
-        <v>6753341</v>
+        <v>6753370</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122567048</v>
+        <v>122567053</v>
       </c>
       <c r="B6" t="n">
-        <v>74757</v>
+        <v>78690</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1104,21 +1104,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6440</v>
+        <v>185</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1128,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>441302</v>
+        <v>441420</v>
       </c>
       <c r="R6" t="n">
-        <v>6753380</v>
+        <v>6753456</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1190,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122567128</v>
+        <v>122567041</v>
       </c>
       <c r="B7" t="n">
-        <v>78656</v>
+        <v>79274</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1206,21 +1206,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1230,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>441350</v>
+        <v>441357</v>
       </c>
       <c r="R7" t="n">
-        <v>6753388</v>
+        <v>6753361</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1292,7 +1292,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122567095</v>
+        <v>122567101</v>
       </c>
       <c r="B8" t="n">
         <v>78656</v>
@@ -1332,10 +1332,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>441406</v>
+        <v>441301</v>
       </c>
       <c r="R8" t="n">
-        <v>6753439</v>
+        <v>6753376</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1394,7 +1394,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122567099</v>
+        <v>122567121</v>
       </c>
       <c r="B9" t="n">
         <v>78656</v>
@@ -1434,10 +1434,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>441323</v>
+        <v>441306</v>
       </c>
       <c r="R9" t="n">
-        <v>6753416</v>
+        <v>6753338</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1496,10 +1496,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122567108</v>
+        <v>122567077</v>
       </c>
       <c r="B10" t="n">
-        <v>78656</v>
+        <v>8441</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1508,38 +1508,43 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>441273</v>
+        <v>441381</v>
       </c>
       <c r="R10" t="n">
-        <v>6753425</v>
+        <v>6753451</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1598,7 +1603,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122567043</v>
+        <v>122567035</v>
       </c>
       <c r="B11" t="n">
         <v>79274</v>
@@ -1638,10 +1643,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>441348</v>
+        <v>441158</v>
       </c>
       <c r="R11" t="n">
-        <v>6753422</v>
+        <v>6753553</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1700,7 +1705,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122567116</v>
+        <v>122567102</v>
       </c>
       <c r="B12" t="n">
         <v>78656</v>
@@ -1740,10 +1745,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>441199</v>
+        <v>441305</v>
       </c>
       <c r="R12" t="n">
-        <v>6753562</v>
+        <v>6753384</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1802,10 +1807,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122567073</v>
+        <v>122567120</v>
       </c>
       <c r="B13" t="n">
-        <v>8441</v>
+        <v>78656</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1814,43 +1819,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>441269</v>
+        <v>441289</v>
       </c>
       <c r="R13" t="n">
-        <v>6753365</v>
+        <v>6753324</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1909,10 +1909,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122567074</v>
+        <v>122567107</v>
       </c>
       <c r="B14" t="n">
-        <v>8441</v>
+        <v>78656</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1921,43 +1921,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>441284</v>
+        <v>441262</v>
       </c>
       <c r="R14" t="n">
-        <v>6753286</v>
+        <v>6753417</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2016,10 +2011,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122567069</v>
+        <v>122567095</v>
       </c>
       <c r="B15" t="n">
-        <v>8441</v>
+        <v>78656</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2028,43 +2023,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>441119</v>
+        <v>441406</v>
       </c>
       <c r="R15" t="n">
-        <v>6753677</v>
+        <v>6753439</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2123,10 +2113,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122567051</v>
+        <v>122567118</v>
       </c>
       <c r="B16" t="n">
-        <v>74757</v>
+        <v>78656</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2139,21 +2129,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2163,10 +2153,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>441352</v>
+        <v>441277</v>
       </c>
       <c r="R16" t="n">
-        <v>6753455</v>
+        <v>6753324</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2225,7 +2215,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122567126</v>
+        <v>122567122</v>
       </c>
       <c r="B17" t="n">
         <v>78656</v>
@@ -2265,10 +2255,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>441344</v>
+        <v>441315</v>
       </c>
       <c r="R17" t="n">
-        <v>6753362</v>
+        <v>6753342</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2327,10 +2317,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122567081</v>
+        <v>122567096</v>
       </c>
       <c r="B18" t="n">
-        <v>78393</v>
+        <v>78656</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2343,21 +2333,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2367,10 +2357,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>441344</v>
+        <v>441319</v>
       </c>
       <c r="R18" t="n">
-        <v>6753341</v>
+        <v>6753442</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2429,10 +2419,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122567103</v>
+        <v>122567069</v>
       </c>
       <c r="B19" t="n">
-        <v>78656</v>
+        <v>8441</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2441,38 +2431,43 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>441287</v>
+        <v>441119</v>
       </c>
       <c r="R19" t="n">
-        <v>6753389</v>
+        <v>6753677</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2531,10 +2526,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122567125</v>
+        <v>122567081</v>
       </c>
       <c r="B20" t="n">
-        <v>78656</v>
+        <v>78393</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2547,21 +2542,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2571,10 +2566,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>441356</v>
+        <v>441344</v>
       </c>
       <c r="R20" t="n">
-        <v>6753361</v>
+        <v>6753341</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2633,10 +2628,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122567072</v>
+        <v>122567106</v>
       </c>
       <c r="B21" t="n">
-        <v>8441</v>
+        <v>78656</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2645,43 +2640,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>441255</v>
+        <v>441266</v>
       </c>
       <c r="R21" t="n">
-        <v>6753382</v>
+        <v>6753401</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2740,10 +2730,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122567112</v>
+        <v>122567068</v>
       </c>
       <c r="B22" t="n">
-        <v>78656</v>
+        <v>8441</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2752,38 +2742,43 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>441217</v>
+        <v>441150</v>
       </c>
       <c r="R22" t="n">
-        <v>6753556</v>
+        <v>6753623</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2842,10 +2837,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122567132</v>
+        <v>122567075</v>
       </c>
       <c r="B23" t="n">
-        <v>78656</v>
+        <v>8441</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2854,38 +2849,43 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>441329</v>
+        <v>441291</v>
       </c>
       <c r="R23" t="n">
-        <v>6753438</v>
+        <v>6753289</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2944,10 +2944,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122567121</v>
+        <v>122567050</v>
       </c>
       <c r="B24" t="n">
-        <v>78656</v>
+        <v>74757</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2960,21 +2960,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2984,10 +2984,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>441306</v>
+        <v>441314</v>
       </c>
       <c r="R24" t="n">
-        <v>6753338</v>
+        <v>6753342</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3046,7 +3046,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122567036</v>
+        <v>122567043</v>
       </c>
       <c r="B25" t="n">
         <v>79274</v>
@@ -3086,10 +3086,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>441283</v>
+        <v>441348</v>
       </c>
       <c r="R25" t="n">
-        <v>6753350</v>
+        <v>6753422</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3148,7 +3148,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122567123</v>
+        <v>122567116</v>
       </c>
       <c r="B26" t="n">
         <v>78656</v>
@@ -3188,10 +3188,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>441334</v>
+        <v>441199</v>
       </c>
       <c r="R26" t="n">
-        <v>6753341</v>
+        <v>6753562</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3250,7 +3250,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122567109</v>
+        <v>122567117</v>
       </c>
       <c r="B27" t="n">
         <v>78656</v>
@@ -3290,10 +3290,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>441223</v>
+        <v>441193</v>
       </c>
       <c r="R27" t="n">
-        <v>6753536</v>
+        <v>6753577</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3352,10 +3352,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122567089</v>
+        <v>122567036</v>
       </c>
       <c r="B28" t="n">
-        <v>56593</v>
+        <v>79274</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3364,33 +3364,28 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
@@ -3400,7 +3395,7 @@
         <v>441283</v>
       </c>
       <c r="R28" t="n">
-        <v>6753349</v>
+        <v>6753350</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3459,10 +3454,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122567083</v>
+        <v>122567088</v>
       </c>
       <c r="B29" t="n">
-        <v>78393</v>
+        <v>56593</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3471,38 +3466,43 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>441348</v>
+        <v>441262</v>
       </c>
       <c r="R29" t="n">
-        <v>6753422</v>
+        <v>6753412</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3561,10 +3561,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122567059</v>
+        <v>122567113</v>
       </c>
       <c r="B30" t="n">
-        <v>8441</v>
+        <v>78656</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3573,43 +3573,38 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>441302</v>
+        <v>441207</v>
       </c>
       <c r="R30" t="n">
-        <v>6753294</v>
+        <v>6753568</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3668,10 +3663,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122567068</v>
+        <v>122567133</v>
       </c>
       <c r="B31" t="n">
-        <v>8441</v>
+        <v>78656</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3680,43 +3675,38 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>441150</v>
+        <v>441321</v>
       </c>
       <c r="R31" t="n">
-        <v>6753623</v>
+        <v>6753447</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3775,7 +3765,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122567137</v>
+        <v>122567099</v>
       </c>
       <c r="B32" t="n">
         <v>78656</v>
@@ -3815,10 +3805,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>441348</v>
+        <v>441323</v>
       </c>
       <c r="R32" t="n">
-        <v>6753444</v>
+        <v>6753416</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3877,7 +3867,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122567098</v>
+        <v>122567105</v>
       </c>
       <c r="B33" t="n">
         <v>78656</v>
@@ -3917,10 +3907,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>441329</v>
+        <v>441269</v>
       </c>
       <c r="R33" t="n">
-        <v>6753411</v>
+        <v>6753398</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3979,10 +3969,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122567034</v>
+        <v>122567089</v>
       </c>
       <c r="B34" t="n">
-        <v>79274</v>
+        <v>56593</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3991,38 +3981,43 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>441152</v>
+        <v>441283</v>
       </c>
       <c r="R34" t="n">
-        <v>6753562</v>
+        <v>6753349</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4081,7 +4076,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122567127</v>
+        <v>122567139</v>
       </c>
       <c r="B35" t="n">
         <v>78656</v>
@@ -4121,10 +4116,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>441338</v>
+        <v>441430</v>
       </c>
       <c r="R35" t="n">
-        <v>6753386</v>
+        <v>6753445</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4183,10 +4178,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122567101</v>
+        <v>122567056</v>
       </c>
       <c r="B36" t="n">
-        <v>78656</v>
+        <v>57399</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4199,34 +4194,39 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>441301</v>
+        <v>441305</v>
       </c>
       <c r="R36" t="n">
-        <v>6753376</v>
+        <v>6753366</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4285,7 +4285,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122567113</v>
+        <v>122567126</v>
       </c>
       <c r="B37" t="n">
         <v>78656</v>
@@ -4325,10 +4325,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>441207</v>
+        <v>441344</v>
       </c>
       <c r="R37" t="n">
-        <v>6753568</v>
+        <v>6753362</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4489,10 +4489,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122567075</v>
+        <v>122567128</v>
       </c>
       <c r="B39" t="n">
-        <v>8441</v>
+        <v>78656</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4501,43 +4501,38 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>441291</v>
+        <v>441350</v>
       </c>
       <c r="R39" t="n">
-        <v>6753289</v>
+        <v>6753388</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4596,10 +4591,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122567070</v>
+        <v>122567048</v>
       </c>
       <c r="B40" t="n">
-        <v>8441</v>
+        <v>74757</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4608,43 +4603,38 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>106545</v>
+        <v>6440</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>441158</v>
+        <v>441302</v>
       </c>
       <c r="R40" t="n">
-        <v>6753533</v>
+        <v>6753380</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4703,7 +4693,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122567120</v>
+        <v>122567091</v>
       </c>
       <c r="B41" t="n">
         <v>78656</v>
@@ -4743,10 +4733,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>441289</v>
+        <v>441420</v>
       </c>
       <c r="R41" t="n">
-        <v>6753324</v>
+        <v>6753456</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4805,10 +4795,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122567035</v>
+        <v>122567119</v>
       </c>
       <c r="B42" t="n">
-        <v>79274</v>
+        <v>78656</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4821,21 +4811,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4845,10 +4835,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>441158</v>
+        <v>441291</v>
       </c>
       <c r="R42" t="n">
-        <v>6753553</v>
+        <v>6753289</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4907,7 +4897,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122567118</v>
+        <v>122567137</v>
       </c>
       <c r="B43" t="n">
         <v>78656</v>
@@ -4947,10 +4937,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>441277</v>
+        <v>441348</v>
       </c>
       <c r="R43" t="n">
-        <v>6753324</v>
+        <v>6753444</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5009,7 +4999,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122567135</v>
+        <v>122567114</v>
       </c>
       <c r="B44" t="n">
         <v>78656</v>
@@ -5049,10 +5039,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>441322</v>
+        <v>441206</v>
       </c>
       <c r="R44" t="n">
-        <v>6753459</v>
+        <v>6753562</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5111,7 +5101,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122567096</v>
+        <v>122567109</v>
       </c>
       <c r="B45" t="n">
         <v>78656</v>
@@ -5151,10 +5141,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>441319</v>
+        <v>441223</v>
       </c>
       <c r="R45" t="n">
-        <v>6753442</v>
+        <v>6753536</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5213,10 +5203,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122567114</v>
+        <v>122567059</v>
       </c>
       <c r="B46" t="n">
-        <v>78656</v>
+        <v>8441</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5225,38 +5215,43 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>441206</v>
+        <v>441302</v>
       </c>
       <c r="R46" t="n">
-        <v>6753562</v>
+        <v>6753294</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5315,7 +5310,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122567107</v>
+        <v>122567125</v>
       </c>
       <c r="B47" t="n">
         <v>78656</v>
@@ -5355,10 +5350,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>441262</v>
+        <v>441356</v>
       </c>
       <c r="R47" t="n">
-        <v>6753417</v>
+        <v>6753361</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5417,7 +5412,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122567119</v>
+        <v>122567098</v>
       </c>
       <c r="B48" t="n">
         <v>78656</v>
@@ -5457,10 +5452,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>441291</v>
+        <v>441329</v>
       </c>
       <c r="R48" t="n">
-        <v>6753289</v>
+        <v>6753411</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5519,10 +5514,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122567046</v>
+        <v>122567108</v>
       </c>
       <c r="B49" t="n">
-        <v>74757</v>
+        <v>78656</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5535,21 +5530,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5559,10 +5554,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>441304</v>
+        <v>441273</v>
       </c>
       <c r="R49" t="n">
-        <v>6753366</v>
+        <v>6753425</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5621,10 +5616,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122567091</v>
+        <v>122567051</v>
       </c>
       <c r="B50" t="n">
-        <v>78656</v>
+        <v>74757</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5637,21 +5632,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5661,10 +5656,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>441420</v>
+        <v>441352</v>
       </c>
       <c r="R50" t="n">
-        <v>6753456</v>
+        <v>6753455</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5723,10 +5718,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122567038</v>
+        <v>122567073</v>
       </c>
       <c r="B51" t="n">
-        <v>79274</v>
+        <v>8441</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5735,38 +5730,43 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>441336</v>
+        <v>441269</v>
       </c>
       <c r="R51" t="n">
-        <v>6753344</v>
+        <v>6753365</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5825,10 +5825,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122567033</v>
+        <v>122567136</v>
       </c>
       <c r="B52" t="n">
-        <v>79274</v>
+        <v>78656</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5841,21 +5841,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5865,10 +5865,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>441194</v>
+        <v>441345</v>
       </c>
       <c r="R52" t="n">
-        <v>6753576</v>
+        <v>6753451</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5927,7 +5927,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122567133</v>
+        <v>122567127</v>
       </c>
       <c r="B53" t="n">
         <v>78656</v>
@@ -5967,10 +5967,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>441321</v>
+        <v>441338</v>
       </c>
       <c r="R53" t="n">
-        <v>6753447</v>
+        <v>6753386</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6029,10 +6029,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122567158</v>
+        <v>122567134</v>
       </c>
       <c r="B54" t="n">
-        <v>78301</v>
+        <v>78656</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6045,21 +6045,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6069,10 +6069,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>441248</v>
+        <v>441320</v>
       </c>
       <c r="R54" t="n">
-        <v>6753389</v>
+        <v>6753453</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6131,10 +6131,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122567136</v>
+        <v>122567049</v>
       </c>
       <c r="B55" t="n">
-        <v>78656</v>
+        <v>74757</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6147,21 +6147,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6171,10 +6171,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>441345</v>
+        <v>441299</v>
       </c>
       <c r="R55" t="n">
-        <v>6753451</v>
+        <v>6753387</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6233,7 +6233,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122567097</v>
+        <v>122567103</v>
       </c>
       <c r="B56" t="n">
         <v>78656</v>
@@ -6273,10 +6273,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>441320</v>
+        <v>441287</v>
       </c>
       <c r="R56" t="n">
-        <v>6753429</v>
+        <v>6753389</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6335,7 +6335,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122567111</v>
+        <v>122567131</v>
       </c>
       <c r="B57" t="n">
         <v>78656</v>
@@ -6375,10 +6375,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>441221</v>
+        <v>441347</v>
       </c>
       <c r="R57" t="n">
-        <v>6753553</v>
+        <v>6753407</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6437,7 +6437,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122567071</v>
+        <v>122567066</v>
       </c>
       <c r="B58" t="n">
         <v>8441</v>
@@ -6482,10 +6482,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>441172</v>
+        <v>441258</v>
       </c>
       <c r="R58" t="n">
-        <v>6753515</v>
+        <v>6753406</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6544,10 +6544,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122567049</v>
+        <v>122567083</v>
       </c>
       <c r="B59" t="n">
-        <v>74757</v>
+        <v>78393</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6560,21 +6560,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6440</v>
+        <v>228912</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6584,10 +6584,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>441299</v>
+        <v>441348</v>
       </c>
       <c r="R59" t="n">
-        <v>6753387</v>
+        <v>6753422</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6646,10 +6646,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122567134</v>
+        <v>122567047</v>
       </c>
       <c r="B60" t="n">
-        <v>78656</v>
+        <v>74757</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6662,21 +6662,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6686,10 +6686,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>441320</v>
+        <v>441304</v>
       </c>
       <c r="R60" t="n">
-        <v>6753453</v>
+        <v>6753377</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6748,10 +6748,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122567042</v>
+        <v>122567132</v>
       </c>
       <c r="B61" t="n">
-        <v>79274</v>
+        <v>78656</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6764,21 +6764,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6788,10 +6788,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>441336</v>
+        <v>441329</v>
       </c>
       <c r="R61" t="n">
-        <v>6753370</v>
+        <v>6753438</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6850,7 +6850,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122567122</v>
+        <v>122567104</v>
       </c>
       <c r="B62" t="n">
         <v>78656</v>
@@ -6890,10 +6890,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>441315</v>
+        <v>441277</v>
       </c>
       <c r="R62" t="n">
-        <v>6753342</v>
+        <v>6753396</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6952,10 +6952,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122567066</v>
+        <v>122567138</v>
       </c>
       <c r="B63" t="n">
-        <v>8441</v>
+        <v>78656</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -6964,43 +6964,38 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>441258</v>
+        <v>441383</v>
       </c>
       <c r="R63" t="n">
-        <v>6753406</v>
+        <v>6753450</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7059,10 +7054,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122567050</v>
+        <v>122567071</v>
       </c>
       <c r="B64" t="n">
-        <v>74757</v>
+        <v>8441</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7071,38 +7066,43 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6440</v>
+        <v>106545</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>441314</v>
+        <v>441172</v>
       </c>
       <c r="R64" t="n">
-        <v>6753342</v>
+        <v>6753515</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7161,7 +7161,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122567047</v>
+        <v>122567046</v>
       </c>
       <c r="B65" t="n">
         <v>74757</v>
@@ -7204,7 +7204,7 @@
         <v>441304</v>
       </c>
       <c r="R65" t="n">
-        <v>6753377</v>
+        <v>6753366</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7263,10 +7263,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122567106</v>
+        <v>122567064</v>
       </c>
       <c r="B66" t="n">
-        <v>78656</v>
+        <v>8441</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7275,38 +7275,43 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>441266</v>
+        <v>441389</v>
       </c>
       <c r="R66" t="n">
-        <v>6753401</v>
+        <v>6753439</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7365,7 +7370,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122567104</v>
+        <v>122567112</v>
       </c>
       <c r="B67" t="n">
         <v>78656</v>
@@ -7405,10 +7410,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>441277</v>
+        <v>441217</v>
       </c>
       <c r="R67" t="n">
-        <v>6753396</v>
+        <v>6753556</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7467,7 +7472,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122567105</v>
+        <v>122567111</v>
       </c>
       <c r="B68" t="n">
         <v>78656</v>
@@ -7507,10 +7512,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>441269</v>
+        <v>441221</v>
       </c>
       <c r="R68" t="n">
-        <v>6753398</v>
+        <v>6753553</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7569,10 +7574,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122567056</v>
+        <v>122567158</v>
       </c>
       <c r="B69" t="n">
-        <v>57399</v>
+        <v>78301</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7585,39 +7590,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100049</v>
+        <v>353</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>441305</v>
+        <v>441248</v>
       </c>
       <c r="R69" t="n">
-        <v>6753366</v>
+        <v>6753389</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7676,7 +7676,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122567077</v>
+        <v>122567074</v>
       </c>
       <c r="B70" t="n">
         <v>8441</v>
@@ -7721,10 +7721,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>441381</v>
+        <v>441284</v>
       </c>
       <c r="R70" t="n">
-        <v>6753451</v>
+        <v>6753286</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7783,10 +7783,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122567044</v>
+        <v>122567070</v>
       </c>
       <c r="B71" t="n">
-        <v>79274</v>
+        <v>8441</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7795,38 +7795,43 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>441348</v>
+        <v>441158</v>
       </c>
       <c r="R71" t="n">
-        <v>6753445</v>
+        <v>6753533</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7885,10 +7890,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122567131</v>
+        <v>122567039</v>
       </c>
       <c r="B72" t="n">
-        <v>78656</v>
+        <v>79274</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -7901,21 +7906,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7925,10 +7930,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>441347</v>
+        <v>441344</v>
       </c>
       <c r="R72" t="n">
-        <v>6753407</v>
+        <v>6753341</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7987,7 +7992,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>122567102</v>
+        <v>122567123</v>
       </c>
       <c r="B73" t="n">
         <v>78656</v>
@@ -8027,10 +8032,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>441305</v>
+        <v>441334</v>
       </c>
       <c r="R73" t="n">
-        <v>6753384</v>
+        <v>6753341</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8089,10 +8094,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>122567138</v>
+        <v>122567072</v>
       </c>
       <c r="B74" t="n">
-        <v>78656</v>
+        <v>8441</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8101,38 +8106,43 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>441383</v>
+        <v>441255</v>
       </c>
       <c r="R74" t="n">
-        <v>6753450</v>
+        <v>6753382</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8191,10 +8201,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>122567139</v>
+        <v>122567044</v>
       </c>
       <c r="B75" t="n">
-        <v>78656</v>
+        <v>79274</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8207,21 +8217,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8231,7 +8241,7 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>441430</v>
+        <v>441348</v>
       </c>
       <c r="R75" t="n">
         <v>6753445</v>
@@ -8293,10 +8303,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>122567053</v>
+        <v>122567034</v>
       </c>
       <c r="B76" t="n">
-        <v>78690</v>
+        <v>79274</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8309,21 +8319,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8333,10 +8343,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>441420</v>
+        <v>441152</v>
       </c>
       <c r="R76" t="n">
-        <v>6753456</v>
+        <v>6753562</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8395,10 +8405,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>122567088</v>
+        <v>122567038</v>
       </c>
       <c r="B77" t="n">
-        <v>56593</v>
+        <v>79274</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8407,43 +8417,38 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>441262</v>
+        <v>441336</v>
       </c>
       <c r="R77" t="n">
-        <v>6753412</v>
+        <v>6753344</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8502,10 +8507,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>122567067</v>
+        <v>122567135</v>
       </c>
       <c r="B78" t="n">
-        <v>8441</v>
+        <v>78656</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8514,43 +8519,38 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>441231</v>
+        <v>441322</v>
       </c>
       <c r="R78" t="n">
-        <v>6753537</v>
+        <v>6753459</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>

--- a/artfynd/A 61943-2024 artfynd.xlsx
+++ b/artfynd/A 61943-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122567067</v>
+        <v>122567101</v>
       </c>
       <c r="B2" t="n">
-        <v>8441</v>
+        <v>78657</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,43 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>441231</v>
+        <v>441301</v>
       </c>
       <c r="R2" t="n">
-        <v>6753537</v>
+        <v>6753376</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122567097</v>
+        <v>122567107</v>
       </c>
       <c r="B3" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -822,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>441320</v>
+        <v>441262</v>
       </c>
       <c r="R3" t="n">
-        <v>6753429</v>
+        <v>6753417</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122567033</v>
+        <v>122567046</v>
       </c>
       <c r="B4" t="n">
-        <v>79274</v>
+        <v>74758</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>6440</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>441194</v>
+        <v>441304</v>
       </c>
       <c r="R4" t="n">
-        <v>6753576</v>
+        <v>6753366</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122567042</v>
+        <v>122567071</v>
       </c>
       <c r="B5" t="n">
-        <v>79274</v>
+        <v>8441</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -998,38 +993,43 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>441336</v>
+        <v>441172</v>
       </c>
       <c r="R5" t="n">
-        <v>6753370</v>
+        <v>6753515</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122567053</v>
+        <v>122567121</v>
       </c>
       <c r="B6" t="n">
-        <v>78690</v>
+        <v>78657</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1104,21 +1104,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1128,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>441420</v>
+        <v>441306</v>
       </c>
       <c r="R6" t="n">
-        <v>6753456</v>
+        <v>6753338</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1190,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122567041</v>
+        <v>122567128</v>
       </c>
       <c r="B7" t="n">
-        <v>79274</v>
+        <v>78657</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1206,21 +1206,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1230,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>441357</v>
+        <v>441350</v>
       </c>
       <c r="R7" t="n">
-        <v>6753361</v>
+        <v>6753388</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1292,10 +1292,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122567101</v>
+        <v>122567117</v>
       </c>
       <c r="B8" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1332,10 +1332,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>441301</v>
+        <v>441193</v>
       </c>
       <c r="R8" t="n">
-        <v>6753376</v>
+        <v>6753577</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1394,10 +1394,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122567121</v>
+        <v>122567118</v>
       </c>
       <c r="B9" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1434,10 +1434,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>441306</v>
+        <v>441277</v>
       </c>
       <c r="R9" t="n">
-        <v>6753338</v>
+        <v>6753324</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1496,10 +1496,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122567077</v>
+        <v>122567088</v>
       </c>
       <c r="B10" t="n">
-        <v>8441</v>
+        <v>56594</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1512,27 +1512,27 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1541,10 +1541,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>441381</v>
+        <v>441262</v>
       </c>
       <c r="R10" t="n">
-        <v>6753451</v>
+        <v>6753412</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1603,10 +1603,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122567035</v>
+        <v>122567049</v>
       </c>
       <c r="B11" t="n">
-        <v>79274</v>
+        <v>74758</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1619,21 +1619,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>6440</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1643,10 +1643,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>441158</v>
+        <v>441299</v>
       </c>
       <c r="R11" t="n">
-        <v>6753553</v>
+        <v>6753387</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1705,10 +1705,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122567102</v>
+        <v>122567048</v>
       </c>
       <c r="B12" t="n">
-        <v>78656</v>
+        <v>74758</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1721,21 +1721,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1745,10 +1745,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>441305</v>
+        <v>441302</v>
       </c>
       <c r="R12" t="n">
-        <v>6753384</v>
+        <v>6753380</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1807,10 +1807,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122567120</v>
+        <v>122567033</v>
       </c>
       <c r="B13" t="n">
-        <v>78656</v>
+        <v>79275</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1823,21 +1823,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1847,10 +1847,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>441289</v>
+        <v>441194</v>
       </c>
       <c r="R13" t="n">
-        <v>6753324</v>
+        <v>6753576</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1909,10 +1909,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122567107</v>
+        <v>122567123</v>
       </c>
       <c r="B14" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1949,10 +1949,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>441262</v>
+        <v>441334</v>
       </c>
       <c r="R14" t="n">
-        <v>6753417</v>
+        <v>6753341</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2014,7 +2014,7 @@
         <v>122567095</v>
       </c>
       <c r="B15" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2113,10 +2113,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122567118</v>
+        <v>122567138</v>
       </c>
       <c r="B16" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2153,10 +2153,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>441277</v>
+        <v>441383</v>
       </c>
       <c r="R16" t="n">
-        <v>6753324</v>
+        <v>6753450</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2215,10 +2215,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122567122</v>
+        <v>122567135</v>
       </c>
       <c r="B17" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2255,10 +2255,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>441315</v>
+        <v>441322</v>
       </c>
       <c r="R17" t="n">
-        <v>6753342</v>
+        <v>6753459</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2317,10 +2317,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122567096</v>
+        <v>122567099</v>
       </c>
       <c r="B18" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2357,10 +2357,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>441319</v>
+        <v>441323</v>
       </c>
       <c r="R18" t="n">
-        <v>6753442</v>
+        <v>6753416</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2419,10 +2419,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122567069</v>
+        <v>122567036</v>
       </c>
       <c r="B19" t="n">
-        <v>8441</v>
+        <v>79275</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2431,43 +2431,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>441119</v>
+        <v>441283</v>
       </c>
       <c r="R19" t="n">
-        <v>6753677</v>
+        <v>6753350</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2526,10 +2521,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122567081</v>
+        <v>122567064</v>
       </c>
       <c r="B20" t="n">
-        <v>78393</v>
+        <v>8441</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2538,38 +2533,43 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>441344</v>
+        <v>441389</v>
       </c>
       <c r="R20" t="n">
-        <v>6753341</v>
+        <v>6753439</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2628,10 +2628,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122567106</v>
+        <v>122567089</v>
       </c>
       <c r="B21" t="n">
-        <v>78656</v>
+        <v>56594</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2640,38 +2640,43 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>441266</v>
+        <v>441283</v>
       </c>
       <c r="R21" t="n">
-        <v>6753401</v>
+        <v>6753349</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2730,7 +2735,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122567068</v>
+        <v>122567073</v>
       </c>
       <c r="B22" t="n">
         <v>8441</v>
@@ -2775,10 +2780,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>441150</v>
+        <v>441269</v>
       </c>
       <c r="R22" t="n">
-        <v>6753623</v>
+        <v>6753365</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2837,10 +2842,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122567075</v>
+        <v>122567109</v>
       </c>
       <c r="B23" t="n">
-        <v>8441</v>
+        <v>78657</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2849,43 +2854,38 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>441291</v>
+        <v>441223</v>
       </c>
       <c r="R23" t="n">
-        <v>6753289</v>
+        <v>6753536</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2944,10 +2944,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122567050</v>
+        <v>122567034</v>
       </c>
       <c r="B24" t="n">
-        <v>74757</v>
+        <v>79275</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2960,21 +2960,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6440</v>
+        <v>6453</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2984,10 +2984,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>441314</v>
+        <v>441152</v>
       </c>
       <c r="R24" t="n">
-        <v>6753342</v>
+        <v>6753562</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3046,10 +3046,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122567043</v>
+        <v>122567112</v>
       </c>
       <c r="B25" t="n">
-        <v>79274</v>
+        <v>78657</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3062,21 +3062,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3086,10 +3086,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>441348</v>
+        <v>441217</v>
       </c>
       <c r="R25" t="n">
-        <v>6753422</v>
+        <v>6753556</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3148,10 +3148,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122567116</v>
+        <v>122567106</v>
       </c>
       <c r="B26" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3188,10 +3188,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>441199</v>
+        <v>441266</v>
       </c>
       <c r="R26" t="n">
-        <v>6753562</v>
+        <v>6753401</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3250,10 +3250,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122567117</v>
+        <v>122567043</v>
       </c>
       <c r="B27" t="n">
-        <v>78656</v>
+        <v>79275</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3266,21 +3266,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3290,10 +3290,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>441193</v>
+        <v>441348</v>
       </c>
       <c r="R27" t="n">
-        <v>6753577</v>
+        <v>6753422</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3352,10 +3352,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122567036</v>
+        <v>122567120</v>
       </c>
       <c r="B28" t="n">
-        <v>79274</v>
+        <v>78657</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3368,21 +3368,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3392,10 +3392,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>441283</v>
+        <v>441289</v>
       </c>
       <c r="R28" t="n">
-        <v>6753350</v>
+        <v>6753324</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3454,10 +3454,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122567088</v>
+        <v>122567131</v>
       </c>
       <c r="B29" t="n">
-        <v>56593</v>
+        <v>78657</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3466,43 +3466,38 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>441262</v>
+        <v>441347</v>
       </c>
       <c r="R29" t="n">
-        <v>6753412</v>
+        <v>6753407</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3561,10 +3556,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122567113</v>
+        <v>122567070</v>
       </c>
       <c r="B30" t="n">
-        <v>78656</v>
+        <v>8441</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3573,38 +3568,43 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>441207</v>
+        <v>441158</v>
       </c>
       <c r="R30" t="n">
-        <v>6753568</v>
+        <v>6753533</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3663,10 +3663,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122567133</v>
+        <v>122567050</v>
       </c>
       <c r="B31" t="n">
-        <v>78656</v>
+        <v>74758</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3679,21 +3679,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3703,10 +3703,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>441321</v>
+        <v>441314</v>
       </c>
       <c r="R31" t="n">
-        <v>6753447</v>
+        <v>6753342</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3765,10 +3765,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122567099</v>
+        <v>122567038</v>
       </c>
       <c r="B32" t="n">
-        <v>78656</v>
+        <v>79275</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3781,21 +3781,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3805,10 +3805,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>441323</v>
+        <v>441336</v>
       </c>
       <c r="R32" t="n">
-        <v>6753416</v>
+        <v>6753344</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3867,10 +3867,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122567105</v>
+        <v>122567047</v>
       </c>
       <c r="B33" t="n">
-        <v>78656</v>
+        <v>74758</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3883,21 +3883,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3907,10 +3907,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>441269</v>
+        <v>441304</v>
       </c>
       <c r="R33" t="n">
-        <v>6753398</v>
+        <v>6753377</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3969,10 +3969,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122567089</v>
+        <v>122567102</v>
       </c>
       <c r="B34" t="n">
-        <v>56593</v>
+        <v>78657</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3981,43 +3981,38 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>441283</v>
+        <v>441305</v>
       </c>
       <c r="R34" t="n">
-        <v>6753349</v>
+        <v>6753384</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4076,10 +4071,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122567139</v>
+        <v>122567137</v>
       </c>
       <c r="B35" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4116,10 +4111,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>441430</v>
+        <v>441348</v>
       </c>
       <c r="R35" t="n">
-        <v>6753445</v>
+        <v>6753444</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4178,10 +4173,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122567056</v>
+        <v>122567108</v>
       </c>
       <c r="B36" t="n">
-        <v>57399</v>
+        <v>78657</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4194,39 +4189,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>441305</v>
+        <v>441273</v>
       </c>
       <c r="R36" t="n">
-        <v>6753366</v>
+        <v>6753425</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4285,10 +4275,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122567126</v>
+        <v>122567105</v>
       </c>
       <c r="B37" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4325,10 +4315,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>441344</v>
+        <v>441269</v>
       </c>
       <c r="R37" t="n">
-        <v>6753362</v>
+        <v>6753398</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4387,10 +4377,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122567100</v>
+        <v>122567125</v>
       </c>
       <c r="B38" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4427,10 +4417,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>441332</v>
+        <v>441356</v>
       </c>
       <c r="R38" t="n">
-        <v>6753382</v>
+        <v>6753361</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4489,10 +4479,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122567128</v>
+        <v>122567041</v>
       </c>
       <c r="B39" t="n">
-        <v>78656</v>
+        <v>79275</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4505,21 +4495,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4529,10 +4519,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>441350</v>
+        <v>441357</v>
       </c>
       <c r="R39" t="n">
-        <v>6753388</v>
+        <v>6753361</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4591,10 +4581,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122567048</v>
+        <v>122567035</v>
       </c>
       <c r="B40" t="n">
-        <v>74757</v>
+        <v>79275</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4607,21 +4597,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6440</v>
+        <v>6453</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4631,10 +4621,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>441302</v>
+        <v>441158</v>
       </c>
       <c r="R40" t="n">
-        <v>6753380</v>
+        <v>6753553</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4693,10 +4683,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122567091</v>
+        <v>122567075</v>
       </c>
       <c r="B41" t="n">
-        <v>78656</v>
+        <v>8441</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4705,38 +4695,43 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>441420</v>
+        <v>441291</v>
       </c>
       <c r="R41" t="n">
-        <v>6753456</v>
+        <v>6753289</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4795,10 +4790,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122567119</v>
+        <v>122567083</v>
       </c>
       <c r="B42" t="n">
-        <v>78656</v>
+        <v>78394</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4811,21 +4806,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4835,10 +4830,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>441291</v>
+        <v>441348</v>
       </c>
       <c r="R42" t="n">
-        <v>6753289</v>
+        <v>6753422</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4897,10 +4892,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122567137</v>
+        <v>122567103</v>
       </c>
       <c r="B43" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4937,10 +4932,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>441348</v>
+        <v>441287</v>
       </c>
       <c r="R43" t="n">
-        <v>6753444</v>
+        <v>6753389</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4999,10 +4994,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122567114</v>
+        <v>122567039</v>
       </c>
       <c r="B44" t="n">
-        <v>78656</v>
+        <v>79275</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5015,21 +5010,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5039,10 +5034,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>441206</v>
+        <v>441344</v>
       </c>
       <c r="R44" t="n">
-        <v>6753562</v>
+        <v>6753341</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5101,10 +5096,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122567109</v>
+        <v>122567066</v>
       </c>
       <c r="B45" t="n">
-        <v>78656</v>
+        <v>8441</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5113,38 +5108,43 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>441223</v>
+        <v>441258</v>
       </c>
       <c r="R45" t="n">
-        <v>6753536</v>
+        <v>6753406</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5203,7 +5203,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122567059</v>
+        <v>122567069</v>
       </c>
       <c r="B46" t="n">
         <v>8441</v>
@@ -5239,7 +5239,7 @@
       <c r="I46" t="inlineStr"/>
       <c r="M46" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -5248,10 +5248,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>441302</v>
+        <v>441119</v>
       </c>
       <c r="R46" t="n">
-        <v>6753294</v>
+        <v>6753677</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5310,10 +5310,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122567125</v>
+        <v>122567081</v>
       </c>
       <c r="B47" t="n">
-        <v>78656</v>
+        <v>78394</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5326,21 +5326,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5350,10 +5350,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>441356</v>
+        <v>441344</v>
       </c>
       <c r="R47" t="n">
-        <v>6753361</v>
+        <v>6753341</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5415,7 +5415,7 @@
         <v>122567098</v>
       </c>
       <c r="B48" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5514,10 +5514,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122567108</v>
+        <v>122567134</v>
       </c>
       <c r="B49" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5554,10 +5554,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>441273</v>
+        <v>441320</v>
       </c>
       <c r="R49" t="n">
-        <v>6753425</v>
+        <v>6753453</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5616,10 +5616,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122567051</v>
+        <v>122567056</v>
       </c>
       <c r="B50" t="n">
-        <v>74757</v>
+        <v>57400</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5632,34 +5632,39 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6440</v>
+        <v>100049</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>441352</v>
+        <v>441305</v>
       </c>
       <c r="R50" t="n">
-        <v>6753455</v>
+        <v>6753366</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5718,10 +5723,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122567073</v>
+        <v>122567136</v>
       </c>
       <c r="B51" t="n">
-        <v>8441</v>
+        <v>78657</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5730,43 +5735,38 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>441269</v>
+        <v>441345</v>
       </c>
       <c r="R51" t="n">
-        <v>6753365</v>
+        <v>6753451</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5825,10 +5825,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122567136</v>
+        <v>122567133</v>
       </c>
       <c r="B52" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5865,10 +5865,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>441345</v>
+        <v>441321</v>
       </c>
       <c r="R52" t="n">
-        <v>6753451</v>
+        <v>6753447</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5927,10 +5927,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122567127</v>
+        <v>122567122</v>
       </c>
       <c r="B53" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5967,10 +5967,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>441338</v>
+        <v>441315</v>
       </c>
       <c r="R53" t="n">
-        <v>6753386</v>
+        <v>6753342</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6029,10 +6029,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122567134</v>
+        <v>122567051</v>
       </c>
       <c r="B54" t="n">
-        <v>78656</v>
+        <v>74758</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6045,21 +6045,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6069,10 +6069,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>441320</v>
+        <v>441352</v>
       </c>
       <c r="R54" t="n">
-        <v>6753453</v>
+        <v>6753455</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6131,10 +6131,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122567049</v>
+        <v>122567126</v>
       </c>
       <c r="B55" t="n">
-        <v>74757</v>
+        <v>78657</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6147,21 +6147,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6171,10 +6171,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>441299</v>
+        <v>441344</v>
       </c>
       <c r="R55" t="n">
-        <v>6753387</v>
+        <v>6753362</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6233,10 +6233,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122567103</v>
+        <v>122567042</v>
       </c>
       <c r="B56" t="n">
-        <v>78656</v>
+        <v>79275</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6249,21 +6249,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6273,10 +6273,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>441287</v>
+        <v>441336</v>
       </c>
       <c r="R56" t="n">
-        <v>6753389</v>
+        <v>6753370</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6335,10 +6335,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122567131</v>
+        <v>122567068</v>
       </c>
       <c r="B57" t="n">
-        <v>78656</v>
+        <v>8441</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6347,38 +6347,43 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>441347</v>
+        <v>441150</v>
       </c>
       <c r="R57" t="n">
-        <v>6753407</v>
+        <v>6753623</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6437,7 +6442,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122567066</v>
+        <v>122567072</v>
       </c>
       <c r="B58" t="n">
         <v>8441</v>
@@ -6482,10 +6487,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>441258</v>
+        <v>441255</v>
       </c>
       <c r="R58" t="n">
-        <v>6753406</v>
+        <v>6753382</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6544,10 +6549,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122567083</v>
+        <v>122567053</v>
       </c>
       <c r="B59" t="n">
-        <v>78393</v>
+        <v>78691</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6560,21 +6565,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>228912</v>
+        <v>185</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6584,10 +6589,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>441348</v>
+        <v>441420</v>
       </c>
       <c r="R59" t="n">
-        <v>6753422</v>
+        <v>6753456</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6646,10 +6651,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122567047</v>
+        <v>122567132</v>
       </c>
       <c r="B60" t="n">
-        <v>74757</v>
+        <v>78657</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6662,21 +6667,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6686,10 +6691,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>441304</v>
+        <v>441329</v>
       </c>
       <c r="R60" t="n">
-        <v>6753377</v>
+        <v>6753438</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6748,10 +6753,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122567132</v>
+        <v>122567139</v>
       </c>
       <c r="B61" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6788,10 +6793,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>441329</v>
+        <v>441430</v>
       </c>
       <c r="R61" t="n">
-        <v>6753438</v>
+        <v>6753445</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6850,10 +6855,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122567104</v>
+        <v>122567091</v>
       </c>
       <c r="B62" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6890,10 +6895,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>441277</v>
+        <v>441420</v>
       </c>
       <c r="R62" t="n">
-        <v>6753396</v>
+        <v>6753456</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6952,10 +6957,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122567138</v>
+        <v>122567044</v>
       </c>
       <c r="B63" t="n">
-        <v>78656</v>
+        <v>79275</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -6968,21 +6973,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6992,10 +6997,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>441383</v>
+        <v>441348</v>
       </c>
       <c r="R63" t="n">
-        <v>6753450</v>
+        <v>6753445</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7054,7 +7059,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122567071</v>
+        <v>122567067</v>
       </c>
       <c r="B64" t="n">
         <v>8441</v>
@@ -7099,10 +7104,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>441172</v>
+        <v>441231</v>
       </c>
       <c r="R64" t="n">
-        <v>6753515</v>
+        <v>6753537</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7161,10 +7166,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122567046</v>
+        <v>122567077</v>
       </c>
       <c r="B65" t="n">
-        <v>74757</v>
+        <v>8441</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7173,38 +7178,43 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6440</v>
+        <v>106545</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>441304</v>
+        <v>441381</v>
       </c>
       <c r="R65" t="n">
-        <v>6753366</v>
+        <v>6753451</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7263,10 +7273,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122567064</v>
+        <v>122567119</v>
       </c>
       <c r="B66" t="n">
-        <v>8441</v>
+        <v>78657</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7275,43 +7285,38 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>441389</v>
+        <v>441291</v>
       </c>
       <c r="R66" t="n">
-        <v>6753439</v>
+        <v>6753289</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7370,10 +7375,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122567112</v>
+        <v>122567096</v>
       </c>
       <c r="B67" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7410,10 +7415,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>441217</v>
+        <v>441319</v>
       </c>
       <c r="R67" t="n">
-        <v>6753556</v>
+        <v>6753442</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7472,10 +7477,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122567111</v>
+        <v>122567158</v>
       </c>
       <c r="B68" t="n">
-        <v>78656</v>
+        <v>78302</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7488,21 +7493,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7512,10 +7517,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>441221</v>
+        <v>441248</v>
       </c>
       <c r="R68" t="n">
-        <v>6753553</v>
+        <v>6753389</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7574,10 +7579,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122567158</v>
+        <v>122567111</v>
       </c>
       <c r="B69" t="n">
-        <v>78301</v>
+        <v>78657</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7590,21 +7595,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7614,10 +7619,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>441248</v>
+        <v>441221</v>
       </c>
       <c r="R69" t="n">
-        <v>6753389</v>
+        <v>6753553</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7783,7 +7788,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122567070</v>
+        <v>122567059</v>
       </c>
       <c r="B71" t="n">
         <v>8441</v>
@@ -7819,7 +7824,7 @@
       <c r="I71" t="inlineStr"/>
       <c r="M71" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
@@ -7828,10 +7833,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>441158</v>
+        <v>441302</v>
       </c>
       <c r="R71" t="n">
-        <v>6753533</v>
+        <v>6753294</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7890,10 +7895,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122567039</v>
+        <v>122567104</v>
       </c>
       <c r="B72" t="n">
-        <v>79274</v>
+        <v>78657</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -7906,21 +7911,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7930,10 +7935,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>441344</v>
+        <v>441277</v>
       </c>
       <c r="R72" t="n">
-        <v>6753341</v>
+        <v>6753396</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7992,10 +7997,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>122567123</v>
+        <v>122567127</v>
       </c>
       <c r="B73" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8032,10 +8037,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>441334</v>
+        <v>441338</v>
       </c>
       <c r="R73" t="n">
-        <v>6753341</v>
+        <v>6753386</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8094,10 +8099,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>122567072</v>
+        <v>122567116</v>
       </c>
       <c r="B74" t="n">
-        <v>8441</v>
+        <v>78657</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8106,43 +8111,38 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>441255</v>
+        <v>441199</v>
       </c>
       <c r="R74" t="n">
-        <v>6753382</v>
+        <v>6753562</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8201,10 +8201,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>122567044</v>
+        <v>122567100</v>
       </c>
       <c r="B75" t="n">
-        <v>79274</v>
+        <v>78657</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8217,21 +8217,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8241,10 +8241,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>441348</v>
+        <v>441332</v>
       </c>
       <c r="R75" t="n">
-        <v>6753445</v>
+        <v>6753382</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8303,10 +8303,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>122567034</v>
+        <v>122567114</v>
       </c>
       <c r="B76" t="n">
-        <v>79274</v>
+        <v>78657</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8319,21 +8319,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8343,7 +8343,7 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>441152</v>
+        <v>441206</v>
       </c>
       <c r="R76" t="n">
         <v>6753562</v>
@@ -8405,10 +8405,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>122567038</v>
+        <v>122567097</v>
       </c>
       <c r="B77" t="n">
-        <v>79274</v>
+        <v>78657</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8421,21 +8421,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8445,10 +8445,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>441336</v>
+        <v>441320</v>
       </c>
       <c r="R77" t="n">
-        <v>6753344</v>
+        <v>6753429</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8507,10 +8507,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>122567135</v>
+        <v>122567113</v>
       </c>
       <c r="B78" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8547,10 +8547,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>441322</v>
+        <v>441207</v>
       </c>
       <c r="R78" t="n">
-        <v>6753459</v>
+        <v>6753568</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>

--- a/artfynd/A 61943-2024 artfynd.xlsx
+++ b/artfynd/A 61943-2024 artfynd.xlsx
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122567071</v>
+        <v>122567121</v>
       </c>
       <c r="B5" t="n">
-        <v>8441</v>
+        <v>78657</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,43 +993,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>441172</v>
+        <v>441306</v>
       </c>
       <c r="R5" t="n">
-        <v>6753515</v>
+        <v>6753338</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,7 +1083,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122567121</v>
+        <v>122567128</v>
       </c>
       <c r="B6" t="n">
         <v>78657</v>
@@ -1128,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>441306</v>
+        <v>441350</v>
       </c>
       <c r="R6" t="n">
-        <v>6753338</v>
+        <v>6753388</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1190,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122567128</v>
+        <v>122567071</v>
       </c>
       <c r="B7" t="n">
-        <v>78657</v>
+        <v>8441</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1202,38 +1197,43 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>441350</v>
+        <v>441172</v>
       </c>
       <c r="R7" t="n">
-        <v>6753388</v>
+        <v>6753515</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1705,10 +1705,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122567048</v>
+        <v>122567033</v>
       </c>
       <c r="B12" t="n">
-        <v>74758</v>
+        <v>79275</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1721,21 +1721,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6440</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1745,10 +1745,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>441302</v>
+        <v>441194</v>
       </c>
       <c r="R12" t="n">
-        <v>6753380</v>
+        <v>6753576</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1807,10 +1807,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122567033</v>
+        <v>122567048</v>
       </c>
       <c r="B13" t="n">
-        <v>79275</v>
+        <v>74758</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1823,21 +1823,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>6440</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1847,10 +1847,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>441194</v>
+        <v>441302</v>
       </c>
       <c r="R13" t="n">
-        <v>6753576</v>
+        <v>6753380</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1909,7 +1909,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122567123</v>
+        <v>122567099</v>
       </c>
       <c r="B14" t="n">
         <v>78657</v>
@@ -1949,10 +1949,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>441334</v>
+        <v>441323</v>
       </c>
       <c r="R14" t="n">
-        <v>6753341</v>
+        <v>6753416</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2011,10 +2011,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122567095</v>
+        <v>122567064</v>
       </c>
       <c r="B15" t="n">
-        <v>78657</v>
+        <v>8441</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2023,35 +2023,40 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>441406</v>
+        <v>441389</v>
       </c>
       <c r="R15" t="n">
         <v>6753439</v>
@@ -2113,7 +2118,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122567138</v>
+        <v>122567123</v>
       </c>
       <c r="B16" t="n">
         <v>78657</v>
@@ -2153,10 +2158,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>441383</v>
+        <v>441334</v>
       </c>
       <c r="R16" t="n">
-        <v>6753450</v>
+        <v>6753341</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2215,7 +2220,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122567135</v>
+        <v>122567095</v>
       </c>
       <c r="B17" t="n">
         <v>78657</v>
@@ -2255,10 +2260,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>441322</v>
+        <v>441406</v>
       </c>
       <c r="R17" t="n">
-        <v>6753459</v>
+        <v>6753439</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2317,7 +2322,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122567099</v>
+        <v>122567138</v>
       </c>
       <c r="B18" t="n">
         <v>78657</v>
@@ -2357,10 +2362,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>441323</v>
+        <v>441383</v>
       </c>
       <c r="R18" t="n">
-        <v>6753416</v>
+        <v>6753450</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2419,10 +2424,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122567036</v>
+        <v>122567135</v>
       </c>
       <c r="B19" t="n">
-        <v>79275</v>
+        <v>78657</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2435,21 +2440,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2459,10 +2464,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>441283</v>
+        <v>441322</v>
       </c>
       <c r="R19" t="n">
-        <v>6753350</v>
+        <v>6753459</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2521,10 +2526,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122567064</v>
+        <v>122567036</v>
       </c>
       <c r="B20" t="n">
-        <v>8441</v>
+        <v>79275</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2533,43 +2538,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>441389</v>
+        <v>441283</v>
       </c>
       <c r="R20" t="n">
-        <v>6753439</v>
+        <v>6753350</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2944,10 +2944,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122567034</v>
+        <v>122567112</v>
       </c>
       <c r="B24" t="n">
-        <v>79275</v>
+        <v>78657</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2960,21 +2960,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2984,10 +2984,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>441152</v>
+        <v>441217</v>
       </c>
       <c r="R24" t="n">
-        <v>6753562</v>
+        <v>6753556</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3046,7 +3046,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122567112</v>
+        <v>122567106</v>
       </c>
       <c r="B25" t="n">
         <v>78657</v>
@@ -3086,10 +3086,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>441217</v>
+        <v>441266</v>
       </c>
       <c r="R25" t="n">
-        <v>6753556</v>
+        <v>6753401</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3148,10 +3148,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122567106</v>
+        <v>122567034</v>
       </c>
       <c r="B26" t="n">
-        <v>78657</v>
+        <v>79275</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3164,21 +3164,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3188,10 +3188,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>441266</v>
+        <v>441152</v>
       </c>
       <c r="R26" t="n">
-        <v>6753401</v>
+        <v>6753562</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -4994,10 +4994,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122567039</v>
+        <v>122567098</v>
       </c>
       <c r="B44" t="n">
-        <v>79275</v>
+        <v>78657</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5010,21 +5010,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5034,10 +5034,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>441344</v>
+        <v>441329</v>
       </c>
       <c r="R44" t="n">
-        <v>6753341</v>
+        <v>6753411</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5096,10 +5096,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122567066</v>
+        <v>122567134</v>
       </c>
       <c r="B45" t="n">
-        <v>8441</v>
+        <v>78657</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5108,43 +5108,38 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>441258</v>
+        <v>441320</v>
       </c>
       <c r="R45" t="n">
-        <v>6753406</v>
+        <v>6753453</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5203,10 +5198,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122567069</v>
+        <v>122567039</v>
       </c>
       <c r="B46" t="n">
-        <v>8441</v>
+        <v>79275</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5215,43 +5210,38 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>441119</v>
+        <v>441344</v>
       </c>
       <c r="R46" t="n">
-        <v>6753677</v>
+        <v>6753341</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5310,10 +5300,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122567081</v>
+        <v>122567066</v>
       </c>
       <c r="B47" t="n">
-        <v>78394</v>
+        <v>8441</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5322,38 +5312,43 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>441344</v>
+        <v>441258</v>
       </c>
       <c r="R47" t="n">
-        <v>6753341</v>
+        <v>6753406</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5412,10 +5407,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122567098</v>
+        <v>122567069</v>
       </c>
       <c r="B48" t="n">
-        <v>78657</v>
+        <v>8441</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5424,38 +5419,43 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>441329</v>
+        <v>441119</v>
       </c>
       <c r="R48" t="n">
-        <v>6753411</v>
+        <v>6753677</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5514,10 +5514,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122567134</v>
+        <v>122567081</v>
       </c>
       <c r="B49" t="n">
-        <v>78657</v>
+        <v>78394</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5530,21 +5530,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5554,10 +5554,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>441320</v>
+        <v>441344</v>
       </c>
       <c r="R49" t="n">
-        <v>6753453</v>
+        <v>6753341</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6131,10 +6131,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122567126</v>
+        <v>122567042</v>
       </c>
       <c r="B55" t="n">
-        <v>78657</v>
+        <v>79275</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6147,21 +6147,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6171,10 +6171,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>441344</v>
+        <v>441336</v>
       </c>
       <c r="R55" t="n">
-        <v>6753362</v>
+        <v>6753370</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6233,10 +6233,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122567042</v>
+        <v>122567068</v>
       </c>
       <c r="B56" t="n">
-        <v>79275</v>
+        <v>8441</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6245,38 +6245,43 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>441336</v>
+        <v>441150</v>
       </c>
       <c r="R56" t="n">
-        <v>6753370</v>
+        <v>6753623</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6335,10 +6340,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122567068</v>
+        <v>122567126</v>
       </c>
       <c r="B57" t="n">
-        <v>8441</v>
+        <v>78657</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6347,43 +6352,38 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>441150</v>
+        <v>441344</v>
       </c>
       <c r="R57" t="n">
-        <v>6753623</v>
+        <v>6753362</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7579,10 +7579,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122567111</v>
+        <v>122567074</v>
       </c>
       <c r="B69" t="n">
-        <v>78657</v>
+        <v>8441</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7591,38 +7591,43 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>441221</v>
+        <v>441284</v>
       </c>
       <c r="R69" t="n">
-        <v>6753553</v>
+        <v>6753286</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7681,10 +7686,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122567074</v>
+        <v>122567111</v>
       </c>
       <c r="B70" t="n">
-        <v>8441</v>
+        <v>78657</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7693,43 +7698,38 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>441284</v>
+        <v>441221</v>
       </c>
       <c r="R70" t="n">
-        <v>6753286</v>
+        <v>6753553</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7788,10 +7788,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122567059</v>
+        <v>122567104</v>
       </c>
       <c r="B71" t="n">
-        <v>8441</v>
+        <v>78657</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7800,43 +7800,38 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>441302</v>
+        <v>441277</v>
       </c>
       <c r="R71" t="n">
-        <v>6753294</v>
+        <v>6753396</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7895,10 +7890,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122567104</v>
+        <v>122567059</v>
       </c>
       <c r="B72" t="n">
-        <v>78657</v>
+        <v>8441</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -7907,38 +7902,43 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>441277</v>
+        <v>441302</v>
       </c>
       <c r="R72" t="n">
-        <v>6753396</v>
+        <v>6753294</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>

--- a/artfynd/A 61943-2024 artfynd.xlsx
+++ b/artfynd/A 61943-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122567101</v>
+        <v>122567070</v>
       </c>
       <c r="B2" t="n">
-        <v>78657</v>
+        <v>8441</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,43 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>441301</v>
+        <v>441158</v>
       </c>
       <c r="R2" t="n">
-        <v>6753376</v>
+        <v>6753533</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122567107</v>
+        <v>122567095</v>
       </c>
       <c r="B3" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>441262</v>
+        <v>441406</v>
       </c>
       <c r="R3" t="n">
-        <v>6753417</v>
+        <v>6753439</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122567046</v>
+        <v>122567117</v>
       </c>
       <c r="B4" t="n">
-        <v>74758</v>
+        <v>78660</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>441304</v>
+        <v>441193</v>
       </c>
       <c r="R4" t="n">
-        <v>6753366</v>
+        <v>6753577</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122567121</v>
+        <v>122567138</v>
       </c>
       <c r="B5" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1021,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>441306</v>
+        <v>441383</v>
       </c>
       <c r="R5" t="n">
-        <v>6753338</v>
+        <v>6753450</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122567128</v>
+        <v>122567122</v>
       </c>
       <c r="B6" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1123,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>441350</v>
+        <v>441315</v>
       </c>
       <c r="R6" t="n">
-        <v>6753388</v>
+        <v>6753342</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,7 +1190,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122567071</v>
+        <v>122567064</v>
       </c>
       <c r="B7" t="n">
         <v>8441</v>
@@ -1230,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>441172</v>
+        <v>441389</v>
       </c>
       <c r="R7" t="n">
-        <v>6753515</v>
+        <v>6753439</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1292,10 +1297,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122567117</v>
+        <v>122567068</v>
       </c>
       <c r="B8" t="n">
-        <v>78657</v>
+        <v>8441</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1304,38 +1309,43 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>441193</v>
+        <v>441150</v>
       </c>
       <c r="R8" t="n">
-        <v>6753577</v>
+        <v>6753623</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1394,10 +1404,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122567118</v>
+        <v>122567106</v>
       </c>
       <c r="B9" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1434,10 +1444,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>441277</v>
+        <v>441266</v>
       </c>
       <c r="R9" t="n">
-        <v>6753324</v>
+        <v>6753401</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1496,10 +1506,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122567088</v>
+        <v>122567134</v>
       </c>
       <c r="B10" t="n">
-        <v>56594</v>
+        <v>78660</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1508,43 +1518,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>441262</v>
+        <v>441320</v>
       </c>
       <c r="R10" t="n">
-        <v>6753412</v>
+        <v>6753453</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1603,10 +1608,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122567049</v>
+        <v>122567113</v>
       </c>
       <c r="B11" t="n">
-        <v>74758</v>
+        <v>78660</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1619,21 +1624,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1643,10 +1648,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>441299</v>
+        <v>441207</v>
       </c>
       <c r="R11" t="n">
-        <v>6753387</v>
+        <v>6753568</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1705,10 +1710,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122567033</v>
+        <v>122567131</v>
       </c>
       <c r="B12" t="n">
-        <v>79275</v>
+        <v>78660</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1721,21 +1726,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1745,10 +1750,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>441194</v>
+        <v>441347</v>
       </c>
       <c r="R12" t="n">
-        <v>6753576</v>
+        <v>6753407</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1807,10 +1812,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122567048</v>
+        <v>122567135</v>
       </c>
       <c r="B13" t="n">
-        <v>74758</v>
+        <v>78660</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1823,21 +1828,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1847,10 +1852,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>441302</v>
+        <v>441322</v>
       </c>
       <c r="R13" t="n">
-        <v>6753380</v>
+        <v>6753459</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1909,10 +1914,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122567099</v>
+        <v>122567039</v>
       </c>
       <c r="B14" t="n">
-        <v>78657</v>
+        <v>79278</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1925,21 +1930,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1949,10 +1954,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>441323</v>
+        <v>441344</v>
       </c>
       <c r="R14" t="n">
-        <v>6753416</v>
+        <v>6753341</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2011,7 +2016,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122567064</v>
+        <v>122567073</v>
       </c>
       <c r="B15" t="n">
         <v>8441</v>
@@ -2056,10 +2061,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>441389</v>
+        <v>441269</v>
       </c>
       <c r="R15" t="n">
-        <v>6753439</v>
+        <v>6753365</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2118,10 +2123,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122567123</v>
+        <v>122567050</v>
       </c>
       <c r="B16" t="n">
-        <v>78657</v>
+        <v>74761</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2134,21 +2139,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2158,10 +2163,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>441334</v>
+        <v>441314</v>
       </c>
       <c r="R16" t="n">
-        <v>6753341</v>
+        <v>6753342</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2220,10 +2225,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122567095</v>
+        <v>122567081</v>
       </c>
       <c r="B17" t="n">
-        <v>78657</v>
+        <v>78397</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2236,21 +2241,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2260,10 +2265,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>441406</v>
+        <v>441344</v>
       </c>
       <c r="R17" t="n">
-        <v>6753439</v>
+        <v>6753341</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2322,10 +2327,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122567138</v>
+        <v>122567102</v>
       </c>
       <c r="B18" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2362,10 +2367,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>441383</v>
+        <v>441305</v>
       </c>
       <c r="R18" t="n">
-        <v>6753450</v>
+        <v>6753384</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2424,10 +2429,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122567135</v>
+        <v>122567035</v>
       </c>
       <c r="B19" t="n">
-        <v>78657</v>
+        <v>79278</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2440,21 +2445,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2464,10 +2469,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>441322</v>
+        <v>441158</v>
       </c>
       <c r="R19" t="n">
-        <v>6753459</v>
+        <v>6753553</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2526,10 +2531,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122567036</v>
+        <v>122567077</v>
       </c>
       <c r="B20" t="n">
-        <v>79275</v>
+        <v>8441</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2538,38 +2543,43 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>441283</v>
+        <v>441381</v>
       </c>
       <c r="R20" t="n">
-        <v>6753350</v>
+        <v>6753451</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2628,10 +2638,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122567089</v>
+        <v>122567112</v>
       </c>
       <c r="B21" t="n">
-        <v>56594</v>
+        <v>78660</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2640,43 +2650,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>441283</v>
+        <v>441217</v>
       </c>
       <c r="R21" t="n">
-        <v>6753349</v>
+        <v>6753556</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2735,10 +2740,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122567073</v>
+        <v>122567136</v>
       </c>
       <c r="B22" t="n">
-        <v>8441</v>
+        <v>78660</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2747,43 +2752,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>441269</v>
+        <v>441345</v>
       </c>
       <c r="R22" t="n">
-        <v>6753365</v>
+        <v>6753451</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2842,10 +2842,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122567109</v>
+        <v>122567103</v>
       </c>
       <c r="B23" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2882,10 +2882,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>441223</v>
+        <v>441287</v>
       </c>
       <c r="R23" t="n">
-        <v>6753536</v>
+        <v>6753389</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2944,10 +2944,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122567112</v>
+        <v>122567051</v>
       </c>
       <c r="B24" t="n">
-        <v>78657</v>
+        <v>74761</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2960,21 +2960,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2984,10 +2984,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>441217</v>
+        <v>441352</v>
       </c>
       <c r="R24" t="n">
-        <v>6753556</v>
+        <v>6753455</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3046,10 +3046,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122567106</v>
+        <v>122567121</v>
       </c>
       <c r="B25" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3086,10 +3086,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>441266</v>
+        <v>441306</v>
       </c>
       <c r="R25" t="n">
-        <v>6753401</v>
+        <v>6753338</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3148,10 +3148,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122567034</v>
+        <v>122567042</v>
       </c>
       <c r="B26" t="n">
-        <v>79275</v>
+        <v>79278</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3188,10 +3188,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>441152</v>
+        <v>441336</v>
       </c>
       <c r="R26" t="n">
-        <v>6753562</v>
+        <v>6753370</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3250,10 +3250,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122567043</v>
+        <v>122567036</v>
       </c>
       <c r="B27" t="n">
-        <v>79275</v>
+        <v>79278</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3290,10 +3290,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>441348</v>
+        <v>441283</v>
       </c>
       <c r="R27" t="n">
-        <v>6753422</v>
+        <v>6753350</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3352,10 +3352,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122567120</v>
+        <v>122567033</v>
       </c>
       <c r="B28" t="n">
-        <v>78657</v>
+        <v>79278</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3368,21 +3368,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3392,10 +3392,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>441289</v>
+        <v>441194</v>
       </c>
       <c r="R28" t="n">
-        <v>6753324</v>
+        <v>6753576</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3454,10 +3454,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122567131</v>
+        <v>122567089</v>
       </c>
       <c r="B29" t="n">
-        <v>78657</v>
+        <v>56594</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3466,38 +3466,43 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>441347</v>
+        <v>441283</v>
       </c>
       <c r="R29" t="n">
-        <v>6753407</v>
+        <v>6753349</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3556,10 +3561,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122567070</v>
+        <v>122567088</v>
       </c>
       <c r="B30" t="n">
-        <v>8441</v>
+        <v>56594</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3572,27 +3577,27 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -3601,10 +3606,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>441158</v>
+        <v>441262</v>
       </c>
       <c r="R30" t="n">
-        <v>6753533</v>
+        <v>6753412</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3663,10 +3668,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122567050</v>
+        <v>122567139</v>
       </c>
       <c r="B31" t="n">
-        <v>74758</v>
+        <v>78660</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3679,21 +3684,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3703,10 +3708,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>441314</v>
+        <v>441430</v>
       </c>
       <c r="R31" t="n">
-        <v>6753342</v>
+        <v>6753445</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3765,10 +3770,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122567038</v>
+        <v>122567066</v>
       </c>
       <c r="B32" t="n">
-        <v>79275</v>
+        <v>8441</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3777,38 +3782,43 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>441336</v>
+        <v>441258</v>
       </c>
       <c r="R32" t="n">
-        <v>6753344</v>
+        <v>6753406</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3867,10 +3877,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122567047</v>
+        <v>122567041</v>
       </c>
       <c r="B33" t="n">
-        <v>74758</v>
+        <v>79278</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3883,21 +3893,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6440</v>
+        <v>6453</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3907,10 +3917,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>441304</v>
+        <v>441357</v>
       </c>
       <c r="R33" t="n">
-        <v>6753377</v>
+        <v>6753361</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3969,10 +3979,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122567102</v>
+        <v>122567038</v>
       </c>
       <c r="B34" t="n">
-        <v>78657</v>
+        <v>79278</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3985,21 +3995,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4009,10 +4019,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>441305</v>
+        <v>441336</v>
       </c>
       <c r="R34" t="n">
-        <v>6753384</v>
+        <v>6753344</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4071,10 +4081,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122567137</v>
+        <v>122567116</v>
       </c>
       <c r="B35" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4111,10 +4121,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>441348</v>
+        <v>441199</v>
       </c>
       <c r="R35" t="n">
-        <v>6753444</v>
+        <v>6753562</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4176,7 +4186,7 @@
         <v>122567108</v>
       </c>
       <c r="B36" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4275,10 +4285,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122567105</v>
+        <v>122567137</v>
       </c>
       <c r="B37" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4315,10 +4325,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>441269</v>
+        <v>441348</v>
       </c>
       <c r="R37" t="n">
-        <v>6753398</v>
+        <v>6753444</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4377,10 +4387,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122567125</v>
+        <v>122567072</v>
       </c>
       <c r="B38" t="n">
-        <v>78657</v>
+        <v>8441</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4389,38 +4399,43 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>441356</v>
+        <v>441255</v>
       </c>
       <c r="R38" t="n">
-        <v>6753361</v>
+        <v>6753382</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4479,10 +4494,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122567041</v>
+        <v>122567126</v>
       </c>
       <c r="B39" t="n">
-        <v>79275</v>
+        <v>78660</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4495,21 +4510,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4519,10 +4534,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>441357</v>
+        <v>441344</v>
       </c>
       <c r="R39" t="n">
-        <v>6753361</v>
+        <v>6753362</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4581,10 +4596,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122567035</v>
+        <v>122567120</v>
       </c>
       <c r="B40" t="n">
-        <v>79275</v>
+        <v>78660</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4597,21 +4612,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4621,10 +4636,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>441158</v>
+        <v>441289</v>
       </c>
       <c r="R40" t="n">
-        <v>6753553</v>
+        <v>6753324</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4683,10 +4698,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122567075</v>
+        <v>122567044</v>
       </c>
       <c r="B41" t="n">
-        <v>8441</v>
+        <v>79278</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4695,43 +4710,38 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>441291</v>
+        <v>441348</v>
       </c>
       <c r="R41" t="n">
-        <v>6753289</v>
+        <v>6753445</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4790,10 +4800,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122567083</v>
+        <v>122567091</v>
       </c>
       <c r="B42" t="n">
-        <v>78394</v>
+        <v>78660</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4806,21 +4816,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4830,10 +4840,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>441348</v>
+        <v>441420</v>
       </c>
       <c r="R42" t="n">
-        <v>6753422</v>
+        <v>6753456</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4892,10 +4902,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122567103</v>
+        <v>122567049</v>
       </c>
       <c r="B43" t="n">
-        <v>78657</v>
+        <v>74761</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4908,21 +4918,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4932,10 +4942,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>441287</v>
+        <v>441299</v>
       </c>
       <c r="R43" t="n">
-        <v>6753389</v>
+        <v>6753387</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4994,10 +5004,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122567098</v>
+        <v>122567105</v>
       </c>
       <c r="B44" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5034,10 +5044,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>441329</v>
+        <v>441269</v>
       </c>
       <c r="R44" t="n">
-        <v>6753411</v>
+        <v>6753398</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5096,10 +5106,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122567134</v>
+        <v>122567074</v>
       </c>
       <c r="B45" t="n">
-        <v>78657</v>
+        <v>8441</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5108,38 +5118,43 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>441320</v>
+        <v>441284</v>
       </c>
       <c r="R45" t="n">
-        <v>6753453</v>
+        <v>6753286</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5198,10 +5213,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122567039</v>
+        <v>122567069</v>
       </c>
       <c r="B46" t="n">
-        <v>79275</v>
+        <v>8441</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5210,38 +5225,43 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>441344</v>
+        <v>441119</v>
       </c>
       <c r="R46" t="n">
-        <v>6753341</v>
+        <v>6753677</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5300,10 +5320,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122567066</v>
+        <v>122567097</v>
       </c>
       <c r="B47" t="n">
-        <v>8441</v>
+        <v>78660</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5312,43 +5332,38 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>441258</v>
+        <v>441320</v>
       </c>
       <c r="R47" t="n">
-        <v>6753406</v>
+        <v>6753429</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5407,10 +5422,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122567069</v>
+        <v>122567119</v>
       </c>
       <c r="B48" t="n">
-        <v>8441</v>
+        <v>78660</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5419,43 +5434,38 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>441119</v>
+        <v>441291</v>
       </c>
       <c r="R48" t="n">
-        <v>6753677</v>
+        <v>6753289</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5514,10 +5524,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122567081</v>
+        <v>122567096</v>
       </c>
       <c r="B49" t="n">
-        <v>78394</v>
+        <v>78660</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5530,21 +5540,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5554,10 +5564,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>441344</v>
+        <v>441319</v>
       </c>
       <c r="R49" t="n">
-        <v>6753341</v>
+        <v>6753442</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5616,10 +5626,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122567056</v>
+        <v>122567034</v>
       </c>
       <c r="B50" t="n">
-        <v>57400</v>
+        <v>79278</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5632,39 +5642,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>441305</v>
+        <v>441152</v>
       </c>
       <c r="R50" t="n">
-        <v>6753366</v>
+        <v>6753562</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5723,10 +5728,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122567136</v>
+        <v>122567128</v>
       </c>
       <c r="B51" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5763,10 +5768,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>441345</v>
+        <v>441350</v>
       </c>
       <c r="R51" t="n">
-        <v>6753451</v>
+        <v>6753388</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5825,10 +5830,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122567133</v>
+        <v>122567111</v>
       </c>
       <c r="B52" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5865,10 +5870,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>441321</v>
+        <v>441221</v>
       </c>
       <c r="R52" t="n">
-        <v>6753447</v>
+        <v>6753553</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5927,10 +5932,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122567122</v>
+        <v>122567104</v>
       </c>
       <c r="B53" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5967,10 +5972,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>441315</v>
+        <v>441277</v>
       </c>
       <c r="R53" t="n">
-        <v>6753342</v>
+        <v>6753396</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6029,10 +6034,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122567051</v>
+        <v>122567046</v>
       </c>
       <c r="B54" t="n">
-        <v>74758</v>
+        <v>74761</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6069,10 +6074,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>441352</v>
+        <v>441304</v>
       </c>
       <c r="R54" t="n">
-        <v>6753455</v>
+        <v>6753366</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6131,10 +6136,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122567042</v>
+        <v>122567075</v>
       </c>
       <c r="B55" t="n">
-        <v>79275</v>
+        <v>8441</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6143,38 +6148,43 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>441336</v>
+        <v>441291</v>
       </c>
       <c r="R55" t="n">
-        <v>6753370</v>
+        <v>6753289</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6233,7 +6243,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122567068</v>
+        <v>122567059</v>
       </c>
       <c r="B56" t="n">
         <v>8441</v>
@@ -6269,7 +6279,7 @@
       <c r="I56" t="inlineStr"/>
       <c r="M56" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -6278,10 +6288,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>441150</v>
+        <v>441302</v>
       </c>
       <c r="R56" t="n">
-        <v>6753623</v>
+        <v>6753294</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6340,10 +6350,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122567126</v>
+        <v>122567114</v>
       </c>
       <c r="B57" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6380,10 +6390,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>441344</v>
+        <v>441206</v>
       </c>
       <c r="R57" t="n">
-        <v>6753362</v>
+        <v>6753562</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6442,10 +6452,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122567072</v>
+        <v>122567083</v>
       </c>
       <c r="B58" t="n">
-        <v>8441</v>
+        <v>78397</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6454,43 +6464,38 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>441255</v>
+        <v>441348</v>
       </c>
       <c r="R58" t="n">
-        <v>6753382</v>
+        <v>6753422</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6549,10 +6554,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122567053</v>
+        <v>122567056</v>
       </c>
       <c r="B59" t="n">
-        <v>78691</v>
+        <v>57400</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6565,34 +6570,39 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>185</v>
+        <v>100049</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>441420</v>
+        <v>441305</v>
       </c>
       <c r="R59" t="n">
-        <v>6753456</v>
+        <v>6753366</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6651,10 +6661,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122567132</v>
+        <v>122567118</v>
       </c>
       <c r="B60" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6691,10 +6701,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>441329</v>
+        <v>441277</v>
       </c>
       <c r="R60" t="n">
-        <v>6753438</v>
+        <v>6753324</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6753,10 +6763,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122567139</v>
+        <v>122567098</v>
       </c>
       <c r="B61" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6793,10 +6803,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>441430</v>
+        <v>441329</v>
       </c>
       <c r="R61" t="n">
-        <v>6753445</v>
+        <v>6753411</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6855,10 +6865,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122567091</v>
+        <v>122567133</v>
       </c>
       <c r="B62" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6895,10 +6905,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>441420</v>
+        <v>441321</v>
       </c>
       <c r="R62" t="n">
-        <v>6753456</v>
+        <v>6753447</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6957,10 +6967,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122567044</v>
+        <v>122567125</v>
       </c>
       <c r="B63" t="n">
-        <v>79275</v>
+        <v>78660</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -6973,21 +6983,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6997,10 +7007,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>441348</v>
+        <v>441356</v>
       </c>
       <c r="R63" t="n">
-        <v>6753445</v>
+        <v>6753361</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7059,10 +7069,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122567067</v>
+        <v>122567107</v>
       </c>
       <c r="B64" t="n">
-        <v>8441</v>
+        <v>78660</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7071,43 +7081,38 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>441231</v>
+        <v>441262</v>
       </c>
       <c r="R64" t="n">
-        <v>6753537</v>
+        <v>6753417</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7166,10 +7171,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122567077</v>
+        <v>122567123</v>
       </c>
       <c r="B65" t="n">
-        <v>8441</v>
+        <v>78660</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7178,43 +7183,38 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>441381</v>
+        <v>441334</v>
       </c>
       <c r="R65" t="n">
-        <v>6753451</v>
+        <v>6753341</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7273,10 +7273,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122567119</v>
+        <v>122567071</v>
       </c>
       <c r="B66" t="n">
-        <v>78657</v>
+        <v>8441</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7285,38 +7285,43 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>441291</v>
+        <v>441172</v>
       </c>
       <c r="R66" t="n">
-        <v>6753289</v>
+        <v>6753515</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7375,10 +7380,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122567096</v>
+        <v>122567099</v>
       </c>
       <c r="B67" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7415,10 +7420,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>441319</v>
+        <v>441323</v>
       </c>
       <c r="R67" t="n">
-        <v>6753442</v>
+        <v>6753416</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7477,10 +7482,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122567158</v>
+        <v>122567109</v>
       </c>
       <c r="B68" t="n">
-        <v>78302</v>
+        <v>78660</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7493,21 +7498,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7517,10 +7522,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>441248</v>
+        <v>441223</v>
       </c>
       <c r="R68" t="n">
-        <v>6753389</v>
+        <v>6753536</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7579,7 +7584,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122567074</v>
+        <v>122567067</v>
       </c>
       <c r="B69" t="n">
         <v>8441</v>
@@ -7624,10 +7629,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>441284</v>
+        <v>441231</v>
       </c>
       <c r="R69" t="n">
-        <v>6753286</v>
+        <v>6753537</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7686,10 +7691,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122567111</v>
+        <v>122567132</v>
       </c>
       <c r="B70" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7726,10 +7731,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>441221</v>
+        <v>441329</v>
       </c>
       <c r="R70" t="n">
-        <v>6753553</v>
+        <v>6753438</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7788,10 +7793,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122567104</v>
+        <v>122567127</v>
       </c>
       <c r="B71" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7828,10 +7833,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>441277</v>
+        <v>441338</v>
       </c>
       <c r="R71" t="n">
-        <v>6753396</v>
+        <v>6753386</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7890,10 +7895,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122567059</v>
+        <v>122567100</v>
       </c>
       <c r="B72" t="n">
-        <v>8441</v>
+        <v>78660</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -7902,43 +7907,38 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>441302</v>
+        <v>441332</v>
       </c>
       <c r="R72" t="n">
-        <v>6753294</v>
+        <v>6753382</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7997,10 +7997,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>122567127</v>
+        <v>122567101</v>
       </c>
       <c r="B73" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8037,10 +8037,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>441338</v>
+        <v>441301</v>
       </c>
       <c r="R73" t="n">
-        <v>6753386</v>
+        <v>6753376</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8099,10 +8099,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>122567116</v>
+        <v>122567158</v>
       </c>
       <c r="B74" t="n">
-        <v>78657</v>
+        <v>78305</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8115,21 +8115,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8139,10 +8139,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>441199</v>
+        <v>441248</v>
       </c>
       <c r="R74" t="n">
-        <v>6753562</v>
+        <v>6753389</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8201,10 +8201,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>122567100</v>
+        <v>122567043</v>
       </c>
       <c r="B75" t="n">
-        <v>78657</v>
+        <v>79278</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8217,21 +8217,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8241,10 +8241,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>441332</v>
+        <v>441348</v>
       </c>
       <c r="R75" t="n">
-        <v>6753382</v>
+        <v>6753422</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8303,10 +8303,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>122567114</v>
+        <v>122567048</v>
       </c>
       <c r="B76" t="n">
-        <v>78657</v>
+        <v>74761</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8319,21 +8319,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8343,10 +8343,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>441206</v>
+        <v>441302</v>
       </c>
       <c r="R76" t="n">
-        <v>6753562</v>
+        <v>6753380</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8405,10 +8405,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>122567097</v>
+        <v>122567047</v>
       </c>
       <c r="B77" t="n">
-        <v>78657</v>
+        <v>74761</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8421,21 +8421,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8445,10 +8445,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>441320</v>
+        <v>441304</v>
       </c>
       <c r="R77" t="n">
-        <v>6753429</v>
+        <v>6753377</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8507,10 +8507,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>122567113</v>
+        <v>122567053</v>
       </c>
       <c r="B78" t="n">
-        <v>78657</v>
+        <v>78694</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8523,21 +8523,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8547,10 +8547,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>441207</v>
+        <v>441420</v>
       </c>
       <c r="R78" t="n">
-        <v>6753568</v>
+        <v>6753456</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>

--- a/artfynd/A 61943-2024 artfynd.xlsx
+++ b/artfynd/A 61943-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122567070</v>
+        <v>122567106</v>
       </c>
       <c r="B2" t="n">
-        <v>8441</v>
+        <v>78660</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,43 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>441158</v>
+        <v>441266</v>
       </c>
       <c r="R2" t="n">
-        <v>6753533</v>
+        <v>6753401</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122567095</v>
+        <v>122567100</v>
       </c>
       <c r="B3" t="n">
         <v>78660</v>
@@ -822,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>441406</v>
+        <v>441332</v>
       </c>
       <c r="R3" t="n">
-        <v>6753439</v>
+        <v>6753382</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122567117</v>
+        <v>122567047</v>
       </c>
       <c r="B4" t="n">
-        <v>78660</v>
+        <v>74761</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>441193</v>
+        <v>441304</v>
       </c>
       <c r="R4" t="n">
-        <v>6753577</v>
+        <v>6753377</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122567138</v>
+        <v>122567067</v>
       </c>
       <c r="B5" t="n">
-        <v>78660</v>
+        <v>8441</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -998,38 +993,43 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>441383</v>
+        <v>441231</v>
       </c>
       <c r="R5" t="n">
-        <v>6753450</v>
+        <v>6753537</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122567122</v>
+        <v>122567066</v>
       </c>
       <c r="B6" t="n">
-        <v>78660</v>
+        <v>8441</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1100,38 +1100,43 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>441315</v>
+        <v>441258</v>
       </c>
       <c r="R6" t="n">
-        <v>6753342</v>
+        <v>6753406</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1190,10 +1195,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122567064</v>
+        <v>122567103</v>
       </c>
       <c r="B7" t="n">
-        <v>8441</v>
+        <v>78660</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1202,43 +1207,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>441389</v>
+        <v>441287</v>
       </c>
       <c r="R7" t="n">
-        <v>6753439</v>
+        <v>6753389</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1297,10 +1297,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122567068</v>
+        <v>122567051</v>
       </c>
       <c r="B8" t="n">
-        <v>8441</v>
+        <v>74761</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1309,43 +1309,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106545</v>
+        <v>6440</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>441150</v>
+        <v>441352</v>
       </c>
       <c r="R8" t="n">
-        <v>6753623</v>
+        <v>6753455</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1404,7 +1399,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122567106</v>
+        <v>122567099</v>
       </c>
       <c r="B9" t="n">
         <v>78660</v>
@@ -1444,10 +1439,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>441266</v>
+        <v>441323</v>
       </c>
       <c r="R9" t="n">
-        <v>6753401</v>
+        <v>6753416</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1506,10 +1501,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122567134</v>
+        <v>122567088</v>
       </c>
       <c r="B10" t="n">
-        <v>78660</v>
+        <v>56594</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1518,38 +1513,43 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>441320</v>
+        <v>441262</v>
       </c>
       <c r="R10" t="n">
-        <v>6753453</v>
+        <v>6753412</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1608,7 +1608,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122567113</v>
+        <v>122567112</v>
       </c>
       <c r="B11" t="n">
         <v>78660</v>
@@ -1648,10 +1648,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>441207</v>
+        <v>441217</v>
       </c>
       <c r="R11" t="n">
-        <v>6753568</v>
+        <v>6753556</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1710,10 +1710,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122567131</v>
+        <v>122567050</v>
       </c>
       <c r="B12" t="n">
-        <v>78660</v>
+        <v>74761</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1726,21 +1726,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1750,10 +1750,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>441347</v>
+        <v>441314</v>
       </c>
       <c r="R12" t="n">
-        <v>6753407</v>
+        <v>6753342</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1812,7 +1812,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122567135</v>
+        <v>122567104</v>
       </c>
       <c r="B13" t="n">
         <v>78660</v>
@@ -1852,10 +1852,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>441322</v>
+        <v>441277</v>
       </c>
       <c r="R13" t="n">
-        <v>6753459</v>
+        <v>6753396</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1914,10 +1914,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122567039</v>
+        <v>122567101</v>
       </c>
       <c r="B14" t="n">
-        <v>79278</v>
+        <v>78660</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1930,21 +1930,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1954,10 +1954,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>441344</v>
+        <v>441301</v>
       </c>
       <c r="R14" t="n">
-        <v>6753341</v>
+        <v>6753376</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2016,7 +2016,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122567073</v>
+        <v>122567059</v>
       </c>
       <c r="B15" t="n">
         <v>8441</v>
@@ -2052,7 +2052,7 @@
       <c r="I15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2061,10 +2061,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>441269</v>
+        <v>441302</v>
       </c>
       <c r="R15" t="n">
-        <v>6753365</v>
+        <v>6753294</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2123,10 +2123,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122567050</v>
+        <v>122567070</v>
       </c>
       <c r="B16" t="n">
-        <v>74761</v>
+        <v>8441</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2135,38 +2135,43 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6440</v>
+        <v>106545</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>441314</v>
+        <v>441158</v>
       </c>
       <c r="R16" t="n">
-        <v>6753342</v>
+        <v>6753533</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2225,10 +2230,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122567081</v>
+        <v>122567038</v>
       </c>
       <c r="B17" t="n">
-        <v>78397</v>
+        <v>79278</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2241,21 +2246,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2265,10 +2270,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>441344</v>
+        <v>441336</v>
       </c>
       <c r="R17" t="n">
-        <v>6753341</v>
+        <v>6753344</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2327,7 +2332,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122567102</v>
+        <v>122567096</v>
       </c>
       <c r="B18" t="n">
         <v>78660</v>
@@ -2367,10 +2372,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>441305</v>
+        <v>441319</v>
       </c>
       <c r="R18" t="n">
-        <v>6753384</v>
+        <v>6753442</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2429,10 +2434,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122567035</v>
+        <v>122567097</v>
       </c>
       <c r="B19" t="n">
-        <v>79278</v>
+        <v>78660</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2445,21 +2450,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2469,10 +2474,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>441158</v>
+        <v>441320</v>
       </c>
       <c r="R19" t="n">
-        <v>6753553</v>
+        <v>6753429</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2531,10 +2536,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122567077</v>
+        <v>122567122</v>
       </c>
       <c r="B20" t="n">
-        <v>8441</v>
+        <v>78660</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2543,43 +2548,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>441381</v>
+        <v>441315</v>
       </c>
       <c r="R20" t="n">
-        <v>6753451</v>
+        <v>6753342</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2638,10 +2638,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122567112</v>
+        <v>122567073</v>
       </c>
       <c r="B21" t="n">
-        <v>78660</v>
+        <v>8441</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2650,38 +2650,43 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>441217</v>
+        <v>441269</v>
       </c>
       <c r="R21" t="n">
-        <v>6753556</v>
+        <v>6753365</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2740,7 +2745,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122567136</v>
+        <v>122567119</v>
       </c>
       <c r="B22" t="n">
         <v>78660</v>
@@ -2780,10 +2785,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>441345</v>
+        <v>441291</v>
       </c>
       <c r="R22" t="n">
-        <v>6753451</v>
+        <v>6753289</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2842,7 +2847,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122567103</v>
+        <v>122567136</v>
       </c>
       <c r="B23" t="n">
         <v>78660</v>
@@ -2882,10 +2887,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>441287</v>
+        <v>441345</v>
       </c>
       <c r="R23" t="n">
-        <v>6753389</v>
+        <v>6753451</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2944,10 +2949,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122567051</v>
+        <v>122567109</v>
       </c>
       <c r="B24" t="n">
-        <v>74761</v>
+        <v>78660</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2960,21 +2965,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2984,10 +2989,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>441352</v>
+        <v>441223</v>
       </c>
       <c r="R24" t="n">
-        <v>6753455</v>
+        <v>6753536</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3046,7 +3051,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122567121</v>
+        <v>122567095</v>
       </c>
       <c r="B25" t="n">
         <v>78660</v>
@@ -3086,10 +3091,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>441306</v>
+        <v>441406</v>
       </c>
       <c r="R25" t="n">
-        <v>6753338</v>
+        <v>6753439</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3148,7 +3153,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122567042</v>
+        <v>122567043</v>
       </c>
       <c r="B26" t="n">
         <v>79278</v>
@@ -3188,10 +3193,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>441336</v>
+        <v>441348</v>
       </c>
       <c r="R26" t="n">
-        <v>6753370</v>
+        <v>6753422</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3250,10 +3255,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122567036</v>
+        <v>122567158</v>
       </c>
       <c r="B27" t="n">
-        <v>79278</v>
+        <v>78305</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3266,21 +3271,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3290,10 +3295,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>441283</v>
+        <v>441248</v>
       </c>
       <c r="R27" t="n">
-        <v>6753350</v>
+        <v>6753389</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3352,10 +3357,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122567033</v>
+        <v>122567056</v>
       </c>
       <c r="B28" t="n">
-        <v>79278</v>
+        <v>57400</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3368,34 +3373,39 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>441194</v>
+        <v>441305</v>
       </c>
       <c r="R28" t="n">
-        <v>6753576</v>
+        <v>6753366</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3454,10 +3464,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122567089</v>
+        <v>122567074</v>
       </c>
       <c r="B29" t="n">
-        <v>56594</v>
+        <v>8441</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3470,27 +3480,27 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100138</v>
+        <v>106545</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3499,10 +3509,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>441283</v>
+        <v>441284</v>
       </c>
       <c r="R29" t="n">
-        <v>6753349</v>
+        <v>6753286</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3561,10 +3571,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122567088</v>
+        <v>122567132</v>
       </c>
       <c r="B30" t="n">
-        <v>56594</v>
+        <v>78660</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3573,43 +3583,38 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>441262</v>
+        <v>441329</v>
       </c>
       <c r="R30" t="n">
-        <v>6753412</v>
+        <v>6753438</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3668,10 +3673,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122567139</v>
+        <v>122567044</v>
       </c>
       <c r="B31" t="n">
-        <v>78660</v>
+        <v>79278</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3684,21 +3689,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3708,7 +3713,7 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>441430</v>
+        <v>441348</v>
       </c>
       <c r="R31" t="n">
         <v>6753445</v>
@@ -3770,10 +3775,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122567066</v>
+        <v>122567128</v>
       </c>
       <c r="B32" t="n">
-        <v>8441</v>
+        <v>78660</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3782,43 +3787,38 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>441258</v>
+        <v>441350</v>
       </c>
       <c r="R32" t="n">
-        <v>6753406</v>
+        <v>6753388</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3877,10 +3877,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122567041</v>
+        <v>122567123</v>
       </c>
       <c r="B33" t="n">
-        <v>79278</v>
+        <v>78660</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3893,21 +3893,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3917,10 +3917,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>441357</v>
+        <v>441334</v>
       </c>
       <c r="R33" t="n">
-        <v>6753361</v>
+        <v>6753341</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3979,10 +3979,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122567038</v>
+        <v>122567138</v>
       </c>
       <c r="B34" t="n">
-        <v>79278</v>
+        <v>78660</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3995,21 +3995,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4019,10 +4019,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>441336</v>
+        <v>441383</v>
       </c>
       <c r="R34" t="n">
-        <v>6753344</v>
+        <v>6753450</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4081,10 +4081,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122567116</v>
+        <v>122567077</v>
       </c>
       <c r="B35" t="n">
-        <v>78660</v>
+        <v>8441</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4093,38 +4093,43 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>441199</v>
+        <v>441381</v>
       </c>
       <c r="R35" t="n">
-        <v>6753562</v>
+        <v>6753451</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4183,10 +4188,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122567108</v>
+        <v>122567042</v>
       </c>
       <c r="B36" t="n">
-        <v>78660</v>
+        <v>79278</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4199,21 +4204,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4223,10 +4228,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>441273</v>
+        <v>441336</v>
       </c>
       <c r="R36" t="n">
-        <v>6753425</v>
+        <v>6753370</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4285,10 +4290,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122567137</v>
+        <v>122567072</v>
       </c>
       <c r="B37" t="n">
-        <v>78660</v>
+        <v>8441</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4297,38 +4302,43 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>441348</v>
+        <v>441255</v>
       </c>
       <c r="R37" t="n">
-        <v>6753444</v>
+        <v>6753382</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4387,10 +4397,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122567072</v>
+        <v>122567118</v>
       </c>
       <c r="B38" t="n">
-        <v>8441</v>
+        <v>78660</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4399,43 +4409,38 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>441255</v>
+        <v>441277</v>
       </c>
       <c r="R38" t="n">
-        <v>6753382</v>
+        <v>6753324</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4494,7 +4499,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122567126</v>
+        <v>122567108</v>
       </c>
       <c r="B39" t="n">
         <v>78660</v>
@@ -4534,10 +4539,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>441344</v>
+        <v>441273</v>
       </c>
       <c r="R39" t="n">
-        <v>6753362</v>
+        <v>6753425</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4596,7 +4601,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122567120</v>
+        <v>122567139</v>
       </c>
       <c r="B40" t="n">
         <v>78660</v>
@@ -4636,10 +4641,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>441289</v>
+        <v>441430</v>
       </c>
       <c r="R40" t="n">
-        <v>6753324</v>
+        <v>6753445</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4698,10 +4703,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122567044</v>
+        <v>122567049</v>
       </c>
       <c r="B41" t="n">
-        <v>79278</v>
+        <v>74761</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4714,21 +4719,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6453</v>
+        <v>6440</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4738,10 +4743,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>441348</v>
+        <v>441299</v>
       </c>
       <c r="R41" t="n">
-        <v>6753445</v>
+        <v>6753387</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4800,7 +4805,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122567091</v>
+        <v>122567111</v>
       </c>
       <c r="B42" t="n">
         <v>78660</v>
@@ -4840,10 +4845,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>441420</v>
+        <v>441221</v>
       </c>
       <c r="R42" t="n">
-        <v>6753456</v>
+        <v>6753553</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4902,10 +4907,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122567049</v>
+        <v>122567075</v>
       </c>
       <c r="B43" t="n">
-        <v>74761</v>
+        <v>8441</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4914,38 +4919,43 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6440</v>
+        <v>106545</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>441299</v>
+        <v>441291</v>
       </c>
       <c r="R43" t="n">
-        <v>6753387</v>
+        <v>6753289</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5004,10 +5014,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122567105</v>
+        <v>122567069</v>
       </c>
       <c r="B44" t="n">
-        <v>78660</v>
+        <v>8441</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5016,38 +5026,43 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>441269</v>
+        <v>441119</v>
       </c>
       <c r="R44" t="n">
-        <v>6753398</v>
+        <v>6753677</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5106,10 +5121,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122567074</v>
+        <v>122567137</v>
       </c>
       <c r="B45" t="n">
-        <v>8441</v>
+        <v>78660</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5118,43 +5133,38 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>441284</v>
+        <v>441348</v>
       </c>
       <c r="R45" t="n">
-        <v>6753286</v>
+        <v>6753444</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5213,10 +5223,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122567069</v>
+        <v>122567135</v>
       </c>
       <c r="B46" t="n">
-        <v>8441</v>
+        <v>78660</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5225,43 +5235,38 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>441119</v>
+        <v>441322</v>
       </c>
       <c r="R46" t="n">
-        <v>6753677</v>
+        <v>6753459</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5320,10 +5325,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122567097</v>
+        <v>122567033</v>
       </c>
       <c r="B47" t="n">
-        <v>78660</v>
+        <v>79278</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5336,21 +5341,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5360,10 +5365,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>441320</v>
+        <v>441194</v>
       </c>
       <c r="R47" t="n">
-        <v>6753429</v>
+        <v>6753576</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5422,7 +5427,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122567119</v>
+        <v>122567091</v>
       </c>
       <c r="B48" t="n">
         <v>78660</v>
@@ -5462,10 +5467,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>441291</v>
+        <v>441420</v>
       </c>
       <c r="R48" t="n">
-        <v>6753289</v>
+        <v>6753456</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5524,7 +5529,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122567096</v>
+        <v>122567121</v>
       </c>
       <c r="B49" t="n">
         <v>78660</v>
@@ -5564,10 +5569,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>441319</v>
+        <v>441306</v>
       </c>
       <c r="R49" t="n">
-        <v>6753442</v>
+        <v>6753338</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5626,10 +5631,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122567034</v>
+        <v>122567125</v>
       </c>
       <c r="B50" t="n">
-        <v>79278</v>
+        <v>78660</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5642,21 +5647,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5666,10 +5671,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>441152</v>
+        <v>441356</v>
       </c>
       <c r="R50" t="n">
-        <v>6753562</v>
+        <v>6753361</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5728,7 +5733,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122567128</v>
+        <v>122567116</v>
       </c>
       <c r="B51" t="n">
         <v>78660</v>
@@ -5768,10 +5773,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>441350</v>
+        <v>441199</v>
       </c>
       <c r="R51" t="n">
-        <v>6753388</v>
+        <v>6753562</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5830,7 +5835,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122567111</v>
+        <v>122567107</v>
       </c>
       <c r="B52" t="n">
         <v>78660</v>
@@ -5870,10 +5875,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>441221</v>
+        <v>441262</v>
       </c>
       <c r="R52" t="n">
-        <v>6753553</v>
+        <v>6753417</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5932,7 +5937,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122567104</v>
+        <v>122567127</v>
       </c>
       <c r="B53" t="n">
         <v>78660</v>
@@ -5972,10 +5977,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>441277</v>
+        <v>441338</v>
       </c>
       <c r="R53" t="n">
-        <v>6753396</v>
+        <v>6753386</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6034,10 +6039,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122567046</v>
+        <v>122567120</v>
       </c>
       <c r="B54" t="n">
-        <v>74761</v>
+        <v>78660</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6050,21 +6055,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6074,10 +6079,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>441304</v>
+        <v>441289</v>
       </c>
       <c r="R54" t="n">
-        <v>6753366</v>
+        <v>6753324</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6136,10 +6141,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122567075</v>
+        <v>122567114</v>
       </c>
       <c r="B55" t="n">
-        <v>8441</v>
+        <v>78660</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6148,43 +6153,38 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>441291</v>
+        <v>441206</v>
       </c>
       <c r="R55" t="n">
-        <v>6753289</v>
+        <v>6753562</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6243,10 +6243,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122567059</v>
+        <v>122567046</v>
       </c>
       <c r="B56" t="n">
-        <v>8441</v>
+        <v>74761</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6255,43 +6255,38 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>106545</v>
+        <v>6440</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>441302</v>
+        <v>441304</v>
       </c>
       <c r="R56" t="n">
-        <v>6753294</v>
+        <v>6753366</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6350,10 +6345,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122567114</v>
+        <v>122567068</v>
       </c>
       <c r="B57" t="n">
-        <v>78660</v>
+        <v>8441</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6362,38 +6357,43 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>441206</v>
+        <v>441150</v>
       </c>
       <c r="R57" t="n">
-        <v>6753562</v>
+        <v>6753623</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6452,10 +6452,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122567083</v>
+        <v>122567126</v>
       </c>
       <c r="B58" t="n">
-        <v>78397</v>
+        <v>78660</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6468,21 +6468,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6492,10 +6492,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>441348</v>
+        <v>441344</v>
       </c>
       <c r="R58" t="n">
-        <v>6753422</v>
+        <v>6753362</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6554,10 +6554,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122567056</v>
+        <v>122567039</v>
       </c>
       <c r="B59" t="n">
-        <v>57400</v>
+        <v>79278</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6570,39 +6570,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>441305</v>
+        <v>441344</v>
       </c>
       <c r="R59" t="n">
-        <v>6753366</v>
+        <v>6753341</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6661,7 +6656,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122567118</v>
+        <v>122567098</v>
       </c>
       <c r="B60" t="n">
         <v>78660</v>
@@ -6701,10 +6696,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>441277</v>
+        <v>441329</v>
       </c>
       <c r="R60" t="n">
-        <v>6753324</v>
+        <v>6753411</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6763,10 +6758,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122567098</v>
+        <v>122567034</v>
       </c>
       <c r="B61" t="n">
-        <v>78660</v>
+        <v>79278</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6779,21 +6774,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6803,10 +6798,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>441329</v>
+        <v>441152</v>
       </c>
       <c r="R61" t="n">
-        <v>6753411</v>
+        <v>6753562</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6865,7 +6860,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122567133</v>
+        <v>122567113</v>
       </c>
       <c r="B62" t="n">
         <v>78660</v>
@@ -6905,10 +6900,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>441321</v>
+        <v>441207</v>
       </c>
       <c r="R62" t="n">
-        <v>6753447</v>
+        <v>6753568</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6967,7 +6962,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122567125</v>
+        <v>122567134</v>
       </c>
       <c r="B63" t="n">
         <v>78660</v>
@@ -7007,10 +7002,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>441356</v>
+        <v>441320</v>
       </c>
       <c r="R63" t="n">
-        <v>6753361</v>
+        <v>6753453</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7069,7 +7064,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122567107</v>
+        <v>122567131</v>
       </c>
       <c r="B64" t="n">
         <v>78660</v>
@@ -7109,10 +7104,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>441262</v>
+        <v>441347</v>
       </c>
       <c r="R64" t="n">
-        <v>6753417</v>
+        <v>6753407</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7171,7 +7166,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122567123</v>
+        <v>122567105</v>
       </c>
       <c r="B65" t="n">
         <v>78660</v>
@@ -7211,10 +7206,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>441334</v>
+        <v>441269</v>
       </c>
       <c r="R65" t="n">
-        <v>6753341</v>
+        <v>6753398</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7380,10 +7375,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122567099</v>
+        <v>122567053</v>
       </c>
       <c r="B67" t="n">
-        <v>78660</v>
+        <v>78694</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7396,21 +7391,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7420,10 +7415,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>441323</v>
+        <v>441420</v>
       </c>
       <c r="R67" t="n">
-        <v>6753416</v>
+        <v>6753456</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7482,10 +7477,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122567109</v>
+        <v>122567083</v>
       </c>
       <c r="B68" t="n">
-        <v>78660</v>
+        <v>78397</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7498,21 +7493,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7522,10 +7517,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>441223</v>
+        <v>441348</v>
       </c>
       <c r="R68" t="n">
-        <v>6753536</v>
+        <v>6753422</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7584,10 +7579,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122567067</v>
+        <v>122567035</v>
       </c>
       <c r="B69" t="n">
-        <v>8441</v>
+        <v>79278</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7596,43 +7591,38 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>441231</v>
+        <v>441158</v>
       </c>
       <c r="R69" t="n">
-        <v>6753537</v>
+        <v>6753553</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7691,10 +7681,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122567132</v>
+        <v>122567089</v>
       </c>
       <c r="B70" t="n">
-        <v>78660</v>
+        <v>56594</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7703,38 +7693,43 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>441329</v>
+        <v>441283</v>
       </c>
       <c r="R70" t="n">
-        <v>6753438</v>
+        <v>6753349</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7793,7 +7788,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122567127</v>
+        <v>122567102</v>
       </c>
       <c r="B71" t="n">
         <v>78660</v>
@@ -7833,10 +7828,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>441338</v>
+        <v>441305</v>
       </c>
       <c r="R71" t="n">
-        <v>6753386</v>
+        <v>6753384</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7895,10 +7890,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122567100</v>
+        <v>122567081</v>
       </c>
       <c r="B72" t="n">
-        <v>78660</v>
+        <v>78397</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -7911,21 +7906,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7935,10 +7930,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>441332</v>
+        <v>441344</v>
       </c>
       <c r="R72" t="n">
-        <v>6753382</v>
+        <v>6753341</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7997,10 +7992,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>122567101</v>
+        <v>122567064</v>
       </c>
       <c r="B73" t="n">
-        <v>78660</v>
+        <v>8441</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8009,38 +8004,43 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>441301</v>
+        <v>441389</v>
       </c>
       <c r="R73" t="n">
-        <v>6753376</v>
+        <v>6753439</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8099,10 +8099,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>122567158</v>
+        <v>122567133</v>
       </c>
       <c r="B74" t="n">
-        <v>78305</v>
+        <v>78660</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8115,21 +8115,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8139,10 +8139,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>441248</v>
+        <v>441321</v>
       </c>
       <c r="R74" t="n">
-        <v>6753389</v>
+        <v>6753447</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8201,7 +8201,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>122567043</v>
+        <v>122567036</v>
       </c>
       <c r="B75" t="n">
         <v>79278</v>
@@ -8241,10 +8241,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>441348</v>
+        <v>441283</v>
       </c>
       <c r="R75" t="n">
-        <v>6753422</v>
+        <v>6753350</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8405,10 +8405,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>122567047</v>
+        <v>122567041</v>
       </c>
       <c r="B77" t="n">
-        <v>74761</v>
+        <v>79278</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8421,21 +8421,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6440</v>
+        <v>6453</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8445,10 +8445,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>441304</v>
+        <v>441357</v>
       </c>
       <c r="R77" t="n">
-        <v>6753377</v>
+        <v>6753361</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8507,10 +8507,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>122567053</v>
+        <v>122567117</v>
       </c>
       <c r="B78" t="n">
-        <v>78694</v>
+        <v>78660</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8523,21 +8523,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8547,10 +8547,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>441420</v>
+        <v>441193</v>
       </c>
       <c r="R78" t="n">
-        <v>6753456</v>
+        <v>6753577</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>

--- a/artfynd/A 61943-2024 artfynd.xlsx
+++ b/artfynd/A 61943-2024 artfynd.xlsx
@@ -5733,10 +5733,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122567116</v>
+        <v>122567068</v>
       </c>
       <c r="B51" t="n">
-        <v>78660</v>
+        <v>8441</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5745,38 +5745,43 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>441199</v>
+        <v>441150</v>
       </c>
       <c r="R51" t="n">
-        <v>6753562</v>
+        <v>6753623</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5835,7 +5840,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122567107</v>
+        <v>122567116</v>
       </c>
       <c r="B52" t="n">
         <v>78660</v>
@@ -5875,10 +5880,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>441262</v>
+        <v>441199</v>
       </c>
       <c r="R52" t="n">
-        <v>6753417</v>
+        <v>6753562</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5937,7 +5942,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122567127</v>
+        <v>122567107</v>
       </c>
       <c r="B53" t="n">
         <v>78660</v>
@@ -5977,10 +5982,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>441338</v>
+        <v>441262</v>
       </c>
       <c r="R53" t="n">
-        <v>6753386</v>
+        <v>6753417</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6039,7 +6044,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122567120</v>
+        <v>122567127</v>
       </c>
       <c r="B54" t="n">
         <v>78660</v>
@@ -6079,10 +6084,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>441289</v>
+        <v>441338</v>
       </c>
       <c r="R54" t="n">
-        <v>6753324</v>
+        <v>6753386</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6141,7 +6146,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122567114</v>
+        <v>122567120</v>
       </c>
       <c r="B55" t="n">
         <v>78660</v>
@@ -6181,10 +6186,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>441206</v>
+        <v>441289</v>
       </c>
       <c r="R55" t="n">
-        <v>6753562</v>
+        <v>6753324</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6243,10 +6248,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122567046</v>
+        <v>122567114</v>
       </c>
       <c r="B56" t="n">
-        <v>74761</v>
+        <v>78660</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6259,21 +6264,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6283,10 +6288,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>441304</v>
+        <v>441206</v>
       </c>
       <c r="R56" t="n">
-        <v>6753366</v>
+        <v>6753562</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6345,10 +6350,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122567068</v>
+        <v>122567046</v>
       </c>
       <c r="B57" t="n">
-        <v>8441</v>
+        <v>74761</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6357,43 +6362,38 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>106545</v>
+        <v>6440</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>441150</v>
+        <v>441304</v>
       </c>
       <c r="R57" t="n">
-        <v>6753623</v>
+        <v>6753366</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7375,10 +7375,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122567053</v>
+        <v>122567035</v>
       </c>
       <c r="B67" t="n">
-        <v>78694</v>
+        <v>79278</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7391,21 +7391,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7415,10 +7415,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>441420</v>
+        <v>441158</v>
       </c>
       <c r="R67" t="n">
-        <v>6753456</v>
+        <v>6753553</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7477,10 +7477,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122567083</v>
+        <v>122567053</v>
       </c>
       <c r="B68" t="n">
-        <v>78397</v>
+        <v>78694</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7493,21 +7493,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>228912</v>
+        <v>185</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7517,10 +7517,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>441348</v>
+        <v>441420</v>
       </c>
       <c r="R68" t="n">
-        <v>6753422</v>
+        <v>6753456</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7579,10 +7579,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122567035</v>
+        <v>122567089</v>
       </c>
       <c r="B69" t="n">
-        <v>79278</v>
+        <v>56594</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7591,38 +7591,43 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>441158</v>
+        <v>441283</v>
       </c>
       <c r="R69" t="n">
-        <v>6753553</v>
+        <v>6753349</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7681,10 +7686,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122567089</v>
+        <v>122567083</v>
       </c>
       <c r="B70" t="n">
-        <v>56594</v>
+        <v>78397</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7693,43 +7698,38 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>441283</v>
+        <v>441348</v>
       </c>
       <c r="R70" t="n">
-        <v>6753349</v>
+        <v>6753422</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7890,10 +7890,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122567081</v>
+        <v>122567133</v>
       </c>
       <c r="B72" t="n">
-        <v>78397</v>
+        <v>78660</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -7906,21 +7906,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7930,10 +7930,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>441344</v>
+        <v>441321</v>
       </c>
       <c r="R72" t="n">
-        <v>6753341</v>
+        <v>6753447</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7992,10 +7992,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>122567064</v>
+        <v>122567036</v>
       </c>
       <c r="B73" t="n">
-        <v>8441</v>
+        <v>79278</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8004,43 +8004,38 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>441389</v>
+        <v>441283</v>
       </c>
       <c r="R73" t="n">
-        <v>6753439</v>
+        <v>6753350</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8099,10 +8094,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>122567133</v>
+        <v>122567081</v>
       </c>
       <c r="B74" t="n">
-        <v>78660</v>
+        <v>78397</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8115,21 +8110,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8139,10 +8134,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>441321</v>
+        <v>441344</v>
       </c>
       <c r="R74" t="n">
-        <v>6753447</v>
+        <v>6753341</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8201,10 +8196,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>122567036</v>
+        <v>122567048</v>
       </c>
       <c r="B75" t="n">
-        <v>79278</v>
+        <v>74761</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8217,21 +8212,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6453</v>
+        <v>6440</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8241,10 +8236,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>441283</v>
+        <v>441302</v>
       </c>
       <c r="R75" t="n">
-        <v>6753350</v>
+        <v>6753380</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8303,10 +8298,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>122567048</v>
+        <v>122567064</v>
       </c>
       <c r="B76" t="n">
-        <v>74761</v>
+        <v>8441</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8315,38 +8310,43 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6440</v>
+        <v>106545</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>441302</v>
+        <v>441389</v>
       </c>
       <c r="R76" t="n">
-        <v>6753380</v>
+        <v>6753439</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>

--- a/artfynd/A 61943-2024 artfynd.xlsx
+++ b/artfynd/A 61943-2024 artfynd.xlsx
@@ -2434,10 +2434,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122567097</v>
+        <v>122567073</v>
       </c>
       <c r="B19" t="n">
-        <v>78660</v>
+        <v>8441</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2446,38 +2446,43 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>441320</v>
+        <v>441269</v>
       </c>
       <c r="R19" t="n">
-        <v>6753429</v>
+        <v>6753365</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2536,7 +2541,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122567122</v>
+        <v>122567119</v>
       </c>
       <c r="B20" t="n">
         <v>78660</v>
@@ -2576,10 +2581,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>441315</v>
+        <v>441291</v>
       </c>
       <c r="R20" t="n">
-        <v>6753342</v>
+        <v>6753289</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2638,10 +2643,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122567073</v>
+        <v>122567136</v>
       </c>
       <c r="B21" t="n">
-        <v>8441</v>
+        <v>78660</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2650,43 +2655,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>441269</v>
+        <v>441345</v>
       </c>
       <c r="R21" t="n">
-        <v>6753365</v>
+        <v>6753451</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2745,7 +2745,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122567119</v>
+        <v>122567109</v>
       </c>
       <c r="B22" t="n">
         <v>78660</v>
@@ -2785,10 +2785,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>441291</v>
+        <v>441223</v>
       </c>
       <c r="R22" t="n">
-        <v>6753289</v>
+        <v>6753536</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2847,7 +2847,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122567136</v>
+        <v>122567097</v>
       </c>
       <c r="B23" t="n">
         <v>78660</v>
@@ -2887,10 +2887,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>441345</v>
+        <v>441320</v>
       </c>
       <c r="R23" t="n">
-        <v>6753451</v>
+        <v>6753429</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2949,7 +2949,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122567109</v>
+        <v>122567122</v>
       </c>
       <c r="B24" t="n">
         <v>78660</v>
@@ -2989,10 +2989,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>441223</v>
+        <v>441315</v>
       </c>
       <c r="R24" t="n">
-        <v>6753536</v>
+        <v>6753342</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -4397,10 +4397,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122567118</v>
+        <v>122567049</v>
       </c>
       <c r="B38" t="n">
-        <v>78660</v>
+        <v>74761</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4413,21 +4413,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4437,10 +4437,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>441277</v>
+        <v>441299</v>
       </c>
       <c r="R38" t="n">
-        <v>6753324</v>
+        <v>6753387</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4499,7 +4499,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122567108</v>
+        <v>122567111</v>
       </c>
       <c r="B39" t="n">
         <v>78660</v>
@@ -4539,10 +4539,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>441273</v>
+        <v>441221</v>
       </c>
       <c r="R39" t="n">
-        <v>6753425</v>
+        <v>6753553</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4601,7 +4601,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122567139</v>
+        <v>122567118</v>
       </c>
       <c r="B40" t="n">
         <v>78660</v>
@@ -4641,10 +4641,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>441430</v>
+        <v>441277</v>
       </c>
       <c r="R40" t="n">
-        <v>6753445</v>
+        <v>6753324</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4703,10 +4703,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122567049</v>
+        <v>122567139</v>
       </c>
       <c r="B41" t="n">
-        <v>74761</v>
+        <v>78660</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4719,21 +4719,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4743,10 +4743,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>441299</v>
+        <v>441430</v>
       </c>
       <c r="R41" t="n">
-        <v>6753387</v>
+        <v>6753445</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4805,10 +4805,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122567111</v>
+        <v>122567075</v>
       </c>
       <c r="B42" t="n">
-        <v>78660</v>
+        <v>8441</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4817,38 +4817,43 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>441221</v>
+        <v>441291</v>
       </c>
       <c r="R42" t="n">
-        <v>6753553</v>
+        <v>6753289</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4907,7 +4912,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122567075</v>
+        <v>122567069</v>
       </c>
       <c r="B43" t="n">
         <v>8441</v>
@@ -4952,10 +4957,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>441291</v>
+        <v>441119</v>
       </c>
       <c r="R43" t="n">
-        <v>6753289</v>
+        <v>6753677</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5014,10 +5019,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122567069</v>
+        <v>122567108</v>
       </c>
       <c r="B44" t="n">
-        <v>8441</v>
+        <v>78660</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5026,43 +5031,38 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>441119</v>
+        <v>441273</v>
       </c>
       <c r="R44" t="n">
-        <v>6753677</v>
+        <v>6753425</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5733,10 +5733,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122567068</v>
+        <v>122567116</v>
       </c>
       <c r="B51" t="n">
-        <v>8441</v>
+        <v>78660</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5745,43 +5745,38 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>441150</v>
+        <v>441199</v>
       </c>
       <c r="R51" t="n">
-        <v>6753623</v>
+        <v>6753562</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5840,7 +5835,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122567116</v>
+        <v>122567107</v>
       </c>
       <c r="B52" t="n">
         <v>78660</v>
@@ -5880,10 +5875,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>441199</v>
+        <v>441262</v>
       </c>
       <c r="R52" t="n">
-        <v>6753562</v>
+        <v>6753417</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5942,7 +5937,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122567107</v>
+        <v>122567127</v>
       </c>
       <c r="B53" t="n">
         <v>78660</v>
@@ -5982,10 +5977,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>441262</v>
+        <v>441338</v>
       </c>
       <c r="R53" t="n">
-        <v>6753417</v>
+        <v>6753386</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6044,7 +6039,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122567127</v>
+        <v>122567120</v>
       </c>
       <c r="B54" t="n">
         <v>78660</v>
@@ -6084,10 +6079,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>441338</v>
+        <v>441289</v>
       </c>
       <c r="R54" t="n">
-        <v>6753386</v>
+        <v>6753324</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6146,7 +6141,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122567120</v>
+        <v>122567114</v>
       </c>
       <c r="B55" t="n">
         <v>78660</v>
@@ -6186,10 +6181,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>441289</v>
+        <v>441206</v>
       </c>
       <c r="R55" t="n">
-        <v>6753324</v>
+        <v>6753562</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6248,10 +6243,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122567114</v>
+        <v>122567046</v>
       </c>
       <c r="B56" t="n">
-        <v>78660</v>
+        <v>74761</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6264,21 +6259,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6288,10 +6283,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>441206</v>
+        <v>441304</v>
       </c>
       <c r="R56" t="n">
-        <v>6753562</v>
+        <v>6753366</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6350,10 +6345,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122567046</v>
+        <v>122567068</v>
       </c>
       <c r="B57" t="n">
-        <v>74761</v>
+        <v>8441</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6362,38 +6357,43 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6440</v>
+        <v>106545</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>441304</v>
+        <v>441150</v>
       </c>
       <c r="R57" t="n">
-        <v>6753366</v>
+        <v>6753623</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>

--- a/artfynd/A 61943-2024 artfynd.xlsx
+++ b/artfynd/A 61943-2024 artfynd.xlsx
@@ -1195,10 +1195,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122567103</v>
+        <v>122567088</v>
       </c>
       <c r="B7" t="n">
-        <v>78660</v>
+        <v>56594</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1207,38 +1207,43 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>441287</v>
+        <v>441262</v>
       </c>
       <c r="R7" t="n">
-        <v>6753389</v>
+        <v>6753412</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1297,10 +1302,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122567051</v>
+        <v>122567103</v>
       </c>
       <c r="B8" t="n">
-        <v>74761</v>
+        <v>78660</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1313,21 +1318,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1337,10 +1342,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>441352</v>
+        <v>441287</v>
       </c>
       <c r="R8" t="n">
-        <v>6753455</v>
+        <v>6753389</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1399,10 +1404,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122567099</v>
+        <v>122567051</v>
       </c>
       <c r="B9" t="n">
-        <v>78660</v>
+        <v>74761</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1415,21 +1420,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1439,10 +1444,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>441323</v>
+        <v>441352</v>
       </c>
       <c r="R9" t="n">
-        <v>6753416</v>
+        <v>6753455</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1501,10 +1506,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122567088</v>
+        <v>122567099</v>
       </c>
       <c r="B10" t="n">
-        <v>56594</v>
+        <v>78660</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1513,43 +1518,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>441262</v>
+        <v>441323</v>
       </c>
       <c r="R10" t="n">
-        <v>6753412</v>
+        <v>6753416</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -3877,10 +3877,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122567123</v>
+        <v>122567077</v>
       </c>
       <c r="B33" t="n">
-        <v>78660</v>
+        <v>8441</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3889,38 +3889,43 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>441334</v>
+        <v>441381</v>
       </c>
       <c r="R33" t="n">
-        <v>6753341</v>
+        <v>6753451</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3979,7 +3984,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122567138</v>
+        <v>122567123</v>
       </c>
       <c r="B34" t="n">
         <v>78660</v>
@@ -4019,10 +4024,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>441383</v>
+        <v>441334</v>
       </c>
       <c r="R34" t="n">
-        <v>6753450</v>
+        <v>6753341</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4081,10 +4086,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122567077</v>
+        <v>122567138</v>
       </c>
       <c r="B35" t="n">
-        <v>8441</v>
+        <v>78660</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4093,43 +4098,38 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>441381</v>
+        <v>441383</v>
       </c>
       <c r="R35" t="n">
-        <v>6753451</v>
+        <v>6753450</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -6860,7 +6860,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122567113</v>
+        <v>122567134</v>
       </c>
       <c r="B62" t="n">
         <v>78660</v>
@@ -6900,10 +6900,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>441207</v>
+        <v>441320</v>
       </c>
       <c r="R62" t="n">
-        <v>6753568</v>
+        <v>6753453</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6962,7 +6962,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122567134</v>
+        <v>122567131</v>
       </c>
       <c r="B63" t="n">
         <v>78660</v>
@@ -7002,10 +7002,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>441320</v>
+        <v>441347</v>
       </c>
       <c r="R63" t="n">
-        <v>6753453</v>
+        <v>6753407</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7064,7 +7064,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122567131</v>
+        <v>122567105</v>
       </c>
       <c r="B64" t="n">
         <v>78660</v>
@@ -7104,10 +7104,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>441347</v>
+        <v>441269</v>
       </c>
       <c r="R64" t="n">
-        <v>6753407</v>
+        <v>6753398</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7166,10 +7166,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122567105</v>
+        <v>122567071</v>
       </c>
       <c r="B65" t="n">
-        <v>78660</v>
+        <v>8441</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7178,38 +7178,43 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>441269</v>
+        <v>441172</v>
       </c>
       <c r="R65" t="n">
-        <v>6753398</v>
+        <v>6753515</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7268,10 +7273,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122567071</v>
+        <v>122567113</v>
       </c>
       <c r="B66" t="n">
-        <v>8441</v>
+        <v>78660</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7280,43 +7285,38 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>441172</v>
+        <v>441207</v>
       </c>
       <c r="R66" t="n">
-        <v>6753515</v>
+        <v>6753568</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7375,10 +7375,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122567035</v>
+        <v>122567089</v>
       </c>
       <c r="B67" t="n">
-        <v>79278</v>
+        <v>56594</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7387,38 +7387,43 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>441158</v>
+        <v>441283</v>
       </c>
       <c r="R67" t="n">
-        <v>6753553</v>
+        <v>6753349</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7477,10 +7482,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122567053</v>
+        <v>122567083</v>
       </c>
       <c r="B68" t="n">
-        <v>78694</v>
+        <v>78397</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7493,21 +7498,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>185</v>
+        <v>228912</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7517,10 +7522,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>441420</v>
+        <v>441348</v>
       </c>
       <c r="R68" t="n">
-        <v>6753456</v>
+        <v>6753422</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7579,10 +7584,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122567089</v>
+        <v>122567035</v>
       </c>
       <c r="B69" t="n">
-        <v>56594</v>
+        <v>79278</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7591,43 +7596,38 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>441283</v>
+        <v>441158</v>
       </c>
       <c r="R69" t="n">
-        <v>6753349</v>
+        <v>6753553</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7686,10 +7686,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122567083</v>
+        <v>122567053</v>
       </c>
       <c r="B70" t="n">
-        <v>78397</v>
+        <v>78694</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7702,21 +7702,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>228912</v>
+        <v>185</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7726,10 +7726,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>441348</v>
+        <v>441420</v>
       </c>
       <c r="R70" t="n">
-        <v>6753422</v>
+        <v>6753456</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>

--- a/artfynd/A 61943-2024 artfynd.xlsx
+++ b/artfynd/A 61943-2024 artfynd.xlsx
@@ -2434,10 +2434,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122567073</v>
+        <v>122567097</v>
       </c>
       <c r="B19" t="n">
-        <v>8441</v>
+        <v>78660</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2446,43 +2446,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>441269</v>
+        <v>441320</v>
       </c>
       <c r="R19" t="n">
-        <v>6753365</v>
+        <v>6753429</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2541,7 +2536,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122567119</v>
+        <v>122567122</v>
       </c>
       <c r="B20" t="n">
         <v>78660</v>
@@ -2581,10 +2576,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>441291</v>
+        <v>441315</v>
       </c>
       <c r="R20" t="n">
-        <v>6753289</v>
+        <v>6753342</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2643,10 +2638,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122567136</v>
+        <v>122567073</v>
       </c>
       <c r="B21" t="n">
-        <v>78660</v>
+        <v>8441</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2655,38 +2650,43 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>441345</v>
+        <v>441269</v>
       </c>
       <c r="R21" t="n">
-        <v>6753451</v>
+        <v>6753365</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2745,7 +2745,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122567109</v>
+        <v>122567119</v>
       </c>
       <c r="B22" t="n">
         <v>78660</v>
@@ -2785,10 +2785,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>441223</v>
+        <v>441291</v>
       </c>
       <c r="R22" t="n">
-        <v>6753536</v>
+        <v>6753289</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2847,7 +2847,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122567097</v>
+        <v>122567136</v>
       </c>
       <c r="B23" t="n">
         <v>78660</v>
@@ -2887,10 +2887,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>441320</v>
+        <v>441345</v>
       </c>
       <c r="R23" t="n">
-        <v>6753429</v>
+        <v>6753451</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2949,7 +2949,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122567122</v>
+        <v>122567109</v>
       </c>
       <c r="B24" t="n">
         <v>78660</v>
@@ -2989,10 +2989,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>441315</v>
+        <v>441223</v>
       </c>
       <c r="R24" t="n">
-        <v>6753342</v>
+        <v>6753536</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -7375,10 +7375,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122567089</v>
+        <v>122567053</v>
       </c>
       <c r="B67" t="n">
-        <v>56594</v>
+        <v>78694</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7387,43 +7387,38 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100138</v>
+        <v>185</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>441283</v>
+        <v>441420</v>
       </c>
       <c r="R67" t="n">
-        <v>6753349</v>
+        <v>6753456</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7686,10 +7681,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122567053</v>
+        <v>122567089</v>
       </c>
       <c r="B70" t="n">
-        <v>78694</v>
+        <v>56594</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7698,38 +7693,43 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>185</v>
+        <v>100138</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>441420</v>
+        <v>441283</v>
       </c>
       <c r="R70" t="n">
-        <v>6753456</v>
+        <v>6753349</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7890,10 +7890,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122567133</v>
+        <v>122567081</v>
       </c>
       <c r="B72" t="n">
-        <v>78660</v>
+        <v>78397</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -7906,21 +7906,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7930,10 +7930,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>441321</v>
+        <v>441344</v>
       </c>
       <c r="R72" t="n">
-        <v>6753447</v>
+        <v>6753341</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7992,10 +7992,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>122567036</v>
+        <v>122567064</v>
       </c>
       <c r="B73" t="n">
-        <v>79278</v>
+        <v>8441</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8004,38 +8004,43 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>441283</v>
+        <v>441389</v>
       </c>
       <c r="R73" t="n">
-        <v>6753350</v>
+        <v>6753439</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8094,10 +8099,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>122567081</v>
+        <v>122567133</v>
       </c>
       <c r="B74" t="n">
-        <v>78397</v>
+        <v>78660</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8110,21 +8115,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8134,10 +8139,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>441344</v>
+        <v>441321</v>
       </c>
       <c r="R74" t="n">
-        <v>6753341</v>
+        <v>6753447</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8196,10 +8201,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>122567048</v>
+        <v>122567036</v>
       </c>
       <c r="B75" t="n">
-        <v>74761</v>
+        <v>79278</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8212,21 +8217,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6440</v>
+        <v>6453</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8236,10 +8241,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>441302</v>
+        <v>441283</v>
       </c>
       <c r="R75" t="n">
-        <v>6753380</v>
+        <v>6753350</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8298,10 +8303,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>122567064</v>
+        <v>122567048</v>
       </c>
       <c r="B76" t="n">
-        <v>8441</v>
+        <v>74761</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8310,43 +8315,38 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>106545</v>
+        <v>6440</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>441389</v>
+        <v>441302</v>
       </c>
       <c r="R76" t="n">
-        <v>6753439</v>
+        <v>6753380</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>

--- a/artfynd/A 61943-2024 artfynd.xlsx
+++ b/artfynd/A 61943-2024 artfynd.xlsx
@@ -2434,10 +2434,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122567097</v>
+        <v>122567073</v>
       </c>
       <c r="B19" t="n">
-        <v>78660</v>
+        <v>8441</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2446,38 +2446,43 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>441320</v>
+        <v>441269</v>
       </c>
       <c r="R19" t="n">
-        <v>6753429</v>
+        <v>6753365</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2536,7 +2541,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122567122</v>
+        <v>122567119</v>
       </c>
       <c r="B20" t="n">
         <v>78660</v>
@@ -2576,10 +2581,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>441315</v>
+        <v>441291</v>
       </c>
       <c r="R20" t="n">
-        <v>6753342</v>
+        <v>6753289</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2638,10 +2643,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122567073</v>
+        <v>122567136</v>
       </c>
       <c r="B21" t="n">
-        <v>8441</v>
+        <v>78660</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2650,43 +2655,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>441269</v>
+        <v>441345</v>
       </c>
       <c r="R21" t="n">
-        <v>6753365</v>
+        <v>6753451</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2745,7 +2745,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122567119</v>
+        <v>122567109</v>
       </c>
       <c r="B22" t="n">
         <v>78660</v>
@@ -2785,10 +2785,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>441291</v>
+        <v>441223</v>
       </c>
       <c r="R22" t="n">
-        <v>6753289</v>
+        <v>6753536</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2847,7 +2847,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122567136</v>
+        <v>122567097</v>
       </c>
       <c r="B23" t="n">
         <v>78660</v>
@@ -2887,10 +2887,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>441345</v>
+        <v>441320</v>
       </c>
       <c r="R23" t="n">
-        <v>6753451</v>
+        <v>6753429</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2949,7 +2949,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122567109</v>
+        <v>122567122</v>
       </c>
       <c r="B24" t="n">
         <v>78660</v>
@@ -2989,10 +2989,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>441223</v>
+        <v>441315</v>
       </c>
       <c r="R24" t="n">
-        <v>6753536</v>
+        <v>6753342</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -4397,10 +4397,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122567049</v>
+        <v>122567118</v>
       </c>
       <c r="B38" t="n">
-        <v>74761</v>
+        <v>78660</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4413,21 +4413,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4437,10 +4437,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>441299</v>
+        <v>441277</v>
       </c>
       <c r="R38" t="n">
-        <v>6753387</v>
+        <v>6753324</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4499,7 +4499,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122567111</v>
+        <v>122567108</v>
       </c>
       <c r="B39" t="n">
         <v>78660</v>
@@ -4539,10 +4539,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>441221</v>
+        <v>441273</v>
       </c>
       <c r="R39" t="n">
-        <v>6753553</v>
+        <v>6753425</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4601,7 +4601,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122567118</v>
+        <v>122567139</v>
       </c>
       <c r="B40" t="n">
         <v>78660</v>
@@ -4641,10 +4641,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>441277</v>
+        <v>441430</v>
       </c>
       <c r="R40" t="n">
-        <v>6753324</v>
+        <v>6753445</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4703,10 +4703,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122567139</v>
+        <v>122567049</v>
       </c>
       <c r="B41" t="n">
-        <v>78660</v>
+        <v>74761</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4719,21 +4719,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4743,10 +4743,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>441430</v>
+        <v>441299</v>
       </c>
       <c r="R41" t="n">
-        <v>6753445</v>
+        <v>6753387</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4805,10 +4805,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122567075</v>
+        <v>122567111</v>
       </c>
       <c r="B42" t="n">
-        <v>8441</v>
+        <v>78660</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4817,43 +4817,38 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>441291</v>
+        <v>441221</v>
       </c>
       <c r="R42" t="n">
-        <v>6753289</v>
+        <v>6753553</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4912,7 +4907,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122567069</v>
+        <v>122567075</v>
       </c>
       <c r="B43" t="n">
         <v>8441</v>
@@ -4957,10 +4952,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>441119</v>
+        <v>441291</v>
       </c>
       <c r="R43" t="n">
-        <v>6753677</v>
+        <v>6753289</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5019,10 +5014,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122567108</v>
+        <v>122567069</v>
       </c>
       <c r="B44" t="n">
-        <v>78660</v>
+        <v>8441</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5031,38 +5026,43 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>441273</v>
+        <v>441119</v>
       </c>
       <c r="R44" t="n">
-        <v>6753425</v>
+        <v>6753677</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5733,10 +5733,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122567116</v>
+        <v>122567068</v>
       </c>
       <c r="B51" t="n">
-        <v>78660</v>
+        <v>8441</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5745,38 +5745,43 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>441199</v>
+        <v>441150</v>
       </c>
       <c r="R51" t="n">
-        <v>6753562</v>
+        <v>6753623</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5835,7 +5840,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122567107</v>
+        <v>122567116</v>
       </c>
       <c r="B52" t="n">
         <v>78660</v>
@@ -5875,10 +5880,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>441262</v>
+        <v>441199</v>
       </c>
       <c r="R52" t="n">
-        <v>6753417</v>
+        <v>6753562</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5937,7 +5942,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122567127</v>
+        <v>122567107</v>
       </c>
       <c r="B53" t="n">
         <v>78660</v>
@@ -5977,10 +5982,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>441338</v>
+        <v>441262</v>
       </c>
       <c r="R53" t="n">
-        <v>6753386</v>
+        <v>6753417</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6039,7 +6044,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122567120</v>
+        <v>122567127</v>
       </c>
       <c r="B54" t="n">
         <v>78660</v>
@@ -6079,10 +6084,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>441289</v>
+        <v>441338</v>
       </c>
       <c r="R54" t="n">
-        <v>6753324</v>
+        <v>6753386</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6141,7 +6146,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122567114</v>
+        <v>122567120</v>
       </c>
       <c r="B55" t="n">
         <v>78660</v>
@@ -6181,10 +6186,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>441206</v>
+        <v>441289</v>
       </c>
       <c r="R55" t="n">
-        <v>6753562</v>
+        <v>6753324</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6243,10 +6248,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122567046</v>
+        <v>122567114</v>
       </c>
       <c r="B56" t="n">
-        <v>74761</v>
+        <v>78660</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6259,21 +6264,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6283,10 +6288,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>441304</v>
+        <v>441206</v>
       </c>
       <c r="R56" t="n">
-        <v>6753366</v>
+        <v>6753562</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6345,10 +6350,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122567068</v>
+        <v>122567046</v>
       </c>
       <c r="B57" t="n">
-        <v>8441</v>
+        <v>74761</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6357,43 +6362,38 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>106545</v>
+        <v>6440</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>441150</v>
+        <v>441304</v>
       </c>
       <c r="R57" t="n">
-        <v>6753623</v>
+        <v>6753366</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6860,7 +6860,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122567134</v>
+        <v>122567113</v>
       </c>
       <c r="B62" t="n">
         <v>78660</v>
@@ -6900,10 +6900,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>441320</v>
+        <v>441207</v>
       </c>
       <c r="R62" t="n">
-        <v>6753453</v>
+        <v>6753568</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6962,7 +6962,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122567131</v>
+        <v>122567134</v>
       </c>
       <c r="B63" t="n">
         <v>78660</v>
@@ -7002,10 +7002,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>441347</v>
+        <v>441320</v>
       </c>
       <c r="R63" t="n">
-        <v>6753407</v>
+        <v>6753453</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7064,7 +7064,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122567105</v>
+        <v>122567131</v>
       </c>
       <c r="B64" t="n">
         <v>78660</v>
@@ -7104,10 +7104,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>441269</v>
+        <v>441347</v>
       </c>
       <c r="R64" t="n">
-        <v>6753398</v>
+        <v>6753407</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7166,10 +7166,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122567071</v>
+        <v>122567105</v>
       </c>
       <c r="B65" t="n">
-        <v>8441</v>
+        <v>78660</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7178,43 +7178,38 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>441172</v>
+        <v>441269</v>
       </c>
       <c r="R65" t="n">
-        <v>6753515</v>
+        <v>6753398</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7273,10 +7268,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122567113</v>
+        <v>122567071</v>
       </c>
       <c r="B66" t="n">
-        <v>78660</v>
+        <v>8441</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7285,38 +7280,43 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>441207</v>
+        <v>441172</v>
       </c>
       <c r="R66" t="n">
-        <v>6753568</v>
+        <v>6753515</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>

--- a/artfynd/A 61943-2024 artfynd.xlsx
+++ b/artfynd/A 61943-2024 artfynd.xlsx
@@ -1909,10 +1909,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122567042</v>
+        <v>122567083</v>
       </c>
       <c r="B14" t="n">
-        <v>79380</v>
+        <v>78499</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1925,21 +1925,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1949,10 +1949,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>441336</v>
+        <v>441348</v>
       </c>
       <c r="R14" t="n">
-        <v>6753370</v>
+        <v>6753422</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2011,7 +2011,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122567036</v>
+        <v>122567042</v>
       </c>
       <c r="B15" t="n">
         <v>79380</v>
@@ -2051,10 +2051,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>441283</v>
+        <v>441336</v>
       </c>
       <c r="R15" t="n">
-        <v>6753350</v>
+        <v>6753370</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2113,10 +2113,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122567083</v>
+        <v>122567036</v>
       </c>
       <c r="B16" t="n">
-        <v>78499</v>
+        <v>79380</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2129,21 +2129,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2153,10 +2153,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>441348</v>
+        <v>441283</v>
       </c>
       <c r="R16" t="n">
-        <v>6753422</v>
+        <v>6753350</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2623,10 +2623,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122567088</v>
+        <v>122567074</v>
       </c>
       <c r="B21" t="n">
-        <v>56688</v>
+        <v>8441</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2639,27 +2639,27 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100138</v>
+        <v>106545</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2668,10 +2668,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>441262</v>
+        <v>441284</v>
       </c>
       <c r="R21" t="n">
-        <v>6753412</v>
+        <v>6753286</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2730,10 +2730,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122567103</v>
+        <v>122567088</v>
       </c>
       <c r="B22" t="n">
-        <v>78762</v>
+        <v>56688</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2742,38 +2742,43 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>441287</v>
+        <v>441262</v>
       </c>
       <c r="R22" t="n">
-        <v>6753389</v>
+        <v>6753412</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2832,7 +2837,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122567095</v>
+        <v>122567103</v>
       </c>
       <c r="B23" t="n">
         <v>78762</v>
@@ -2872,10 +2877,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>441406</v>
+        <v>441287</v>
       </c>
       <c r="R23" t="n">
-        <v>6753439</v>
+        <v>6753389</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2934,7 +2939,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122567106</v>
+        <v>122567095</v>
       </c>
       <c r="B24" t="n">
         <v>78762</v>
@@ -2974,10 +2979,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>441266</v>
+        <v>441406</v>
       </c>
       <c r="R24" t="n">
-        <v>6753401</v>
+        <v>6753439</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3036,10 +3041,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122567044</v>
+        <v>122567106</v>
       </c>
       <c r="B25" t="n">
-        <v>79380</v>
+        <v>78762</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3052,21 +3057,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3076,10 +3081,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>441348</v>
+        <v>441266</v>
       </c>
       <c r="R25" t="n">
-        <v>6753445</v>
+        <v>6753401</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3138,10 +3143,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122567133</v>
+        <v>122567044</v>
       </c>
       <c r="B26" t="n">
-        <v>78762</v>
+        <v>79380</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3154,21 +3159,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3178,10 +3183,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>441321</v>
+        <v>441348</v>
       </c>
       <c r="R26" t="n">
-        <v>6753447</v>
+        <v>6753445</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3240,10 +3245,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122567074</v>
+        <v>122567133</v>
       </c>
       <c r="B27" t="n">
-        <v>8441</v>
+        <v>78762</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3252,43 +3257,38 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>441284</v>
+        <v>441321</v>
       </c>
       <c r="R27" t="n">
-        <v>6753286</v>
+        <v>6753447</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3347,10 +3347,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122567117</v>
+        <v>122567064</v>
       </c>
       <c r="B28" t="n">
-        <v>78762</v>
+        <v>8441</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3359,38 +3359,43 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>441193</v>
+        <v>441389</v>
       </c>
       <c r="R28" t="n">
-        <v>6753577</v>
+        <v>6753439</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3449,7 +3454,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122567099</v>
+        <v>122567117</v>
       </c>
       <c r="B29" t="n">
         <v>78762</v>
@@ -3489,10 +3494,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>441323</v>
+        <v>441193</v>
       </c>
       <c r="R29" t="n">
-        <v>6753416</v>
+        <v>6753577</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3551,7 +3556,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122567120</v>
+        <v>122567099</v>
       </c>
       <c r="B30" t="n">
         <v>78762</v>
@@ -3591,10 +3596,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>441289</v>
+        <v>441323</v>
       </c>
       <c r="R30" t="n">
-        <v>6753324</v>
+        <v>6753416</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3653,7 +3658,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122567102</v>
+        <v>122567120</v>
       </c>
       <c r="B31" t="n">
         <v>78762</v>
@@ -3693,10 +3698,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>441305</v>
+        <v>441289</v>
       </c>
       <c r="R31" t="n">
-        <v>6753384</v>
+        <v>6753324</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3755,7 +3760,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122567127</v>
+        <v>122567102</v>
       </c>
       <c r="B32" t="n">
         <v>78762</v>
@@ -3795,10 +3800,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>441338</v>
+        <v>441305</v>
       </c>
       <c r="R32" t="n">
-        <v>6753386</v>
+        <v>6753384</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3857,10 +3862,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122567064</v>
+        <v>122567127</v>
       </c>
       <c r="B33" t="n">
-        <v>8441</v>
+        <v>78762</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3869,43 +3874,38 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>441389</v>
+        <v>441338</v>
       </c>
       <c r="R33" t="n">
-        <v>6753439</v>
+        <v>6753386</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3964,10 +3964,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122567158</v>
+        <v>122567056</v>
       </c>
       <c r="B34" t="n">
-        <v>78407</v>
+        <v>57494</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3980,34 +3980,39 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>353</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>441248</v>
+        <v>441305</v>
       </c>
       <c r="R34" t="n">
-        <v>6753389</v>
+        <v>6753366</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4066,10 +4071,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122567056</v>
+        <v>122567043</v>
       </c>
       <c r="B35" t="n">
-        <v>57494</v>
+        <v>79380</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4082,39 +4087,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>441305</v>
+        <v>441348</v>
       </c>
       <c r="R35" t="n">
-        <v>6753366</v>
+        <v>6753422</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4173,10 +4173,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122567043</v>
+        <v>122567137</v>
       </c>
       <c r="B36" t="n">
-        <v>79380</v>
+        <v>78762</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4189,21 +4189,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4216,7 +4216,7 @@
         <v>441348</v>
       </c>
       <c r="R36" t="n">
-        <v>6753422</v>
+        <v>6753444</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4275,10 +4275,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122567137</v>
+        <v>122567158</v>
       </c>
       <c r="B37" t="n">
-        <v>78762</v>
+        <v>78407</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4291,21 +4291,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4315,10 +4315,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>441348</v>
+        <v>441248</v>
       </c>
       <c r="R37" t="n">
-        <v>6753444</v>
+        <v>6753389</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -6136,10 +6136,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122567070</v>
+        <v>122567053</v>
       </c>
       <c r="B55" t="n">
-        <v>8441</v>
+        <v>78796</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6148,43 +6148,38 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>106545</v>
+        <v>185</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>441158</v>
+        <v>441420</v>
       </c>
       <c r="R55" t="n">
-        <v>6753533</v>
+        <v>6753456</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6243,10 +6238,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122567053</v>
+        <v>122567121</v>
       </c>
       <c r="B56" t="n">
-        <v>78796</v>
+        <v>78762</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6259,21 +6254,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6283,10 +6278,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>441420</v>
+        <v>441306</v>
       </c>
       <c r="R56" t="n">
-        <v>6753456</v>
+        <v>6753338</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6345,7 +6340,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122567121</v>
+        <v>122567096</v>
       </c>
       <c r="B57" t="n">
         <v>78762</v>
@@ -6385,10 +6380,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>441306</v>
+        <v>441319</v>
       </c>
       <c r="R57" t="n">
-        <v>6753338</v>
+        <v>6753442</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6447,7 +6442,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122567096</v>
+        <v>122567109</v>
       </c>
       <c r="B58" t="n">
         <v>78762</v>
@@ -6487,10 +6482,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>441319</v>
+        <v>441223</v>
       </c>
       <c r="R58" t="n">
-        <v>6753442</v>
+        <v>6753536</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6549,10 +6544,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122567109</v>
+        <v>122567070</v>
       </c>
       <c r="B59" t="n">
-        <v>78762</v>
+        <v>8441</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6561,38 +6556,43 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>441223</v>
+        <v>441158</v>
       </c>
       <c r="R59" t="n">
-        <v>6753536</v>
+        <v>6753533</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>

--- a/artfynd/A 61943-2024 artfynd.xlsx
+++ b/artfynd/A 61943-2024 artfynd.xlsx
@@ -1909,10 +1909,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122567083</v>
+        <v>122567042</v>
       </c>
       <c r="B14" t="n">
-        <v>78499</v>
+        <v>79380</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1925,21 +1925,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1949,10 +1949,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>441348</v>
+        <v>441336</v>
       </c>
       <c r="R14" t="n">
-        <v>6753422</v>
+        <v>6753370</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2011,7 +2011,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122567042</v>
+        <v>122567036</v>
       </c>
       <c r="B15" t="n">
         <v>79380</v>
@@ -2051,10 +2051,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>441336</v>
+        <v>441283</v>
       </c>
       <c r="R15" t="n">
-        <v>6753370</v>
+        <v>6753350</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2113,10 +2113,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122567036</v>
+        <v>122567083</v>
       </c>
       <c r="B16" t="n">
-        <v>79380</v>
+        <v>78499</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2129,21 +2129,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2153,10 +2153,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>441283</v>
+        <v>441348</v>
       </c>
       <c r="R16" t="n">
-        <v>6753350</v>
+        <v>6753422</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -3347,10 +3347,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122567064</v>
+        <v>122567117</v>
       </c>
       <c r="B28" t="n">
-        <v>8441</v>
+        <v>78762</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3359,43 +3359,38 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>441389</v>
+        <v>441193</v>
       </c>
       <c r="R28" t="n">
-        <v>6753439</v>
+        <v>6753577</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3454,7 +3449,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122567117</v>
+        <v>122567099</v>
       </c>
       <c r="B29" t="n">
         <v>78762</v>
@@ -3494,10 +3489,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>441193</v>
+        <v>441323</v>
       </c>
       <c r="R29" t="n">
-        <v>6753577</v>
+        <v>6753416</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3556,7 +3551,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122567099</v>
+        <v>122567120</v>
       </c>
       <c r="B30" t="n">
         <v>78762</v>
@@ -3596,10 +3591,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>441323</v>
+        <v>441289</v>
       </c>
       <c r="R30" t="n">
-        <v>6753416</v>
+        <v>6753324</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3658,7 +3653,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122567120</v>
+        <v>122567102</v>
       </c>
       <c r="B31" t="n">
         <v>78762</v>
@@ -3698,10 +3693,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>441289</v>
+        <v>441305</v>
       </c>
       <c r="R31" t="n">
-        <v>6753324</v>
+        <v>6753384</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3760,7 +3755,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122567102</v>
+        <v>122567127</v>
       </c>
       <c r="B32" t="n">
         <v>78762</v>
@@ -3800,10 +3795,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>441305</v>
+        <v>441338</v>
       </c>
       <c r="R32" t="n">
-        <v>6753384</v>
+        <v>6753386</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3862,10 +3857,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122567127</v>
+        <v>122567064</v>
       </c>
       <c r="B33" t="n">
-        <v>78762</v>
+        <v>8441</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3874,38 +3869,43 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>441338</v>
+        <v>441389</v>
       </c>
       <c r="R33" t="n">
-        <v>6753386</v>
+        <v>6753439</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3964,10 +3964,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122567056</v>
+        <v>122567158</v>
       </c>
       <c r="B34" t="n">
-        <v>57494</v>
+        <v>78407</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3980,39 +3980,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>353</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>441305</v>
+        <v>441248</v>
       </c>
       <c r="R34" t="n">
-        <v>6753366</v>
+        <v>6753389</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4071,10 +4066,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122567043</v>
+        <v>122567056</v>
       </c>
       <c r="B35" t="n">
-        <v>79380</v>
+        <v>57494</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4087,34 +4082,39 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>441348</v>
+        <v>441305</v>
       </c>
       <c r="R35" t="n">
-        <v>6753422</v>
+        <v>6753366</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4173,10 +4173,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122567137</v>
+        <v>122567043</v>
       </c>
       <c r="B36" t="n">
-        <v>78762</v>
+        <v>79380</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4189,21 +4189,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4216,7 +4216,7 @@
         <v>441348</v>
       </c>
       <c r="R36" t="n">
-        <v>6753444</v>
+        <v>6753422</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4275,10 +4275,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122567158</v>
+        <v>122567137</v>
       </c>
       <c r="B37" t="n">
-        <v>78407</v>
+        <v>78762</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4291,21 +4291,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4315,10 +4315,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>441248</v>
+        <v>441348</v>
       </c>
       <c r="R37" t="n">
-        <v>6753389</v>
+        <v>6753444</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5820,10 +5820,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122567116</v>
+        <v>122567059</v>
       </c>
       <c r="B52" t="n">
-        <v>78762</v>
+        <v>8441</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5832,38 +5832,43 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>441199</v>
+        <v>441302</v>
       </c>
       <c r="R52" t="n">
-        <v>6753562</v>
+        <v>6753294</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5922,7 +5927,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122567059</v>
+        <v>122567072</v>
       </c>
       <c r="B53" t="n">
         <v>8441</v>
@@ -5958,7 +5963,7 @@
       <c r="I53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -5967,10 +5972,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>441302</v>
+        <v>441255</v>
       </c>
       <c r="R53" t="n">
-        <v>6753294</v>
+        <v>6753382</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6029,10 +6034,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122567072</v>
+        <v>122567116</v>
       </c>
       <c r="B54" t="n">
-        <v>8441</v>
+        <v>78762</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6041,43 +6046,38 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>441255</v>
+        <v>441199</v>
       </c>
       <c r="R54" t="n">
-        <v>6753382</v>
+        <v>6753562</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>

--- a/artfynd/A 61943-2024 artfynd.xlsx
+++ b/artfynd/A 61943-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122567100</v>
+        <v>122567135</v>
       </c>
       <c r="B2" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>441332</v>
+        <v>441322</v>
       </c>
       <c r="R2" t="n">
-        <v>6753382</v>
+        <v>6753459</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -780,7 +780,7 @@
         <v>122567035</v>
       </c>
       <c r="B3" t="n">
-        <v>79380</v>
+        <v>79384</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122567051</v>
+        <v>122567132</v>
       </c>
       <c r="B4" t="n">
-        <v>74863</v>
+        <v>78766</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>441352</v>
+        <v>441329</v>
       </c>
       <c r="R4" t="n">
-        <v>6753455</v>
+        <v>6753438</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122567077</v>
+        <v>122567050</v>
       </c>
       <c r="B5" t="n">
-        <v>8441</v>
+        <v>74863</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,43 +993,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>106545</v>
+        <v>6440</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>441381</v>
+        <v>441314</v>
       </c>
       <c r="R5" t="n">
-        <v>6753451</v>
+        <v>6753342</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122567081</v>
+        <v>122567108</v>
       </c>
       <c r="B6" t="n">
-        <v>78499</v>
+        <v>78766</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1104,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1128,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>441344</v>
+        <v>441273</v>
       </c>
       <c r="R6" t="n">
-        <v>6753341</v>
+        <v>6753425</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1190,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122567111</v>
+        <v>122567106</v>
       </c>
       <c r="B7" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1230,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>441221</v>
+        <v>441266</v>
       </c>
       <c r="R7" t="n">
-        <v>6753553</v>
+        <v>6753401</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1295,7 +1290,7 @@
         <v>122567126</v>
       </c>
       <c r="B8" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1394,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122567049</v>
+        <v>122567091</v>
       </c>
       <c r="B9" t="n">
-        <v>74863</v>
+        <v>78766</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1410,21 +1405,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1434,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>441299</v>
+        <v>441420</v>
       </c>
       <c r="R9" t="n">
-        <v>6753387</v>
+        <v>6753456</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1496,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122567107</v>
+        <v>122567071</v>
       </c>
       <c r="B10" t="n">
-        <v>78762</v>
+        <v>8441</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1508,38 +1503,43 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>441262</v>
+        <v>441172</v>
       </c>
       <c r="R10" t="n">
-        <v>6753417</v>
+        <v>6753515</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1598,10 +1598,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122567091</v>
+        <v>122567068</v>
       </c>
       <c r="B11" t="n">
-        <v>78762</v>
+        <v>8441</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1610,38 +1610,43 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>441420</v>
+        <v>441150</v>
       </c>
       <c r="R11" t="n">
-        <v>6753456</v>
+        <v>6753623</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1700,10 +1705,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122567098</v>
+        <v>122567103</v>
       </c>
       <c r="B12" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1740,10 +1745,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>441329</v>
+        <v>441287</v>
       </c>
       <c r="R12" t="n">
-        <v>6753411</v>
+        <v>6753389</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1802,10 +1807,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122567066</v>
+        <v>122567034</v>
       </c>
       <c r="B13" t="n">
-        <v>8441</v>
+        <v>79384</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1814,43 +1819,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>441258</v>
+        <v>441152</v>
       </c>
       <c r="R13" t="n">
-        <v>6753406</v>
+        <v>6753562</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1909,10 +1909,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122567042</v>
+        <v>122567105</v>
       </c>
       <c r="B14" t="n">
-        <v>79380</v>
+        <v>78766</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1925,21 +1925,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1949,10 +1949,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>441336</v>
+        <v>441269</v>
       </c>
       <c r="R14" t="n">
-        <v>6753370</v>
+        <v>6753398</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2011,10 +2011,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122567036</v>
+        <v>122567033</v>
       </c>
       <c r="B15" t="n">
-        <v>79380</v>
+        <v>79384</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2051,10 +2051,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>441283</v>
+        <v>441194</v>
       </c>
       <c r="R15" t="n">
-        <v>6753350</v>
+        <v>6753576</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2113,10 +2113,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122567083</v>
+        <v>122567134</v>
       </c>
       <c r="B16" t="n">
-        <v>78499</v>
+        <v>78766</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2129,21 +2129,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2153,10 +2153,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>441348</v>
+        <v>441320</v>
       </c>
       <c r="R16" t="n">
-        <v>6753422</v>
+        <v>6753453</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2215,10 +2215,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122567039</v>
+        <v>122567047</v>
       </c>
       <c r="B17" t="n">
-        <v>79380</v>
+        <v>74863</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2231,21 +2231,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>6440</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2255,10 +2255,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>441344</v>
+        <v>441304</v>
       </c>
       <c r="R17" t="n">
-        <v>6753341</v>
+        <v>6753377</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2317,10 +2317,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122567048</v>
+        <v>122567056</v>
       </c>
       <c r="B18" t="n">
-        <v>74863</v>
+        <v>57494</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2333,34 +2333,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6440</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>441302</v>
+        <v>441305</v>
       </c>
       <c r="R18" t="n">
-        <v>6753380</v>
+        <v>6753366</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2419,10 +2424,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122567114</v>
+        <v>122567118</v>
       </c>
       <c r="B19" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2459,10 +2464,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>441206</v>
+        <v>441277</v>
       </c>
       <c r="R19" t="n">
-        <v>6753562</v>
+        <v>6753324</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2521,10 +2526,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122567123</v>
+        <v>122567128</v>
       </c>
       <c r="B20" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2561,10 +2566,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>441334</v>
+        <v>441350</v>
       </c>
       <c r="R20" t="n">
-        <v>6753341</v>
+        <v>6753388</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2623,10 +2628,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122567074</v>
+        <v>122567137</v>
       </c>
       <c r="B21" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2635,43 +2640,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>441284</v>
+        <v>441348</v>
       </c>
       <c r="R21" t="n">
-        <v>6753286</v>
+        <v>6753444</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2730,10 +2730,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122567088</v>
+        <v>122567096</v>
       </c>
       <c r="B22" t="n">
-        <v>56688</v>
+        <v>78766</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2742,43 +2742,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>441262</v>
+        <v>441319</v>
       </c>
       <c r="R22" t="n">
-        <v>6753412</v>
+        <v>6753442</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2837,10 +2832,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122567103</v>
+        <v>122567111</v>
       </c>
       <c r="B23" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2877,10 +2872,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>441287</v>
+        <v>441221</v>
       </c>
       <c r="R23" t="n">
-        <v>6753389</v>
+        <v>6753553</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2939,10 +2934,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122567095</v>
+        <v>122567123</v>
       </c>
       <c r="B24" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2979,10 +2974,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>441406</v>
+        <v>441334</v>
       </c>
       <c r="R24" t="n">
-        <v>6753439</v>
+        <v>6753341</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3041,10 +3036,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122567106</v>
+        <v>122567049</v>
       </c>
       <c r="B25" t="n">
-        <v>78762</v>
+        <v>74863</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3057,21 +3052,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3081,10 +3076,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>441266</v>
+        <v>441299</v>
       </c>
       <c r="R25" t="n">
-        <v>6753401</v>
+        <v>6753387</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3143,10 +3138,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122567044</v>
+        <v>122567069</v>
       </c>
       <c r="B26" t="n">
-        <v>79380</v>
+        <v>8441</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3155,38 +3150,43 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>441348</v>
+        <v>441119</v>
       </c>
       <c r="R26" t="n">
-        <v>6753445</v>
+        <v>6753677</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3245,10 +3245,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122567133</v>
+        <v>122567075</v>
       </c>
       <c r="B27" t="n">
-        <v>78762</v>
+        <v>8441</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3257,38 +3257,43 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>441321</v>
+        <v>441291</v>
       </c>
       <c r="R27" t="n">
-        <v>6753447</v>
+        <v>6753289</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3347,10 +3352,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122567117</v>
+        <v>122567077</v>
       </c>
       <c r="B28" t="n">
-        <v>78762</v>
+        <v>8441</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3359,38 +3364,43 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>441193</v>
+        <v>441381</v>
       </c>
       <c r="R28" t="n">
-        <v>6753577</v>
+        <v>6753451</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3449,10 +3459,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122567099</v>
+        <v>122567097</v>
       </c>
       <c r="B29" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3489,10 +3499,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>441323</v>
+        <v>441320</v>
       </c>
       <c r="R29" t="n">
-        <v>6753416</v>
+        <v>6753429</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3551,10 +3561,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122567120</v>
+        <v>122567104</v>
       </c>
       <c r="B30" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3591,10 +3601,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>441289</v>
+        <v>441277</v>
       </c>
       <c r="R30" t="n">
-        <v>6753324</v>
+        <v>6753396</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3653,10 +3663,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122567102</v>
+        <v>122567100</v>
       </c>
       <c r="B31" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3693,10 +3703,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>441305</v>
+        <v>441332</v>
       </c>
       <c r="R31" t="n">
-        <v>6753384</v>
+        <v>6753382</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3755,10 +3765,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122567127</v>
+        <v>122567125</v>
       </c>
       <c r="B32" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3795,10 +3805,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>441338</v>
+        <v>441356</v>
       </c>
       <c r="R32" t="n">
-        <v>6753386</v>
+        <v>6753361</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3857,10 +3867,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122567064</v>
+        <v>122567114</v>
       </c>
       <c r="B33" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3869,43 +3879,38 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>441389</v>
+        <v>441206</v>
       </c>
       <c r="R33" t="n">
-        <v>6753439</v>
+        <v>6753562</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3964,10 +3969,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122567158</v>
+        <v>122567119</v>
       </c>
       <c r="B34" t="n">
-        <v>78407</v>
+        <v>78766</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3980,21 +3985,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4004,10 +4009,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>441248</v>
+        <v>441291</v>
       </c>
       <c r="R34" t="n">
-        <v>6753389</v>
+        <v>6753289</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4066,10 +4071,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122567056</v>
+        <v>122567089</v>
       </c>
       <c r="B35" t="n">
-        <v>57494</v>
+        <v>56688</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4078,31 +4083,31 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4111,10 +4116,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>441305</v>
+        <v>441283</v>
       </c>
       <c r="R35" t="n">
-        <v>6753366</v>
+        <v>6753349</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4173,10 +4178,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122567043</v>
+        <v>122567048</v>
       </c>
       <c r="B36" t="n">
-        <v>79380</v>
+        <v>74863</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4189,21 +4194,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6453</v>
+        <v>6440</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4213,10 +4218,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>441348</v>
+        <v>441302</v>
       </c>
       <c r="R36" t="n">
-        <v>6753422</v>
+        <v>6753380</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4275,10 +4280,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122567137</v>
+        <v>122567053</v>
       </c>
       <c r="B37" t="n">
-        <v>78762</v>
+        <v>78800</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4291,21 +4296,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4315,10 +4320,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>441348</v>
+        <v>441420</v>
       </c>
       <c r="R37" t="n">
-        <v>6753444</v>
+        <v>6753456</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4377,10 +4382,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122567089</v>
+        <v>122567131</v>
       </c>
       <c r="B38" t="n">
-        <v>56688</v>
+        <v>78766</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4389,43 +4394,38 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>441283</v>
+        <v>441347</v>
       </c>
       <c r="R38" t="n">
-        <v>6753349</v>
+        <v>6753407</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4484,10 +4484,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122567075</v>
+        <v>122567121</v>
       </c>
       <c r="B39" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4496,43 +4496,38 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>441291</v>
+        <v>441306</v>
       </c>
       <c r="R39" t="n">
-        <v>6753289</v>
+        <v>6753338</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4591,10 +4586,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122567050</v>
+        <v>122567139</v>
       </c>
       <c r="B40" t="n">
-        <v>74863</v>
+        <v>78766</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4607,21 +4602,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4631,10 +4626,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>441314</v>
+        <v>441430</v>
       </c>
       <c r="R40" t="n">
-        <v>6753342</v>
+        <v>6753445</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4693,10 +4688,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122567047</v>
+        <v>122567102</v>
       </c>
       <c r="B41" t="n">
-        <v>74863</v>
+        <v>78766</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4709,21 +4704,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4733,10 +4728,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>441304</v>
+        <v>441305</v>
       </c>
       <c r="R41" t="n">
-        <v>6753377</v>
+        <v>6753384</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4795,10 +4790,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122567134</v>
+        <v>122567133</v>
       </c>
       <c r="B42" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4835,10 +4830,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>441320</v>
+        <v>441321</v>
       </c>
       <c r="R42" t="n">
-        <v>6753453</v>
+        <v>6753447</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4897,10 +4892,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122567136</v>
+        <v>122567051</v>
       </c>
       <c r="B43" t="n">
-        <v>78762</v>
+        <v>74863</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4913,21 +4908,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4937,10 +4932,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>441345</v>
+        <v>441352</v>
       </c>
       <c r="R43" t="n">
-        <v>6753451</v>
+        <v>6753455</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4999,10 +4994,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122567104</v>
+        <v>122567066</v>
       </c>
       <c r="B44" t="n">
-        <v>78762</v>
+        <v>8441</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5011,38 +5006,43 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>441277</v>
+        <v>441258</v>
       </c>
       <c r="R44" t="n">
-        <v>6753396</v>
+        <v>6753406</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5101,10 +5101,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122567139</v>
+        <v>122567098</v>
       </c>
       <c r="B45" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5141,10 +5141,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>441430</v>
+        <v>441329</v>
       </c>
       <c r="R45" t="n">
-        <v>6753445</v>
+        <v>6753411</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5203,10 +5203,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122567038</v>
+        <v>122567138</v>
       </c>
       <c r="B46" t="n">
-        <v>79380</v>
+        <v>78766</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5219,21 +5219,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5243,10 +5243,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>441336</v>
+        <v>441383</v>
       </c>
       <c r="R46" t="n">
-        <v>6753344</v>
+        <v>6753450</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5305,10 +5305,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122567122</v>
+        <v>122567059</v>
       </c>
       <c r="B47" t="n">
-        <v>78762</v>
+        <v>8441</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5317,38 +5317,43 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>441315</v>
+        <v>441302</v>
       </c>
       <c r="R47" t="n">
-        <v>6753342</v>
+        <v>6753294</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5407,10 +5412,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122567138</v>
+        <v>122567120</v>
       </c>
       <c r="B48" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5447,10 +5452,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>441383</v>
+        <v>441289</v>
       </c>
       <c r="R48" t="n">
-        <v>6753450</v>
+        <v>6753324</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5509,10 +5514,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122567033</v>
+        <v>122567081</v>
       </c>
       <c r="B49" t="n">
-        <v>79380</v>
+        <v>78503</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5525,21 +5530,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5549,10 +5554,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>441194</v>
+        <v>441344</v>
       </c>
       <c r="R49" t="n">
-        <v>6753576</v>
+        <v>6753341</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5611,10 +5616,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122567119</v>
+        <v>122567083</v>
       </c>
       <c r="B50" t="n">
-        <v>78762</v>
+        <v>78503</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5627,21 +5632,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5651,10 +5656,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>441291</v>
+        <v>441348</v>
       </c>
       <c r="R50" t="n">
-        <v>6753289</v>
+        <v>6753422</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5713,10 +5718,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122567068</v>
+        <v>122567109</v>
       </c>
       <c r="B51" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5725,43 +5730,38 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>441150</v>
+        <v>441223</v>
       </c>
       <c r="R51" t="n">
-        <v>6753623</v>
+        <v>6753536</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5820,10 +5820,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122567059</v>
+        <v>122567038</v>
       </c>
       <c r="B52" t="n">
-        <v>8441</v>
+        <v>79384</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5832,43 +5832,38 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>441302</v>
+        <v>441336</v>
       </c>
       <c r="R52" t="n">
-        <v>6753294</v>
+        <v>6753344</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5927,10 +5922,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122567072</v>
+        <v>122567036</v>
       </c>
       <c r="B53" t="n">
-        <v>8441</v>
+        <v>79384</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5939,43 +5934,38 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>441255</v>
+        <v>441283</v>
       </c>
       <c r="R53" t="n">
-        <v>6753382</v>
+        <v>6753350</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6034,10 +6024,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122567116</v>
+        <v>122567117</v>
       </c>
       <c r="B54" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6074,10 +6064,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>441199</v>
+        <v>441193</v>
       </c>
       <c r="R54" t="n">
-        <v>6753562</v>
+        <v>6753577</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6136,10 +6126,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122567053</v>
+        <v>122567067</v>
       </c>
       <c r="B55" t="n">
-        <v>78796</v>
+        <v>8441</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6148,38 +6138,43 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>185</v>
+        <v>106545</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>441420</v>
+        <v>441231</v>
       </c>
       <c r="R55" t="n">
-        <v>6753456</v>
+        <v>6753537</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6238,10 +6233,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122567121</v>
+        <v>122567064</v>
       </c>
       <c r="B56" t="n">
-        <v>78762</v>
+        <v>8441</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6250,38 +6245,43 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>441306</v>
+        <v>441389</v>
       </c>
       <c r="R56" t="n">
-        <v>6753338</v>
+        <v>6753439</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6340,10 +6340,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122567096</v>
+        <v>122567095</v>
       </c>
       <c r="B57" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6380,10 +6380,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>441319</v>
+        <v>441406</v>
       </c>
       <c r="R57" t="n">
-        <v>6753442</v>
+        <v>6753439</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6442,10 +6442,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122567109</v>
+        <v>122567107</v>
       </c>
       <c r="B58" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6482,10 +6482,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>441223</v>
+        <v>441262</v>
       </c>
       <c r="R58" t="n">
-        <v>6753536</v>
+        <v>6753417</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6544,10 +6544,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122567070</v>
+        <v>122567127</v>
       </c>
       <c r="B59" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6556,43 +6556,38 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>441158</v>
+        <v>441338</v>
       </c>
       <c r="R59" t="n">
-        <v>6753533</v>
+        <v>6753386</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6651,10 +6646,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122567069</v>
+        <v>122567042</v>
       </c>
       <c r="B60" t="n">
-        <v>8441</v>
+        <v>79384</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6663,43 +6658,38 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>441119</v>
+        <v>441336</v>
       </c>
       <c r="R60" t="n">
-        <v>6753677</v>
+        <v>6753370</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6758,10 +6748,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122567041</v>
+        <v>122567122</v>
       </c>
       <c r="B61" t="n">
-        <v>79380</v>
+        <v>78766</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6774,21 +6764,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6798,10 +6788,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>441357</v>
+        <v>441315</v>
       </c>
       <c r="R61" t="n">
-        <v>6753361</v>
+        <v>6753342</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6860,10 +6850,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122567135</v>
+        <v>122567113</v>
       </c>
       <c r="B62" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6900,10 +6890,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>441322</v>
+        <v>441207</v>
       </c>
       <c r="R62" t="n">
-        <v>6753459</v>
+        <v>6753568</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6962,10 +6952,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122567105</v>
+        <v>122567039</v>
       </c>
       <c r="B63" t="n">
-        <v>78762</v>
+        <v>79384</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -6978,21 +6968,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7002,10 +6992,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>441269</v>
+        <v>441344</v>
       </c>
       <c r="R63" t="n">
-        <v>6753398</v>
+        <v>6753341</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7064,10 +7054,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122567101</v>
+        <v>122567046</v>
       </c>
       <c r="B64" t="n">
-        <v>78762</v>
+        <v>74863</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7080,21 +7070,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7104,10 +7094,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>441301</v>
+        <v>441304</v>
       </c>
       <c r="R64" t="n">
-        <v>6753376</v>
+        <v>6753366</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7166,10 +7156,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122567131</v>
+        <v>122567088</v>
       </c>
       <c r="B65" t="n">
-        <v>78762</v>
+        <v>56688</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7178,38 +7168,43 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>441347</v>
+        <v>441262</v>
       </c>
       <c r="R65" t="n">
-        <v>6753407</v>
+        <v>6753412</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7268,10 +7263,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122567128</v>
+        <v>122567074</v>
       </c>
       <c r="B66" t="n">
-        <v>78762</v>
+        <v>8441</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7280,38 +7275,43 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>441350</v>
+        <v>441284</v>
       </c>
       <c r="R66" t="n">
-        <v>6753388</v>
+        <v>6753286</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7370,10 +7370,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122567113</v>
+        <v>122567072</v>
       </c>
       <c r="B67" t="n">
-        <v>78762</v>
+        <v>8441</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7382,38 +7382,43 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>441207</v>
+        <v>441255</v>
       </c>
       <c r="R67" t="n">
-        <v>6753568</v>
+        <v>6753382</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7472,10 +7477,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122567067</v>
+        <v>122567101</v>
       </c>
       <c r="B68" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7484,43 +7489,38 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>441231</v>
+        <v>441301</v>
       </c>
       <c r="R68" t="n">
-        <v>6753537</v>
+        <v>6753376</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7579,10 +7579,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122567071</v>
+        <v>122567099</v>
       </c>
       <c r="B69" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7591,43 +7591,38 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>441172</v>
+        <v>441323</v>
       </c>
       <c r="R69" t="n">
-        <v>6753515</v>
+        <v>6753416</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7686,10 +7681,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122567097</v>
+        <v>122567041</v>
       </c>
       <c r="B70" t="n">
-        <v>78762</v>
+        <v>79384</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7702,21 +7697,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7726,10 +7721,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>441320</v>
+        <v>441357</v>
       </c>
       <c r="R70" t="n">
-        <v>6753429</v>
+        <v>6753361</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7788,10 +7783,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122567108</v>
+        <v>122567044</v>
       </c>
       <c r="B71" t="n">
-        <v>78762</v>
+        <v>79384</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7804,21 +7799,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7828,10 +7823,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>441273</v>
+        <v>441348</v>
       </c>
       <c r="R71" t="n">
-        <v>6753425</v>
+        <v>6753445</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7890,10 +7885,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122567132</v>
+        <v>122567043</v>
       </c>
       <c r="B72" t="n">
-        <v>78762</v>
+        <v>79384</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -7906,21 +7901,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7930,10 +7925,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>441329</v>
+        <v>441348</v>
       </c>
       <c r="R72" t="n">
-        <v>6753438</v>
+        <v>6753422</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7992,10 +7987,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>122567125</v>
+        <v>122567073</v>
       </c>
       <c r="B73" t="n">
-        <v>78762</v>
+        <v>8441</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8004,38 +7999,43 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>441356</v>
+        <v>441269</v>
       </c>
       <c r="R73" t="n">
-        <v>6753361</v>
+        <v>6753365</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8094,10 +8094,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>122567046</v>
+        <v>122567158</v>
       </c>
       <c r="B74" t="n">
-        <v>74863</v>
+        <v>78411</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8110,21 +8110,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6440</v>
+        <v>353</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8134,10 +8134,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>441304</v>
+        <v>441248</v>
       </c>
       <c r="R74" t="n">
-        <v>6753366</v>
+        <v>6753389</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8196,10 +8196,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>122567073</v>
+        <v>122567136</v>
       </c>
       <c r="B75" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8208,43 +8208,38 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>441269</v>
+        <v>441345</v>
       </c>
       <c r="R75" t="n">
-        <v>6753365</v>
+        <v>6753451</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8303,10 +8298,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>122567118</v>
+        <v>122567112</v>
       </c>
       <c r="B76" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8343,10 +8338,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>441277</v>
+        <v>441217</v>
       </c>
       <c r="R76" t="n">
-        <v>6753324</v>
+        <v>6753556</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8405,10 +8400,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>122567112</v>
+        <v>122567116</v>
       </c>
       <c r="B77" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8445,10 +8440,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>441217</v>
+        <v>441199</v>
       </c>
       <c r="R77" t="n">
-        <v>6753556</v>
+        <v>6753562</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8507,10 +8502,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>122567034</v>
+        <v>122567070</v>
       </c>
       <c r="B78" t="n">
-        <v>79380</v>
+        <v>8441</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8519,38 +8514,43 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>441152</v>
+        <v>441158</v>
       </c>
       <c r="R78" t="n">
-        <v>6753562</v>
+        <v>6753533</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>

--- a/artfynd/A 61943-2024 artfynd.xlsx
+++ b/artfynd/A 61943-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122567135</v>
+        <v>122567071</v>
       </c>
       <c r="B2" t="n">
-        <v>78766</v>
+        <v>8441</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,43 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>441322</v>
+        <v>441172</v>
       </c>
       <c r="R2" t="n">
-        <v>6753459</v>
+        <v>6753515</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122567035</v>
+        <v>122567068</v>
       </c>
       <c r="B3" t="n">
-        <v>79384</v>
+        <v>8441</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,38 +794,43 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>441158</v>
+        <v>441150</v>
       </c>
       <c r="R3" t="n">
-        <v>6753553</v>
+        <v>6753623</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122567132</v>
+        <v>122567119</v>
       </c>
       <c r="B4" t="n">
         <v>78766</v>
@@ -919,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>441329</v>
+        <v>441291</v>
       </c>
       <c r="R4" t="n">
-        <v>6753438</v>
+        <v>6753289</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122567050</v>
+        <v>122567107</v>
       </c>
       <c r="B5" t="n">
-        <v>74863</v>
+        <v>78766</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +1007,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>441314</v>
+        <v>441262</v>
       </c>
       <c r="R5" t="n">
-        <v>6753342</v>
+        <v>6753417</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,7 +1093,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122567108</v>
+        <v>122567100</v>
       </c>
       <c r="B6" t="n">
         <v>78766</v>
@@ -1123,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>441273</v>
+        <v>441332</v>
       </c>
       <c r="R6" t="n">
-        <v>6753425</v>
+        <v>6753382</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,7 +1195,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122567106</v>
+        <v>122567096</v>
       </c>
       <c r="B7" t="n">
         <v>78766</v>
@@ -1225,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>441266</v>
+        <v>441319</v>
       </c>
       <c r="R7" t="n">
-        <v>6753401</v>
+        <v>6753442</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,7 +1297,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122567126</v>
+        <v>122567133</v>
       </c>
       <c r="B8" t="n">
         <v>78766</v>
@@ -1327,10 +1337,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>441344</v>
+        <v>441321</v>
       </c>
       <c r="R8" t="n">
-        <v>6753362</v>
+        <v>6753447</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,7 +1399,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122567091</v>
+        <v>122567138</v>
       </c>
       <c r="B9" t="n">
         <v>78766</v>
@@ -1429,10 +1439,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>441420</v>
+        <v>441383</v>
       </c>
       <c r="R9" t="n">
-        <v>6753456</v>
+        <v>6753450</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,10 +1501,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122567071</v>
+        <v>122567050</v>
       </c>
       <c r="B10" t="n">
-        <v>8441</v>
+        <v>74863</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1503,43 +1513,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>106545</v>
+        <v>6440</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>441172</v>
+        <v>441314</v>
       </c>
       <c r="R10" t="n">
-        <v>6753515</v>
+        <v>6753342</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1598,7 +1603,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122567068</v>
+        <v>122567069</v>
       </c>
       <c r="B11" t="n">
         <v>8441</v>
@@ -1643,10 +1648,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>441150</v>
+        <v>441119</v>
       </c>
       <c r="R11" t="n">
-        <v>6753623</v>
+        <v>6753677</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1705,7 +1710,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122567103</v>
+        <v>122567131</v>
       </c>
       <c r="B12" t="n">
         <v>78766</v>
@@ -1745,10 +1750,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>441287</v>
+        <v>441347</v>
       </c>
       <c r="R12" t="n">
-        <v>6753389</v>
+        <v>6753407</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1807,10 +1812,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122567034</v>
+        <v>122567047</v>
       </c>
       <c r="B13" t="n">
-        <v>79384</v>
+        <v>74863</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1823,21 +1828,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>6440</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1847,10 +1852,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>441152</v>
+        <v>441304</v>
       </c>
       <c r="R13" t="n">
-        <v>6753562</v>
+        <v>6753377</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1909,7 +1914,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122567105</v>
+        <v>122567103</v>
       </c>
       <c r="B14" t="n">
         <v>78766</v>
@@ -1949,10 +1954,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>441269</v>
+        <v>441287</v>
       </c>
       <c r="R14" t="n">
-        <v>6753398</v>
+        <v>6753389</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2011,10 +2016,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122567033</v>
+        <v>122567098</v>
       </c>
       <c r="B15" t="n">
-        <v>79384</v>
+        <v>78766</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2027,21 +2032,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2051,10 +2056,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>441194</v>
+        <v>441329</v>
       </c>
       <c r="R15" t="n">
-        <v>6753576</v>
+        <v>6753411</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2113,7 +2118,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122567134</v>
+        <v>122567104</v>
       </c>
       <c r="B16" t="n">
         <v>78766</v>
@@ -2153,10 +2158,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>441320</v>
+        <v>441277</v>
       </c>
       <c r="R16" t="n">
-        <v>6753453</v>
+        <v>6753396</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2215,10 +2220,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122567047</v>
+        <v>122567101</v>
       </c>
       <c r="B17" t="n">
-        <v>74863</v>
+        <v>78766</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2231,21 +2236,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2255,10 +2260,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>441304</v>
+        <v>441301</v>
       </c>
       <c r="R17" t="n">
-        <v>6753377</v>
+        <v>6753376</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2317,10 +2322,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122567056</v>
+        <v>122567128</v>
       </c>
       <c r="B18" t="n">
-        <v>57494</v>
+        <v>78766</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2333,39 +2338,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>441305</v>
+        <v>441350</v>
       </c>
       <c r="R18" t="n">
-        <v>6753366</v>
+        <v>6753388</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2424,10 +2424,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122567118</v>
+        <v>122567033</v>
       </c>
       <c r="B19" t="n">
-        <v>78766</v>
+        <v>79384</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2440,21 +2440,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2464,10 +2464,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>441277</v>
+        <v>441194</v>
       </c>
       <c r="R19" t="n">
-        <v>6753324</v>
+        <v>6753576</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2526,10 +2526,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122567128</v>
+        <v>122567053</v>
       </c>
       <c r="B20" t="n">
-        <v>78766</v>
+        <v>78800</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2542,21 +2542,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2566,10 +2566,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>441350</v>
+        <v>441420</v>
       </c>
       <c r="R20" t="n">
-        <v>6753388</v>
+        <v>6753456</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2628,7 +2628,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122567137</v>
+        <v>122567091</v>
       </c>
       <c r="B21" t="n">
         <v>78766</v>
@@ -2668,10 +2668,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>441348</v>
+        <v>441420</v>
       </c>
       <c r="R21" t="n">
-        <v>6753444</v>
+        <v>6753456</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2730,7 +2730,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122567096</v>
+        <v>122567120</v>
       </c>
       <c r="B22" t="n">
         <v>78766</v>
@@ -2770,10 +2770,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>441319</v>
+        <v>441289</v>
       </c>
       <c r="R22" t="n">
-        <v>6753442</v>
+        <v>6753324</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2934,7 +2934,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122567123</v>
+        <v>122567097</v>
       </c>
       <c r="B24" t="n">
         <v>78766</v>
@@ -2974,10 +2974,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>441334</v>
+        <v>441320</v>
       </c>
       <c r="R24" t="n">
-        <v>6753341</v>
+        <v>6753429</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3036,10 +3036,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122567049</v>
+        <v>122567072</v>
       </c>
       <c r="B25" t="n">
-        <v>74863</v>
+        <v>8441</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3048,38 +3048,43 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6440</v>
+        <v>106545</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>441299</v>
+        <v>441255</v>
       </c>
       <c r="R25" t="n">
-        <v>6753387</v>
+        <v>6753382</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3138,10 +3143,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122567069</v>
+        <v>122567158</v>
       </c>
       <c r="B26" t="n">
-        <v>8441</v>
+        <v>78411</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3150,43 +3155,38 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>106545</v>
+        <v>353</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>441119</v>
+        <v>441248</v>
       </c>
       <c r="R26" t="n">
-        <v>6753677</v>
+        <v>6753389</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3245,7 +3245,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122567075</v>
+        <v>122567059</v>
       </c>
       <c r="B27" t="n">
         <v>8441</v>
@@ -3281,7 +3281,7 @@
       <c r="I27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3290,10 +3290,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>441291</v>
+        <v>441302</v>
       </c>
       <c r="R27" t="n">
-        <v>6753289</v>
+        <v>6753294</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3352,10 +3352,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122567077</v>
+        <v>122567051</v>
       </c>
       <c r="B28" t="n">
-        <v>8441</v>
+        <v>74863</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3364,43 +3364,38 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>106545</v>
+        <v>6440</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>441381</v>
+        <v>441352</v>
       </c>
       <c r="R28" t="n">
-        <v>6753451</v>
+        <v>6753455</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3459,7 +3454,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122567097</v>
+        <v>122567102</v>
       </c>
       <c r="B29" t="n">
         <v>78766</v>
@@ -3499,10 +3494,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>441320</v>
+        <v>441305</v>
       </c>
       <c r="R29" t="n">
-        <v>6753429</v>
+        <v>6753384</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3561,7 +3556,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122567104</v>
+        <v>122567095</v>
       </c>
       <c r="B30" t="n">
         <v>78766</v>
@@ -3601,10 +3596,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>441277</v>
+        <v>441406</v>
       </c>
       <c r="R30" t="n">
-        <v>6753396</v>
+        <v>6753439</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3663,10 +3658,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122567100</v>
+        <v>122567049</v>
       </c>
       <c r="B31" t="n">
-        <v>78766</v>
+        <v>74863</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3679,21 +3674,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3703,10 +3698,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>441332</v>
+        <v>441299</v>
       </c>
       <c r="R31" t="n">
-        <v>6753382</v>
+        <v>6753387</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3765,10 +3760,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122567125</v>
+        <v>122567067</v>
       </c>
       <c r="B32" t="n">
-        <v>78766</v>
+        <v>8441</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3777,38 +3772,43 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>441356</v>
+        <v>441231</v>
       </c>
       <c r="R32" t="n">
-        <v>6753361</v>
+        <v>6753537</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3867,10 +3867,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122567114</v>
+        <v>122567066</v>
       </c>
       <c r="B33" t="n">
-        <v>78766</v>
+        <v>8441</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3879,38 +3879,43 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>441206</v>
+        <v>441258</v>
       </c>
       <c r="R33" t="n">
-        <v>6753562</v>
+        <v>6753406</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3969,7 +3974,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122567119</v>
+        <v>122567112</v>
       </c>
       <c r="B34" t="n">
         <v>78766</v>
@@ -4009,10 +4014,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>441291</v>
+        <v>441217</v>
       </c>
       <c r="R34" t="n">
-        <v>6753289</v>
+        <v>6753556</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4071,10 +4076,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122567089</v>
+        <v>122567035</v>
       </c>
       <c r="B35" t="n">
-        <v>56688</v>
+        <v>79384</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4083,43 +4088,38 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>441283</v>
+        <v>441158</v>
       </c>
       <c r="R35" t="n">
-        <v>6753349</v>
+        <v>6753553</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4178,10 +4178,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122567048</v>
+        <v>122567137</v>
       </c>
       <c r="B36" t="n">
-        <v>74863</v>
+        <v>78766</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4194,21 +4194,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4218,10 +4218,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>441302</v>
+        <v>441348</v>
       </c>
       <c r="R36" t="n">
-        <v>6753380</v>
+        <v>6753444</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4280,10 +4280,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122567053</v>
+        <v>122567114</v>
       </c>
       <c r="B37" t="n">
-        <v>78800</v>
+        <v>78766</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4296,21 +4296,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4320,10 +4320,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>441420</v>
+        <v>441206</v>
       </c>
       <c r="R37" t="n">
-        <v>6753456</v>
+        <v>6753562</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4382,10 +4382,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122567131</v>
+        <v>122567041</v>
       </c>
       <c r="B38" t="n">
-        <v>78766</v>
+        <v>79384</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4398,21 +4398,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4422,10 +4422,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>441347</v>
+        <v>441357</v>
       </c>
       <c r="R38" t="n">
-        <v>6753407</v>
+        <v>6753361</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4484,10 +4484,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122567121</v>
+        <v>122567039</v>
       </c>
       <c r="B39" t="n">
-        <v>78766</v>
+        <v>79384</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4500,21 +4500,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4524,10 +4524,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>441306</v>
+        <v>441344</v>
       </c>
       <c r="R39" t="n">
-        <v>6753338</v>
+        <v>6753341</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4586,10 +4586,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122567139</v>
+        <v>122567043</v>
       </c>
       <c r="B40" t="n">
-        <v>78766</v>
+        <v>79384</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4602,21 +4602,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4626,10 +4626,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>441430</v>
+        <v>441348</v>
       </c>
       <c r="R40" t="n">
-        <v>6753445</v>
+        <v>6753422</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4688,10 +4688,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122567102</v>
+        <v>122567089</v>
       </c>
       <c r="B41" t="n">
-        <v>78766</v>
+        <v>56688</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4700,38 +4700,43 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>441305</v>
+        <v>441283</v>
       </c>
       <c r="R41" t="n">
-        <v>6753384</v>
+        <v>6753349</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4790,7 +4795,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122567133</v>
+        <v>122567122</v>
       </c>
       <c r="B42" t="n">
         <v>78766</v>
@@ -4830,10 +4835,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>441321</v>
+        <v>441315</v>
       </c>
       <c r="R42" t="n">
-        <v>6753447</v>
+        <v>6753342</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4892,10 +4897,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122567051</v>
+        <v>122567126</v>
       </c>
       <c r="B43" t="n">
-        <v>74863</v>
+        <v>78766</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4908,21 +4913,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4932,10 +4937,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>441352</v>
+        <v>441344</v>
       </c>
       <c r="R43" t="n">
-        <v>6753455</v>
+        <v>6753362</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4994,10 +4999,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122567066</v>
+        <v>122567139</v>
       </c>
       <c r="B44" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5006,43 +5011,38 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>441258</v>
+        <v>441430</v>
       </c>
       <c r="R44" t="n">
-        <v>6753406</v>
+        <v>6753445</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5101,7 +5101,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122567098</v>
+        <v>122567127</v>
       </c>
       <c r="B45" t="n">
         <v>78766</v>
@@ -5141,10 +5141,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>441329</v>
+        <v>441338</v>
       </c>
       <c r="R45" t="n">
-        <v>6753411</v>
+        <v>6753386</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5203,7 +5203,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122567138</v>
+        <v>122567135</v>
       </c>
       <c r="B46" t="n">
         <v>78766</v>
@@ -5243,10 +5243,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>441383</v>
+        <v>441322</v>
       </c>
       <c r="R46" t="n">
-        <v>6753450</v>
+        <v>6753459</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5305,10 +5305,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122567059</v>
+        <v>122567038</v>
       </c>
       <c r="B47" t="n">
-        <v>8441</v>
+        <v>79384</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5317,43 +5317,38 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>441302</v>
+        <v>441336</v>
       </c>
       <c r="R47" t="n">
-        <v>6753294</v>
+        <v>6753344</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5412,7 +5407,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122567120</v>
+        <v>122567118</v>
       </c>
       <c r="B48" t="n">
         <v>78766</v>
@@ -5452,7 +5447,7 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>441289</v>
+        <v>441277</v>
       </c>
       <c r="R48" t="n">
         <v>6753324</v>
@@ -5514,10 +5509,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122567081</v>
+        <v>122567134</v>
       </c>
       <c r="B49" t="n">
-        <v>78503</v>
+        <v>78766</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5530,21 +5525,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5554,10 +5549,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>441344</v>
+        <v>441320</v>
       </c>
       <c r="R49" t="n">
-        <v>6753341</v>
+        <v>6753453</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5616,10 +5611,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122567083</v>
+        <v>122567036</v>
       </c>
       <c r="B50" t="n">
-        <v>78503</v>
+        <v>79384</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5632,21 +5627,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5656,10 +5651,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>441348</v>
+        <v>441283</v>
       </c>
       <c r="R50" t="n">
-        <v>6753422</v>
+        <v>6753350</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5718,10 +5713,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122567109</v>
+        <v>122567075</v>
       </c>
       <c r="B51" t="n">
-        <v>78766</v>
+        <v>8441</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5730,38 +5725,43 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>441223</v>
+        <v>441291</v>
       </c>
       <c r="R51" t="n">
-        <v>6753536</v>
+        <v>6753289</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5820,10 +5820,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122567038</v>
+        <v>122567106</v>
       </c>
       <c r="B52" t="n">
-        <v>79384</v>
+        <v>78766</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5836,21 +5836,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5860,10 +5860,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>441336</v>
+        <v>441266</v>
       </c>
       <c r="R52" t="n">
-        <v>6753344</v>
+        <v>6753401</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5922,10 +5922,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122567036</v>
+        <v>122567116</v>
       </c>
       <c r="B53" t="n">
-        <v>79384</v>
+        <v>78766</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5938,21 +5938,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5962,10 +5962,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>441283</v>
+        <v>441199</v>
       </c>
       <c r="R53" t="n">
-        <v>6753350</v>
+        <v>6753562</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6024,10 +6024,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122567117</v>
+        <v>122567088</v>
       </c>
       <c r="B54" t="n">
-        <v>78766</v>
+        <v>56688</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6036,38 +6036,43 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>441193</v>
+        <v>441262</v>
       </c>
       <c r="R54" t="n">
-        <v>6753577</v>
+        <v>6753412</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6126,7 +6131,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122567067</v>
+        <v>122567074</v>
       </c>
       <c r="B55" t="n">
         <v>8441</v>
@@ -6171,10 +6176,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>441231</v>
+        <v>441284</v>
       </c>
       <c r="R55" t="n">
-        <v>6753537</v>
+        <v>6753286</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6233,10 +6238,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122567064</v>
+        <v>122567117</v>
       </c>
       <c r="B56" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6245,43 +6250,38 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>441389</v>
+        <v>441193</v>
       </c>
       <c r="R56" t="n">
-        <v>6753439</v>
+        <v>6753577</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6340,10 +6340,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122567095</v>
+        <v>122567070</v>
       </c>
       <c r="B57" t="n">
-        <v>78766</v>
+        <v>8441</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6352,38 +6352,43 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>441406</v>
+        <v>441158</v>
       </c>
       <c r="R57" t="n">
-        <v>6753439</v>
+        <v>6753533</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6442,10 +6447,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122567107</v>
+        <v>122567077</v>
       </c>
       <c r="B58" t="n">
-        <v>78766</v>
+        <v>8441</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6454,38 +6459,43 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>441262</v>
+        <v>441381</v>
       </c>
       <c r="R58" t="n">
-        <v>6753417</v>
+        <v>6753451</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6544,7 +6554,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122567127</v>
+        <v>122567113</v>
       </c>
       <c r="B59" t="n">
         <v>78766</v>
@@ -6584,10 +6594,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>441338</v>
+        <v>441207</v>
       </c>
       <c r="R59" t="n">
-        <v>6753386</v>
+        <v>6753568</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6646,10 +6656,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122567042</v>
+        <v>122567105</v>
       </c>
       <c r="B60" t="n">
-        <v>79384</v>
+        <v>78766</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6662,21 +6672,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6686,10 +6696,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>441336</v>
+        <v>441269</v>
       </c>
       <c r="R60" t="n">
-        <v>6753370</v>
+        <v>6753398</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6748,10 +6758,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122567122</v>
+        <v>122567056</v>
       </c>
       <c r="B61" t="n">
-        <v>78766</v>
+        <v>57494</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6764,34 +6774,39 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>441315</v>
+        <v>441305</v>
       </c>
       <c r="R61" t="n">
-        <v>6753342</v>
+        <v>6753366</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6850,10 +6865,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122567113</v>
+        <v>122567081</v>
       </c>
       <c r="B62" t="n">
-        <v>78766</v>
+        <v>78503</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6866,21 +6881,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6890,10 +6905,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>441207</v>
+        <v>441344</v>
       </c>
       <c r="R62" t="n">
-        <v>6753568</v>
+        <v>6753341</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6952,10 +6967,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122567039</v>
+        <v>122567132</v>
       </c>
       <c r="B63" t="n">
-        <v>79384</v>
+        <v>78766</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -6968,21 +6983,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6992,10 +7007,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>441344</v>
+        <v>441329</v>
       </c>
       <c r="R63" t="n">
-        <v>6753341</v>
+        <v>6753438</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7054,10 +7069,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122567046</v>
+        <v>122567123</v>
       </c>
       <c r="B64" t="n">
-        <v>74863</v>
+        <v>78766</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7070,21 +7085,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7094,10 +7109,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>441304</v>
+        <v>441334</v>
       </c>
       <c r="R64" t="n">
-        <v>6753366</v>
+        <v>6753341</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7156,10 +7171,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122567088</v>
+        <v>122567099</v>
       </c>
       <c r="B65" t="n">
-        <v>56688</v>
+        <v>78766</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7168,43 +7183,38 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>441262</v>
+        <v>441323</v>
       </c>
       <c r="R65" t="n">
-        <v>6753412</v>
+        <v>6753416</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7263,10 +7273,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122567074</v>
+        <v>122567046</v>
       </c>
       <c r="B66" t="n">
-        <v>8441</v>
+        <v>74863</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7275,43 +7285,38 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>106545</v>
+        <v>6440</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>441284</v>
+        <v>441304</v>
       </c>
       <c r="R66" t="n">
-        <v>6753286</v>
+        <v>6753366</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7370,10 +7375,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122567072</v>
+        <v>122567048</v>
       </c>
       <c r="B67" t="n">
-        <v>8441</v>
+        <v>74863</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7382,43 +7387,38 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>106545</v>
+        <v>6440</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>441255</v>
+        <v>441302</v>
       </c>
       <c r="R67" t="n">
-        <v>6753382</v>
+        <v>6753380</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7477,7 +7477,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122567101</v>
+        <v>122567109</v>
       </c>
       <c r="B68" t="n">
         <v>78766</v>
@@ -7517,10 +7517,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>441301</v>
+        <v>441223</v>
       </c>
       <c r="R68" t="n">
-        <v>6753376</v>
+        <v>6753536</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7579,7 +7579,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122567099</v>
+        <v>122567121</v>
       </c>
       <c r="B69" t="n">
         <v>78766</v>
@@ -7619,10 +7619,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>441323</v>
+        <v>441306</v>
       </c>
       <c r="R69" t="n">
-        <v>6753416</v>
+        <v>6753338</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7681,10 +7681,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122567041</v>
+        <v>122567125</v>
       </c>
       <c r="B70" t="n">
-        <v>79384</v>
+        <v>78766</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7697,21 +7697,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>441357</v>
+        <v>441356</v>
       </c>
       <c r="R70" t="n">
         <v>6753361</v>
@@ -7783,10 +7783,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122567044</v>
+        <v>122567083</v>
       </c>
       <c r="B71" t="n">
-        <v>79384</v>
+        <v>78503</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7799,21 +7799,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7826,7 +7826,7 @@
         <v>441348</v>
       </c>
       <c r="R71" t="n">
-        <v>6753445</v>
+        <v>6753422</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7885,10 +7885,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122567043</v>
+        <v>122567136</v>
       </c>
       <c r="B72" t="n">
-        <v>79384</v>
+        <v>78766</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -7901,21 +7901,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7925,10 +7925,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>441348</v>
+        <v>441345</v>
       </c>
       <c r="R72" t="n">
-        <v>6753422</v>
+        <v>6753451</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7987,10 +7987,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>122567073</v>
+        <v>122567108</v>
       </c>
       <c r="B73" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -7999,43 +7999,38 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>441269</v>
+        <v>441273</v>
       </c>
       <c r="R73" t="n">
-        <v>6753365</v>
+        <v>6753425</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8094,10 +8089,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>122567158</v>
+        <v>122567073</v>
       </c>
       <c r="B74" t="n">
-        <v>78411</v>
+        <v>8441</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8106,38 +8101,43 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>353</v>
+        <v>106545</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>441248</v>
+        <v>441269</v>
       </c>
       <c r="R74" t="n">
-        <v>6753389</v>
+        <v>6753365</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8196,10 +8196,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>122567136</v>
+        <v>122567044</v>
       </c>
       <c r="B75" t="n">
-        <v>78766</v>
+        <v>79384</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8212,21 +8212,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8236,10 +8236,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>441345</v>
+        <v>441348</v>
       </c>
       <c r="R75" t="n">
-        <v>6753451</v>
+        <v>6753445</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8298,10 +8298,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>122567112</v>
+        <v>122567034</v>
       </c>
       <c r="B76" t="n">
-        <v>78766</v>
+        <v>79384</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8314,21 +8314,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8338,10 +8338,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>441217</v>
+        <v>441152</v>
       </c>
       <c r="R76" t="n">
-        <v>6753556</v>
+        <v>6753562</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8400,10 +8400,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>122567116</v>
+        <v>122567042</v>
       </c>
       <c r="B77" t="n">
-        <v>78766</v>
+        <v>79384</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8416,21 +8416,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8440,10 +8440,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>441199</v>
+        <v>441336</v>
       </c>
       <c r="R77" t="n">
-        <v>6753562</v>
+        <v>6753370</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8502,7 +8502,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>122567070</v>
+        <v>122567064</v>
       </c>
       <c r="B78" t="n">
         <v>8441</v>
@@ -8547,10 +8547,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>441158</v>
+        <v>441389</v>
       </c>
       <c r="R78" t="n">
-        <v>6753533</v>
+        <v>6753439</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>

--- a/artfynd/A 61943-2024 artfynd.xlsx
+++ b/artfynd/A 61943-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122567071</v>
+        <v>122567126</v>
       </c>
       <c r="B2" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,43 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>441172</v>
+        <v>441344</v>
       </c>
       <c r="R2" t="n">
-        <v>6753515</v>
+        <v>6753362</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122567068</v>
+        <v>122567105</v>
       </c>
       <c r="B3" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,43 +789,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>441150</v>
+        <v>441269</v>
       </c>
       <c r="R3" t="n">
-        <v>6753623</v>
+        <v>6753398</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122567119</v>
+        <v>122567109</v>
       </c>
       <c r="B4" t="n">
         <v>78766</v>
@@ -929,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>441291</v>
+        <v>441223</v>
       </c>
       <c r="R4" t="n">
-        <v>6753289</v>
+        <v>6753536</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -991,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122567107</v>
+        <v>122567122</v>
       </c>
       <c r="B5" t="n">
         <v>78766</v>
@@ -1031,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>441262</v>
+        <v>441315</v>
       </c>
       <c r="R5" t="n">
-        <v>6753417</v>
+        <v>6753342</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1093,7 +1083,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122567100</v>
+        <v>122567132</v>
       </c>
       <c r="B6" t="n">
         <v>78766</v>
@@ -1133,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>441332</v>
+        <v>441329</v>
       </c>
       <c r="R6" t="n">
-        <v>6753382</v>
+        <v>6753438</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1195,7 +1185,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122567096</v>
+        <v>122567099</v>
       </c>
       <c r="B7" t="n">
         <v>78766</v>
@@ -1235,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>441319</v>
+        <v>441323</v>
       </c>
       <c r="R7" t="n">
-        <v>6753442</v>
+        <v>6753416</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1297,7 +1287,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122567133</v>
+        <v>122567120</v>
       </c>
       <c r="B8" t="n">
         <v>78766</v>
@@ -1337,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>441321</v>
+        <v>441289</v>
       </c>
       <c r="R8" t="n">
-        <v>6753447</v>
+        <v>6753324</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1399,7 +1389,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122567138</v>
+        <v>122567135</v>
       </c>
       <c r="B9" t="n">
         <v>78766</v>
@@ -1439,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>441383</v>
+        <v>441322</v>
       </c>
       <c r="R9" t="n">
-        <v>6753450</v>
+        <v>6753459</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1603,7 +1593,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122567069</v>
+        <v>122567072</v>
       </c>
       <c r="B11" t="n">
         <v>8441</v>
@@ -1648,10 +1638,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>441119</v>
+        <v>441255</v>
       </c>
       <c r="R11" t="n">
-        <v>6753677</v>
+        <v>6753382</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1710,10 +1700,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122567131</v>
+        <v>122567041</v>
       </c>
       <c r="B12" t="n">
-        <v>78766</v>
+        <v>79384</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1726,21 +1716,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1750,10 +1740,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>441347</v>
+        <v>441357</v>
       </c>
       <c r="R12" t="n">
-        <v>6753407</v>
+        <v>6753361</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1812,10 +1802,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122567047</v>
+        <v>122567118</v>
       </c>
       <c r="B13" t="n">
-        <v>74863</v>
+        <v>78766</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1828,21 +1818,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1852,10 +1842,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>441304</v>
+        <v>441277</v>
       </c>
       <c r="R13" t="n">
-        <v>6753377</v>
+        <v>6753324</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1914,7 +1904,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122567103</v>
+        <v>122567106</v>
       </c>
       <c r="B14" t="n">
         <v>78766</v>
@@ -1954,10 +1944,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>441287</v>
+        <v>441266</v>
       </c>
       <c r="R14" t="n">
-        <v>6753389</v>
+        <v>6753401</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2016,10 +2006,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122567098</v>
+        <v>122567039</v>
       </c>
       <c r="B15" t="n">
-        <v>78766</v>
+        <v>79384</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2032,21 +2022,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2056,10 +2046,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>441329</v>
+        <v>441344</v>
       </c>
       <c r="R15" t="n">
-        <v>6753411</v>
+        <v>6753341</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2118,10 +2108,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122567104</v>
+        <v>122567043</v>
       </c>
       <c r="B16" t="n">
-        <v>78766</v>
+        <v>79384</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2134,21 +2124,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2158,10 +2148,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>441277</v>
+        <v>441348</v>
       </c>
       <c r="R16" t="n">
-        <v>6753396</v>
+        <v>6753422</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2220,10 +2210,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122567101</v>
+        <v>122567068</v>
       </c>
       <c r="B17" t="n">
-        <v>78766</v>
+        <v>8441</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2232,38 +2222,43 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>441301</v>
+        <v>441150</v>
       </c>
       <c r="R17" t="n">
-        <v>6753376</v>
+        <v>6753623</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2322,10 +2317,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122567128</v>
+        <v>122567158</v>
       </c>
       <c r="B18" t="n">
-        <v>78766</v>
+        <v>78411</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2338,21 +2333,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2362,10 +2357,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>441350</v>
+        <v>441248</v>
       </c>
       <c r="R18" t="n">
-        <v>6753388</v>
+        <v>6753389</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2424,10 +2419,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122567033</v>
+        <v>122567111</v>
       </c>
       <c r="B19" t="n">
-        <v>79384</v>
+        <v>78766</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2440,21 +2435,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2464,10 +2459,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>441194</v>
+        <v>441221</v>
       </c>
       <c r="R19" t="n">
-        <v>6753576</v>
+        <v>6753553</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2526,10 +2521,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122567053</v>
+        <v>122567104</v>
       </c>
       <c r="B20" t="n">
-        <v>78800</v>
+        <v>78766</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2542,21 +2537,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2566,10 +2561,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>441420</v>
+        <v>441277</v>
       </c>
       <c r="R20" t="n">
-        <v>6753456</v>
+        <v>6753396</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2628,10 +2623,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122567091</v>
+        <v>122567083</v>
       </c>
       <c r="B21" t="n">
-        <v>78766</v>
+        <v>78503</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2644,21 +2639,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2668,10 +2663,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>441420</v>
+        <v>441348</v>
       </c>
       <c r="R21" t="n">
-        <v>6753456</v>
+        <v>6753422</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2730,10 +2725,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122567120</v>
+        <v>122567049</v>
       </c>
       <c r="B22" t="n">
-        <v>78766</v>
+        <v>74863</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2746,21 +2741,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2770,10 +2765,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>441289</v>
+        <v>441299</v>
       </c>
       <c r="R22" t="n">
-        <v>6753324</v>
+        <v>6753387</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2832,10 +2827,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122567111</v>
+        <v>122567034</v>
       </c>
       <c r="B23" t="n">
-        <v>78766</v>
+        <v>79384</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2848,21 +2843,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2872,10 +2867,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>441221</v>
+        <v>441152</v>
       </c>
       <c r="R23" t="n">
-        <v>6753553</v>
+        <v>6753562</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2934,10 +2929,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122567097</v>
+        <v>122567033</v>
       </c>
       <c r="B24" t="n">
-        <v>78766</v>
+        <v>79384</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2950,21 +2945,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2974,10 +2969,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>441320</v>
+        <v>441194</v>
       </c>
       <c r="R24" t="n">
-        <v>6753429</v>
+        <v>6753576</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3036,10 +3031,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122567072</v>
+        <v>122567095</v>
       </c>
       <c r="B25" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3048,43 +3043,38 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>441255</v>
+        <v>441406</v>
       </c>
       <c r="R25" t="n">
-        <v>6753382</v>
+        <v>6753439</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3143,10 +3133,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122567158</v>
+        <v>122567035</v>
       </c>
       <c r="B26" t="n">
-        <v>78411</v>
+        <v>79384</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3159,21 +3149,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3183,10 +3173,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>441248</v>
+        <v>441158</v>
       </c>
       <c r="R26" t="n">
-        <v>6753389</v>
+        <v>6753553</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3245,10 +3235,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122567059</v>
+        <v>122567044</v>
       </c>
       <c r="B27" t="n">
-        <v>8441</v>
+        <v>79384</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3257,43 +3247,38 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>441302</v>
+        <v>441348</v>
       </c>
       <c r="R27" t="n">
-        <v>6753294</v>
+        <v>6753445</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3352,7 +3337,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122567051</v>
+        <v>122567048</v>
       </c>
       <c r="B28" t="n">
         <v>74863</v>
@@ -3392,10 +3377,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>441352</v>
+        <v>441302</v>
       </c>
       <c r="R28" t="n">
-        <v>6753455</v>
+        <v>6753380</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3454,10 +3439,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122567102</v>
+        <v>122567070</v>
       </c>
       <c r="B29" t="n">
-        <v>78766</v>
+        <v>8441</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3466,38 +3451,43 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>441305</v>
+        <v>441158</v>
       </c>
       <c r="R29" t="n">
-        <v>6753384</v>
+        <v>6753533</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3556,7 +3546,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122567095</v>
+        <v>122567119</v>
       </c>
       <c r="B30" t="n">
         <v>78766</v>
@@ -3596,10 +3586,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>441406</v>
+        <v>441291</v>
       </c>
       <c r="R30" t="n">
-        <v>6753439</v>
+        <v>6753289</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3658,10 +3648,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122567049</v>
+        <v>122567136</v>
       </c>
       <c r="B31" t="n">
-        <v>74863</v>
+        <v>78766</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3674,21 +3664,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3698,10 +3688,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>441299</v>
+        <v>441345</v>
       </c>
       <c r="R31" t="n">
-        <v>6753387</v>
+        <v>6753451</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3760,10 +3750,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122567067</v>
+        <v>122567127</v>
       </c>
       <c r="B32" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3772,43 +3762,38 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>441231</v>
+        <v>441338</v>
       </c>
       <c r="R32" t="n">
-        <v>6753537</v>
+        <v>6753386</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3867,10 +3852,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122567066</v>
+        <v>122567098</v>
       </c>
       <c r="B33" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3879,43 +3864,38 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>441258</v>
+        <v>441329</v>
       </c>
       <c r="R33" t="n">
-        <v>6753406</v>
+        <v>6753411</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3974,10 +3954,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122567112</v>
+        <v>122567038</v>
       </c>
       <c r="B34" t="n">
-        <v>78766</v>
+        <v>79384</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3990,21 +3970,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4014,10 +3994,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>441217</v>
+        <v>441336</v>
       </c>
       <c r="R34" t="n">
-        <v>6753556</v>
+        <v>6753344</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4076,10 +4056,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122567035</v>
+        <v>122567064</v>
       </c>
       <c r="B35" t="n">
-        <v>79384</v>
+        <v>8441</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4088,38 +4068,43 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>441158</v>
+        <v>441389</v>
       </c>
       <c r="R35" t="n">
-        <v>6753553</v>
+        <v>6753439</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4178,10 +4163,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122567137</v>
+        <v>122567059</v>
       </c>
       <c r="B36" t="n">
-        <v>78766</v>
+        <v>8441</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4190,38 +4175,43 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>441348</v>
+        <v>441302</v>
       </c>
       <c r="R36" t="n">
-        <v>6753444</v>
+        <v>6753294</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4280,10 +4270,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122567114</v>
+        <v>122567075</v>
       </c>
       <c r="B37" t="n">
-        <v>78766</v>
+        <v>8441</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4292,38 +4282,43 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>441206</v>
+        <v>441291</v>
       </c>
       <c r="R37" t="n">
-        <v>6753562</v>
+        <v>6753289</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4382,10 +4377,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122567041</v>
+        <v>122567117</v>
       </c>
       <c r="B38" t="n">
-        <v>79384</v>
+        <v>78766</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4398,21 +4393,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4422,10 +4417,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>441357</v>
+        <v>441193</v>
       </c>
       <c r="R38" t="n">
-        <v>6753361</v>
+        <v>6753577</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4484,10 +4479,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122567039</v>
+        <v>122567088</v>
       </c>
       <c r="B39" t="n">
-        <v>79384</v>
+        <v>56688</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4496,38 +4491,43 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>441344</v>
+        <v>441262</v>
       </c>
       <c r="R39" t="n">
-        <v>6753341</v>
+        <v>6753412</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4586,10 +4586,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122567043</v>
+        <v>122567046</v>
       </c>
       <c r="B40" t="n">
-        <v>79384</v>
+        <v>74863</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4602,21 +4602,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6453</v>
+        <v>6440</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4626,10 +4626,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>441348</v>
+        <v>441304</v>
       </c>
       <c r="R40" t="n">
-        <v>6753422</v>
+        <v>6753366</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4688,10 +4688,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122567089</v>
+        <v>122567077</v>
       </c>
       <c r="B41" t="n">
-        <v>56688</v>
+        <v>8441</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4704,27 +4704,27 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100138</v>
+        <v>106545</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -4733,10 +4733,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>441283</v>
+        <v>441381</v>
       </c>
       <c r="R41" t="n">
-        <v>6753349</v>
+        <v>6753451</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4795,10 +4795,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122567122</v>
+        <v>122567073</v>
       </c>
       <c r="B42" t="n">
-        <v>78766</v>
+        <v>8441</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4807,38 +4807,43 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>441315</v>
+        <v>441269</v>
       </c>
       <c r="R42" t="n">
-        <v>6753342</v>
+        <v>6753365</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4897,10 +4902,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122567126</v>
+        <v>122567071</v>
       </c>
       <c r="B43" t="n">
-        <v>78766</v>
+        <v>8441</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4909,38 +4914,43 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>441344</v>
+        <v>441172</v>
       </c>
       <c r="R43" t="n">
-        <v>6753362</v>
+        <v>6753515</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4999,7 +5009,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122567139</v>
+        <v>122567096</v>
       </c>
       <c r="B44" t="n">
         <v>78766</v>
@@ -5039,10 +5049,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>441430</v>
+        <v>441319</v>
       </c>
       <c r="R44" t="n">
-        <v>6753445</v>
+        <v>6753442</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5101,10 +5111,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122567127</v>
+        <v>122567051</v>
       </c>
       <c r="B45" t="n">
-        <v>78766</v>
+        <v>74863</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5117,21 +5127,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5141,10 +5151,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>441338</v>
+        <v>441352</v>
       </c>
       <c r="R45" t="n">
-        <v>6753386</v>
+        <v>6753455</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5203,7 +5213,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122567135</v>
+        <v>122567091</v>
       </c>
       <c r="B46" t="n">
         <v>78766</v>
@@ -5243,10 +5253,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>441322</v>
+        <v>441420</v>
       </c>
       <c r="R46" t="n">
-        <v>6753459</v>
+        <v>6753456</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5305,10 +5315,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122567038</v>
+        <v>122567137</v>
       </c>
       <c r="B47" t="n">
-        <v>79384</v>
+        <v>78766</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5321,21 +5331,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5345,10 +5355,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>441336</v>
+        <v>441348</v>
       </c>
       <c r="R47" t="n">
-        <v>6753344</v>
+        <v>6753444</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5407,7 +5417,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122567118</v>
+        <v>122567123</v>
       </c>
       <c r="B48" t="n">
         <v>78766</v>
@@ -5447,10 +5457,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>441277</v>
+        <v>441334</v>
       </c>
       <c r="R48" t="n">
-        <v>6753324</v>
+        <v>6753341</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5509,7 +5519,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122567134</v>
+        <v>122567101</v>
       </c>
       <c r="B49" t="n">
         <v>78766</v>
@@ -5549,10 +5559,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>441320</v>
+        <v>441301</v>
       </c>
       <c r="R49" t="n">
-        <v>6753453</v>
+        <v>6753376</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5611,10 +5621,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122567036</v>
+        <v>122567108</v>
       </c>
       <c r="B50" t="n">
-        <v>79384</v>
+        <v>78766</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5627,21 +5637,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5651,10 +5661,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>441283</v>
+        <v>441273</v>
       </c>
       <c r="R50" t="n">
-        <v>6753350</v>
+        <v>6753425</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5713,10 +5723,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122567075</v>
+        <v>122567056</v>
       </c>
       <c r="B51" t="n">
-        <v>8441</v>
+        <v>57494</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5725,31 +5735,31 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="M51" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -5758,10 +5768,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>441291</v>
+        <v>441305</v>
       </c>
       <c r="R51" t="n">
-        <v>6753289</v>
+        <v>6753366</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5820,7 +5830,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122567106</v>
+        <v>122567102</v>
       </c>
       <c r="B52" t="n">
         <v>78766</v>
@@ -5860,10 +5870,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>441266</v>
+        <v>441305</v>
       </c>
       <c r="R52" t="n">
-        <v>6753401</v>
+        <v>6753384</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5922,7 +5932,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122567116</v>
+        <v>122567100</v>
       </c>
       <c r="B53" t="n">
         <v>78766</v>
@@ -5962,10 +5972,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>441199</v>
+        <v>441332</v>
       </c>
       <c r="R53" t="n">
-        <v>6753562</v>
+        <v>6753382</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6024,10 +6034,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122567088</v>
+        <v>122567125</v>
       </c>
       <c r="B54" t="n">
-        <v>56688</v>
+        <v>78766</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6036,43 +6046,38 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>441262</v>
+        <v>441356</v>
       </c>
       <c r="R54" t="n">
-        <v>6753412</v>
+        <v>6753361</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6131,10 +6136,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122567074</v>
+        <v>122567089</v>
       </c>
       <c r="B55" t="n">
-        <v>8441</v>
+        <v>56688</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6147,27 +6152,27 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="M55" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
@@ -6176,10 +6181,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>441284</v>
+        <v>441283</v>
       </c>
       <c r="R55" t="n">
-        <v>6753286</v>
+        <v>6753349</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6238,7 +6243,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122567117</v>
+        <v>122567139</v>
       </c>
       <c r="B56" t="n">
         <v>78766</v>
@@ -6278,10 +6283,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>441193</v>
+        <v>441430</v>
       </c>
       <c r="R56" t="n">
-        <v>6753577</v>
+        <v>6753445</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6340,10 +6345,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122567070</v>
+        <v>122567121</v>
       </c>
       <c r="B57" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6352,43 +6357,38 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>441158</v>
+        <v>441306</v>
       </c>
       <c r="R57" t="n">
-        <v>6753533</v>
+        <v>6753338</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6447,10 +6447,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122567077</v>
+        <v>122567036</v>
       </c>
       <c r="B58" t="n">
-        <v>8441</v>
+        <v>79384</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6459,43 +6459,38 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>441381</v>
+        <v>441283</v>
       </c>
       <c r="R58" t="n">
-        <v>6753451</v>
+        <v>6753350</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6554,10 +6549,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122567113</v>
+        <v>122567047</v>
       </c>
       <c r="B59" t="n">
-        <v>78766</v>
+        <v>74863</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6570,21 +6565,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6594,10 +6589,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>441207</v>
+        <v>441304</v>
       </c>
       <c r="R59" t="n">
-        <v>6753568</v>
+        <v>6753377</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6656,10 +6651,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122567105</v>
+        <v>122567067</v>
       </c>
       <c r="B60" t="n">
-        <v>78766</v>
+        <v>8441</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6668,38 +6663,43 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>441269</v>
+        <v>441231</v>
       </c>
       <c r="R60" t="n">
-        <v>6753398</v>
+        <v>6753537</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6758,10 +6758,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122567056</v>
+        <v>122567116</v>
       </c>
       <c r="B61" t="n">
-        <v>57494</v>
+        <v>78766</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6774,39 +6774,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>441305</v>
+        <v>441199</v>
       </c>
       <c r="R61" t="n">
-        <v>6753366</v>
+        <v>6753562</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6865,10 +6860,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122567081</v>
+        <v>122567097</v>
       </c>
       <c r="B62" t="n">
-        <v>78503</v>
+        <v>78766</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6881,21 +6876,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6905,10 +6900,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>441344</v>
+        <v>441320</v>
       </c>
       <c r="R62" t="n">
-        <v>6753341</v>
+        <v>6753429</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6967,7 +6962,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122567132</v>
+        <v>122567134</v>
       </c>
       <c r="B63" t="n">
         <v>78766</v>
@@ -7007,10 +7002,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>441329</v>
+        <v>441320</v>
       </c>
       <c r="R63" t="n">
-        <v>6753438</v>
+        <v>6753453</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7069,10 +7064,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122567123</v>
+        <v>122567069</v>
       </c>
       <c r="B64" t="n">
-        <v>78766</v>
+        <v>8441</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7081,38 +7076,43 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>441334</v>
+        <v>441119</v>
       </c>
       <c r="R64" t="n">
-        <v>6753341</v>
+        <v>6753677</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7171,10 +7171,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122567099</v>
+        <v>122567066</v>
       </c>
       <c r="B65" t="n">
-        <v>78766</v>
+        <v>8441</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7183,38 +7183,43 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>441323</v>
+        <v>441258</v>
       </c>
       <c r="R65" t="n">
-        <v>6753416</v>
+        <v>6753406</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7273,10 +7278,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122567046</v>
+        <v>122567053</v>
       </c>
       <c r="B66" t="n">
-        <v>74863</v>
+        <v>78800</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7289,21 +7294,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6440</v>
+        <v>185</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7313,10 +7318,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>441304</v>
+        <v>441420</v>
       </c>
       <c r="R66" t="n">
-        <v>6753366</v>
+        <v>6753456</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7375,10 +7380,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122567048</v>
+        <v>122567042</v>
       </c>
       <c r="B67" t="n">
-        <v>74863</v>
+        <v>79384</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7391,21 +7396,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6440</v>
+        <v>6453</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7415,10 +7420,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>441302</v>
+        <v>441336</v>
       </c>
       <c r="R67" t="n">
-        <v>6753380</v>
+        <v>6753370</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7477,10 +7482,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122567109</v>
+        <v>122567081</v>
       </c>
       <c r="B68" t="n">
-        <v>78766</v>
+        <v>78503</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7493,21 +7498,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7517,10 +7522,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>441223</v>
+        <v>441344</v>
       </c>
       <c r="R68" t="n">
-        <v>6753536</v>
+        <v>6753341</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7579,7 +7584,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122567121</v>
+        <v>122567103</v>
       </c>
       <c r="B69" t="n">
         <v>78766</v>
@@ -7619,10 +7624,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>441306</v>
+        <v>441287</v>
       </c>
       <c r="R69" t="n">
-        <v>6753338</v>
+        <v>6753389</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7681,7 +7686,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122567125</v>
+        <v>122567133</v>
       </c>
       <c r="B70" t="n">
         <v>78766</v>
@@ -7721,10 +7726,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>441356</v>
+        <v>441321</v>
       </c>
       <c r="R70" t="n">
-        <v>6753361</v>
+        <v>6753447</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7783,10 +7788,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122567083</v>
+        <v>122567113</v>
       </c>
       <c r="B71" t="n">
-        <v>78503</v>
+        <v>78766</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7799,21 +7804,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7823,10 +7828,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>441348</v>
+        <v>441207</v>
       </c>
       <c r="R71" t="n">
-        <v>6753422</v>
+        <v>6753568</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7885,7 +7890,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122567136</v>
+        <v>122567131</v>
       </c>
       <c r="B72" t="n">
         <v>78766</v>
@@ -7925,10 +7930,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>441345</v>
+        <v>441347</v>
       </c>
       <c r="R72" t="n">
-        <v>6753451</v>
+        <v>6753407</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7987,7 +7992,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>122567108</v>
+        <v>122567112</v>
       </c>
       <c r="B73" t="n">
         <v>78766</v>
@@ -8027,10 +8032,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>441273</v>
+        <v>441217</v>
       </c>
       <c r="R73" t="n">
-        <v>6753425</v>
+        <v>6753556</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8089,10 +8094,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>122567073</v>
+        <v>122567114</v>
       </c>
       <c r="B74" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8101,43 +8106,38 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>441269</v>
+        <v>441206</v>
       </c>
       <c r="R74" t="n">
-        <v>6753365</v>
+        <v>6753562</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8196,10 +8196,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>122567044</v>
+        <v>122567138</v>
       </c>
       <c r="B75" t="n">
-        <v>79384</v>
+        <v>78766</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8212,21 +8212,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8236,10 +8236,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>441348</v>
+        <v>441383</v>
       </c>
       <c r="R75" t="n">
-        <v>6753445</v>
+        <v>6753450</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8298,10 +8298,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>122567034</v>
+        <v>122567128</v>
       </c>
       <c r="B76" t="n">
-        <v>79384</v>
+        <v>78766</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8314,21 +8314,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8338,10 +8338,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>441152</v>
+        <v>441350</v>
       </c>
       <c r="R76" t="n">
-        <v>6753562</v>
+        <v>6753388</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8400,10 +8400,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>122567042</v>
+        <v>122567107</v>
       </c>
       <c r="B77" t="n">
-        <v>79384</v>
+        <v>78766</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8416,21 +8416,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8440,10 +8440,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>441336</v>
+        <v>441262</v>
       </c>
       <c r="R77" t="n">
-        <v>6753370</v>
+        <v>6753417</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8502,7 +8502,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>122567064</v>
+        <v>122567074</v>
       </c>
       <c r="B78" t="n">
         <v>8441</v>
@@ -8547,10 +8547,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>441389</v>
+        <v>441284</v>
       </c>
       <c r="R78" t="n">
-        <v>6753439</v>
+        <v>6753286</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>

--- a/artfynd/A 61943-2024 artfynd.xlsx
+++ b/artfynd/A 61943-2024 artfynd.xlsx
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122567050</v>
+        <v>122567072</v>
       </c>
       <c r="B10" t="n">
-        <v>74863</v>
+        <v>8441</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1503,38 +1503,43 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6440</v>
+        <v>106545</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>441314</v>
+        <v>441255</v>
       </c>
       <c r="R10" t="n">
-        <v>6753342</v>
+        <v>6753382</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,10 +1598,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122567072</v>
+        <v>122567050</v>
       </c>
       <c r="B11" t="n">
-        <v>8441</v>
+        <v>74863</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1605,43 +1610,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>106545</v>
+        <v>6440</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>441255</v>
+        <v>441314</v>
       </c>
       <c r="R11" t="n">
-        <v>6753382</v>
+        <v>6753342</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -2210,10 +2210,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122567068</v>
+        <v>122567083</v>
       </c>
       <c r="B17" t="n">
-        <v>8441</v>
+        <v>78503</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2222,43 +2222,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>441150</v>
+        <v>441348</v>
       </c>
       <c r="R17" t="n">
-        <v>6753623</v>
+        <v>6753422</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2623,10 +2618,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122567083</v>
+        <v>122567068</v>
       </c>
       <c r="B21" t="n">
-        <v>78503</v>
+        <v>8441</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2635,38 +2630,43 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>441348</v>
+        <v>441150</v>
       </c>
       <c r="R21" t="n">
-        <v>6753422</v>
+        <v>6753623</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2725,10 +2725,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122567049</v>
+        <v>122567095</v>
       </c>
       <c r="B22" t="n">
-        <v>74863</v>
+        <v>78766</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2741,21 +2741,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2765,10 +2765,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>441299</v>
+        <v>441406</v>
       </c>
       <c r="R22" t="n">
-        <v>6753387</v>
+        <v>6753439</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2827,10 +2827,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122567034</v>
+        <v>122567049</v>
       </c>
       <c r="B23" t="n">
-        <v>79384</v>
+        <v>74863</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2843,21 +2843,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6453</v>
+        <v>6440</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2867,10 +2867,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>441152</v>
+        <v>441299</v>
       </c>
       <c r="R23" t="n">
-        <v>6753562</v>
+        <v>6753387</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2929,7 +2929,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122567033</v>
+        <v>122567034</v>
       </c>
       <c r="B24" t="n">
         <v>79384</v>
@@ -2969,10 +2969,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>441194</v>
+        <v>441152</v>
       </c>
       <c r="R24" t="n">
-        <v>6753576</v>
+        <v>6753562</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3031,10 +3031,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122567095</v>
+        <v>122567033</v>
       </c>
       <c r="B25" t="n">
-        <v>78766</v>
+        <v>79384</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3047,21 +3047,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3071,10 +3071,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>441406</v>
+        <v>441194</v>
       </c>
       <c r="R25" t="n">
-        <v>6753439</v>
+        <v>6753576</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3133,10 +3133,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122567035</v>
+        <v>122567070</v>
       </c>
       <c r="B26" t="n">
-        <v>79384</v>
+        <v>8441</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3145,28 +3145,33 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
@@ -3176,7 +3181,7 @@
         <v>441158</v>
       </c>
       <c r="R26" t="n">
-        <v>6753553</v>
+        <v>6753533</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3235,10 +3240,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122567044</v>
+        <v>122567119</v>
       </c>
       <c r="B27" t="n">
-        <v>79384</v>
+        <v>78766</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3251,21 +3256,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3275,10 +3280,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>441348</v>
+        <v>441291</v>
       </c>
       <c r="R27" t="n">
-        <v>6753445</v>
+        <v>6753289</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3337,10 +3342,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122567048</v>
+        <v>122567136</v>
       </c>
       <c r="B28" t="n">
-        <v>74863</v>
+        <v>78766</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3353,21 +3358,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3377,10 +3382,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>441302</v>
+        <v>441345</v>
       </c>
       <c r="R28" t="n">
-        <v>6753380</v>
+        <v>6753451</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3439,10 +3444,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122567070</v>
+        <v>122567127</v>
       </c>
       <c r="B29" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3451,43 +3456,38 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>441158</v>
+        <v>441338</v>
       </c>
       <c r="R29" t="n">
-        <v>6753533</v>
+        <v>6753386</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3546,10 +3546,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122567119</v>
+        <v>122567035</v>
       </c>
       <c r="B30" t="n">
-        <v>78766</v>
+        <v>79384</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3562,21 +3562,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3586,10 +3586,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>441291</v>
+        <v>441158</v>
       </c>
       <c r="R30" t="n">
-        <v>6753289</v>
+        <v>6753553</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3648,10 +3648,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122567136</v>
+        <v>122567044</v>
       </c>
       <c r="B31" t="n">
-        <v>78766</v>
+        <v>79384</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3664,21 +3664,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3688,10 +3688,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>441345</v>
+        <v>441348</v>
       </c>
       <c r="R31" t="n">
-        <v>6753451</v>
+        <v>6753445</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3750,10 +3750,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122567127</v>
+        <v>122567048</v>
       </c>
       <c r="B32" t="n">
-        <v>78766</v>
+        <v>74863</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3766,21 +3766,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3790,10 +3790,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>441338</v>
+        <v>441302</v>
       </c>
       <c r="R32" t="n">
-        <v>6753386</v>
+        <v>6753380</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4795,10 +4795,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122567073</v>
+        <v>122567096</v>
       </c>
       <c r="B42" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4807,43 +4807,38 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>441269</v>
+        <v>441319</v>
       </c>
       <c r="R42" t="n">
-        <v>6753365</v>
+        <v>6753442</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4902,10 +4897,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122567071</v>
+        <v>122567051</v>
       </c>
       <c r="B43" t="n">
-        <v>8441</v>
+        <v>74863</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4914,43 +4909,38 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>106545</v>
+        <v>6440</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>441172</v>
+        <v>441352</v>
       </c>
       <c r="R43" t="n">
-        <v>6753515</v>
+        <v>6753455</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5009,10 +4999,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122567096</v>
+        <v>122567073</v>
       </c>
       <c r="B44" t="n">
-        <v>78766</v>
+        <v>8441</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5021,38 +5011,43 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>441319</v>
+        <v>441269</v>
       </c>
       <c r="R44" t="n">
-        <v>6753442</v>
+        <v>6753365</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5111,10 +5106,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122567051</v>
+        <v>122567071</v>
       </c>
       <c r="B45" t="n">
-        <v>74863</v>
+        <v>8441</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5123,38 +5118,43 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6440</v>
+        <v>106545</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>441352</v>
+        <v>441172</v>
       </c>
       <c r="R45" t="n">
-        <v>6753455</v>
+        <v>6753515</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5830,7 +5830,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122567102</v>
+        <v>122567125</v>
       </c>
       <c r="B52" t="n">
         <v>78766</v>
@@ -5870,10 +5870,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>441305</v>
+        <v>441356</v>
       </c>
       <c r="R52" t="n">
-        <v>6753384</v>
+        <v>6753361</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5932,10 +5932,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122567100</v>
+        <v>122567089</v>
       </c>
       <c r="B53" t="n">
-        <v>78766</v>
+        <v>56688</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5944,38 +5944,43 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>441332</v>
+        <v>441283</v>
       </c>
       <c r="R53" t="n">
-        <v>6753382</v>
+        <v>6753349</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6034,7 +6039,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122567125</v>
+        <v>122567102</v>
       </c>
       <c r="B54" t="n">
         <v>78766</v>
@@ -6074,10 +6079,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>441356</v>
+        <v>441305</v>
       </c>
       <c r="R54" t="n">
-        <v>6753361</v>
+        <v>6753384</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6136,10 +6141,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122567089</v>
+        <v>122567100</v>
       </c>
       <c r="B55" t="n">
-        <v>56688</v>
+        <v>78766</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6148,43 +6153,38 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>441283</v>
+        <v>441332</v>
       </c>
       <c r="R55" t="n">
-        <v>6753349</v>
+        <v>6753382</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6758,7 +6758,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122567116</v>
+        <v>122567097</v>
       </c>
       <c r="B61" t="n">
         <v>78766</v>
@@ -6798,10 +6798,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>441199</v>
+        <v>441320</v>
       </c>
       <c r="R61" t="n">
-        <v>6753562</v>
+        <v>6753429</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6860,7 +6860,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122567097</v>
+        <v>122567134</v>
       </c>
       <c r="B62" t="n">
         <v>78766</v>
@@ -6903,7 +6903,7 @@
         <v>441320</v>
       </c>
       <c r="R62" t="n">
-        <v>6753429</v>
+        <v>6753453</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6962,10 +6962,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122567134</v>
+        <v>122567066</v>
       </c>
       <c r="B63" t="n">
-        <v>78766</v>
+        <v>8441</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -6974,38 +6974,43 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>441320</v>
+        <v>441258</v>
       </c>
       <c r="R63" t="n">
-        <v>6753453</v>
+        <v>6753406</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7064,10 +7069,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122567069</v>
+        <v>122567116</v>
       </c>
       <c r="B64" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7076,43 +7081,38 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>441119</v>
+        <v>441199</v>
       </c>
       <c r="R64" t="n">
-        <v>6753677</v>
+        <v>6753562</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7171,7 +7171,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122567066</v>
+        <v>122567069</v>
       </c>
       <c r="B65" t="n">
         <v>8441</v>
@@ -7216,10 +7216,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>441258</v>
+        <v>441119</v>
       </c>
       <c r="R65" t="n">
-        <v>6753406</v>
+        <v>6753677</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7380,10 +7380,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122567042</v>
+        <v>122567103</v>
       </c>
       <c r="B67" t="n">
-        <v>79384</v>
+        <v>78766</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7396,21 +7396,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7420,10 +7420,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>441336</v>
+        <v>441287</v>
       </c>
       <c r="R67" t="n">
-        <v>6753370</v>
+        <v>6753389</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7482,10 +7482,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122567081</v>
+        <v>122567042</v>
       </c>
       <c r="B68" t="n">
-        <v>78503</v>
+        <v>79384</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7498,21 +7498,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7522,10 +7522,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>441344</v>
+        <v>441336</v>
       </c>
       <c r="R68" t="n">
-        <v>6753341</v>
+        <v>6753370</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7584,10 +7584,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122567103</v>
+        <v>122567081</v>
       </c>
       <c r="B69" t="n">
-        <v>78766</v>
+        <v>78503</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7600,21 +7600,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7624,10 +7624,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>441287</v>
+        <v>441344</v>
       </c>
       <c r="R69" t="n">
-        <v>6753389</v>
+        <v>6753341</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>

--- a/artfynd/A 61943-2024 artfynd.xlsx
+++ b/artfynd/A 61943-2024 artfynd.xlsx
@@ -2210,10 +2210,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122567083</v>
+        <v>122567068</v>
       </c>
       <c r="B17" t="n">
-        <v>78503</v>
+        <v>8441</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2222,38 +2222,43 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>441348</v>
+        <v>441150</v>
       </c>
       <c r="R17" t="n">
-        <v>6753422</v>
+        <v>6753623</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2618,10 +2623,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122567068</v>
+        <v>122567083</v>
       </c>
       <c r="B21" t="n">
-        <v>8441</v>
+        <v>78503</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2630,43 +2635,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>441150</v>
+        <v>441348</v>
       </c>
       <c r="R21" t="n">
-        <v>6753623</v>
+        <v>6753422</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3133,10 +3133,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122567070</v>
+        <v>122567035</v>
       </c>
       <c r="B26" t="n">
-        <v>8441</v>
+        <v>79384</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3145,33 +3145,28 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
@@ -3181,7 +3176,7 @@
         <v>441158</v>
       </c>
       <c r="R26" t="n">
-        <v>6753533</v>
+        <v>6753553</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3240,10 +3235,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122567119</v>
+        <v>122567044</v>
       </c>
       <c r="B27" t="n">
-        <v>78766</v>
+        <v>79384</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3256,21 +3251,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3280,10 +3275,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>441291</v>
+        <v>441348</v>
       </c>
       <c r="R27" t="n">
-        <v>6753289</v>
+        <v>6753445</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3342,10 +3337,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122567136</v>
+        <v>122567048</v>
       </c>
       <c r="B28" t="n">
-        <v>78766</v>
+        <v>74863</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3358,21 +3353,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3382,10 +3377,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>441345</v>
+        <v>441302</v>
       </c>
       <c r="R28" t="n">
-        <v>6753451</v>
+        <v>6753380</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3444,10 +3439,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122567127</v>
+        <v>122567070</v>
       </c>
       <c r="B29" t="n">
-        <v>78766</v>
+        <v>8441</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3456,38 +3451,43 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>441338</v>
+        <v>441158</v>
       </c>
       <c r="R29" t="n">
-        <v>6753386</v>
+        <v>6753533</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3546,10 +3546,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122567035</v>
+        <v>122567119</v>
       </c>
       <c r="B30" t="n">
-        <v>79384</v>
+        <v>78766</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3562,21 +3562,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3586,10 +3586,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>441158</v>
+        <v>441291</v>
       </c>
       <c r="R30" t="n">
-        <v>6753553</v>
+        <v>6753289</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3648,10 +3648,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122567044</v>
+        <v>122567136</v>
       </c>
       <c r="B31" t="n">
-        <v>79384</v>
+        <v>78766</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3664,21 +3664,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3688,10 +3688,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>441348</v>
+        <v>441345</v>
       </c>
       <c r="R31" t="n">
-        <v>6753445</v>
+        <v>6753451</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3750,10 +3750,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122567048</v>
+        <v>122567127</v>
       </c>
       <c r="B32" t="n">
-        <v>74863</v>
+        <v>78766</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3766,21 +3766,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3790,10 +3790,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>441302</v>
+        <v>441338</v>
       </c>
       <c r="R32" t="n">
-        <v>6753380</v>
+        <v>6753386</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3954,10 +3954,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122567038</v>
+        <v>122567064</v>
       </c>
       <c r="B34" t="n">
-        <v>79384</v>
+        <v>8441</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3966,38 +3966,43 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>441336</v>
+        <v>441389</v>
       </c>
       <c r="R34" t="n">
-        <v>6753344</v>
+        <v>6753439</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4056,10 +4061,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122567064</v>
+        <v>122567038</v>
       </c>
       <c r="B35" t="n">
-        <v>8441</v>
+        <v>79384</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4068,43 +4073,38 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>441389</v>
+        <v>441336</v>
       </c>
       <c r="R35" t="n">
-        <v>6753439</v>
+        <v>6753344</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4586,10 +4586,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122567046</v>
+        <v>122567077</v>
       </c>
       <c r="B40" t="n">
-        <v>74863</v>
+        <v>8441</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4598,38 +4598,43 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6440</v>
+        <v>106545</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>441304</v>
+        <v>441381</v>
       </c>
       <c r="R40" t="n">
-        <v>6753366</v>
+        <v>6753451</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4688,10 +4693,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122567077</v>
+        <v>122567046</v>
       </c>
       <c r="B41" t="n">
-        <v>8441</v>
+        <v>74863</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4700,43 +4705,38 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>106545</v>
+        <v>6440</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>441381</v>
+        <v>441304</v>
       </c>
       <c r="R41" t="n">
-        <v>6753451</v>
+        <v>6753366</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>

--- a/artfynd/A 61943-2024 artfynd.xlsx
+++ b/artfynd/A 61943-2024 artfynd.xlsx
@@ -3133,10 +3133,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122567035</v>
+        <v>122567070</v>
       </c>
       <c r="B26" t="n">
-        <v>79384</v>
+        <v>8441</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3145,28 +3145,33 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
@@ -3176,7 +3181,7 @@
         <v>441158</v>
       </c>
       <c r="R26" t="n">
-        <v>6753553</v>
+        <v>6753533</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3235,10 +3240,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122567044</v>
+        <v>122567119</v>
       </c>
       <c r="B27" t="n">
-        <v>79384</v>
+        <v>78766</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3251,21 +3256,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3275,10 +3280,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>441348</v>
+        <v>441291</v>
       </c>
       <c r="R27" t="n">
-        <v>6753445</v>
+        <v>6753289</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3337,10 +3342,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122567048</v>
+        <v>122567136</v>
       </c>
       <c r="B28" t="n">
-        <v>74863</v>
+        <v>78766</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3353,21 +3358,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3377,10 +3382,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>441302</v>
+        <v>441345</v>
       </c>
       <c r="R28" t="n">
-        <v>6753380</v>
+        <v>6753451</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3439,10 +3444,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122567070</v>
+        <v>122567127</v>
       </c>
       <c r="B29" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3451,43 +3456,38 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>441158</v>
+        <v>441338</v>
       </c>
       <c r="R29" t="n">
-        <v>6753533</v>
+        <v>6753386</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3546,10 +3546,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122567119</v>
+        <v>122567035</v>
       </c>
       <c r="B30" t="n">
-        <v>78766</v>
+        <v>79384</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3562,21 +3562,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3586,10 +3586,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>441291</v>
+        <v>441158</v>
       </c>
       <c r="R30" t="n">
-        <v>6753289</v>
+        <v>6753553</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3648,10 +3648,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122567136</v>
+        <v>122567044</v>
       </c>
       <c r="B31" t="n">
-        <v>78766</v>
+        <v>79384</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3664,21 +3664,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3688,10 +3688,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>441345</v>
+        <v>441348</v>
       </c>
       <c r="R31" t="n">
-        <v>6753451</v>
+        <v>6753445</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3750,10 +3750,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122567127</v>
+        <v>122567048</v>
       </c>
       <c r="B32" t="n">
-        <v>78766</v>
+        <v>74863</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3766,21 +3766,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3790,10 +3790,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>441338</v>
+        <v>441302</v>
       </c>
       <c r="R32" t="n">
-        <v>6753386</v>
+        <v>6753380</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4479,10 +4479,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122567088</v>
+        <v>122567046</v>
       </c>
       <c r="B39" t="n">
-        <v>56688</v>
+        <v>74863</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4491,43 +4491,38 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100138</v>
+        <v>6440</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>441262</v>
+        <v>441304</v>
       </c>
       <c r="R39" t="n">
-        <v>6753412</v>
+        <v>6753366</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4586,10 +4581,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122567077</v>
+        <v>122567088</v>
       </c>
       <c r="B40" t="n">
-        <v>8441</v>
+        <v>56688</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4602,27 +4597,27 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -4631,10 +4626,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>441381</v>
+        <v>441262</v>
       </c>
       <c r="R40" t="n">
-        <v>6753451</v>
+        <v>6753412</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4693,10 +4688,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122567046</v>
+        <v>122567077</v>
       </c>
       <c r="B41" t="n">
-        <v>74863</v>
+        <v>8441</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4705,38 +4700,43 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6440</v>
+        <v>106545</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>441304</v>
+        <v>441381</v>
       </c>
       <c r="R41" t="n">
-        <v>6753366</v>
+        <v>6753451</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4795,10 +4795,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122567096</v>
+        <v>122567073</v>
       </c>
       <c r="B42" t="n">
-        <v>78766</v>
+        <v>8441</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4807,38 +4807,43 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>441319</v>
+        <v>441269</v>
       </c>
       <c r="R42" t="n">
-        <v>6753442</v>
+        <v>6753365</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4897,10 +4902,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122567051</v>
+        <v>122567071</v>
       </c>
       <c r="B43" t="n">
-        <v>74863</v>
+        <v>8441</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4909,38 +4914,43 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6440</v>
+        <v>106545</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>441352</v>
+        <v>441172</v>
       </c>
       <c r="R43" t="n">
-        <v>6753455</v>
+        <v>6753515</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4999,10 +5009,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122567073</v>
+        <v>122567096</v>
       </c>
       <c r="B44" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5011,43 +5021,38 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>441269</v>
+        <v>441319</v>
       </c>
       <c r="R44" t="n">
-        <v>6753365</v>
+        <v>6753442</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5106,10 +5111,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122567071</v>
+        <v>122567051</v>
       </c>
       <c r="B45" t="n">
-        <v>8441</v>
+        <v>74863</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5118,43 +5123,38 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>106545</v>
+        <v>6440</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>441172</v>
+        <v>441352</v>
       </c>
       <c r="R45" t="n">
-        <v>6753515</v>
+        <v>6753455</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -7380,10 +7380,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122567103</v>
+        <v>122567042</v>
       </c>
       <c r="B67" t="n">
-        <v>78766</v>
+        <v>79384</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7396,21 +7396,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7420,10 +7420,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>441287</v>
+        <v>441336</v>
       </c>
       <c r="R67" t="n">
-        <v>6753389</v>
+        <v>6753370</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7482,10 +7482,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122567042</v>
+        <v>122567081</v>
       </c>
       <c r="B68" t="n">
-        <v>79384</v>
+        <v>78503</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7498,21 +7498,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7522,10 +7522,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>441336</v>
+        <v>441344</v>
       </c>
       <c r="R68" t="n">
-        <v>6753370</v>
+        <v>6753341</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7584,10 +7584,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122567081</v>
+        <v>122567103</v>
       </c>
       <c r="B69" t="n">
-        <v>78503</v>
+        <v>78766</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7600,21 +7600,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7624,10 +7624,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>441344</v>
+        <v>441287</v>
       </c>
       <c r="R69" t="n">
-        <v>6753341</v>
+        <v>6753389</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>

--- a/artfynd/A 61943-2024 artfynd.xlsx
+++ b/artfynd/A 61943-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122567126</v>
+        <v>122567066</v>
       </c>
       <c r="B2" t="n">
-        <v>78766</v>
+        <v>8441</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,43 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>441344</v>
+        <v>441258</v>
       </c>
       <c r="R2" t="n">
-        <v>6753362</v>
+        <v>6753406</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122567105</v>
+        <v>122567073</v>
       </c>
       <c r="B3" t="n">
-        <v>78766</v>
+        <v>8441</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,28 +794,33 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
@@ -820,7 +830,7 @@
         <v>441269</v>
       </c>
       <c r="R3" t="n">
-        <v>6753398</v>
+        <v>6753365</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122567109</v>
+        <v>122567100</v>
       </c>
       <c r="B4" t="n">
         <v>78766</v>
@@ -919,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>441223</v>
+        <v>441332</v>
       </c>
       <c r="R4" t="n">
-        <v>6753536</v>
+        <v>6753382</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,7 +991,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122567122</v>
+        <v>122567104</v>
       </c>
       <c r="B5" t="n">
         <v>78766</v>
@@ -1021,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>441315</v>
+        <v>441277</v>
       </c>
       <c r="R5" t="n">
-        <v>6753342</v>
+        <v>6753396</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,7 +1093,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122567132</v>
+        <v>122567128</v>
       </c>
       <c r="B6" t="n">
         <v>78766</v>
@@ -1123,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>441329</v>
+        <v>441350</v>
       </c>
       <c r="R6" t="n">
-        <v>6753438</v>
+        <v>6753388</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1195,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122567099</v>
+        <v>122567033</v>
       </c>
       <c r="B7" t="n">
-        <v>78766</v>
+        <v>79384</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1211,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>441323</v>
+        <v>441194</v>
       </c>
       <c r="R7" t="n">
-        <v>6753416</v>
+        <v>6753576</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1297,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122567120</v>
+        <v>122567089</v>
       </c>
       <c r="B8" t="n">
-        <v>78766</v>
+        <v>56688</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1299,38 +1309,43 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>441289</v>
+        <v>441283</v>
       </c>
       <c r="R8" t="n">
-        <v>6753324</v>
+        <v>6753349</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,7 +1404,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122567135</v>
+        <v>122567131</v>
       </c>
       <c r="B9" t="n">
         <v>78766</v>
@@ -1429,10 +1444,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>441322</v>
+        <v>441347</v>
       </c>
       <c r="R9" t="n">
-        <v>6753459</v>
+        <v>6753407</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,10 +1506,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122567072</v>
+        <v>122567105</v>
       </c>
       <c r="B10" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1503,43 +1518,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>441255</v>
+        <v>441269</v>
       </c>
       <c r="R10" t="n">
-        <v>6753382</v>
+        <v>6753398</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1598,7 +1608,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122567050</v>
+        <v>122567051</v>
       </c>
       <c r="B11" t="n">
         <v>74863</v>
@@ -1638,10 +1648,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>441314</v>
+        <v>441352</v>
       </c>
       <c r="R11" t="n">
-        <v>6753342</v>
+        <v>6753455</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1700,7 +1710,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122567041</v>
+        <v>122567044</v>
       </c>
       <c r="B12" t="n">
         <v>79384</v>
@@ -1740,10 +1750,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>441357</v>
+        <v>441348</v>
       </c>
       <c r="R12" t="n">
-        <v>6753361</v>
+        <v>6753445</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1802,10 +1812,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122567118</v>
+        <v>122567047</v>
       </c>
       <c r="B13" t="n">
-        <v>78766</v>
+        <v>74863</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1818,21 +1828,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1842,10 +1852,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>441277</v>
+        <v>441304</v>
       </c>
       <c r="R13" t="n">
-        <v>6753324</v>
+        <v>6753377</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1904,7 +1914,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122567106</v>
+        <v>122567135</v>
       </c>
       <c r="B14" t="n">
         <v>78766</v>
@@ -1944,10 +1954,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>441266</v>
+        <v>441322</v>
       </c>
       <c r="R14" t="n">
-        <v>6753401</v>
+        <v>6753459</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2006,10 +2016,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122567039</v>
+        <v>122567095</v>
       </c>
       <c r="B15" t="n">
-        <v>79384</v>
+        <v>78766</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2022,21 +2032,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2046,10 +2056,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>441344</v>
+        <v>441406</v>
       </c>
       <c r="R15" t="n">
-        <v>6753341</v>
+        <v>6753439</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2108,10 +2118,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122567043</v>
+        <v>122567134</v>
       </c>
       <c r="B16" t="n">
-        <v>79384</v>
+        <v>78766</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2124,21 +2134,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2148,10 +2158,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>441348</v>
+        <v>441320</v>
       </c>
       <c r="R16" t="n">
-        <v>6753422</v>
+        <v>6753453</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2210,10 +2220,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122567068</v>
+        <v>122567101</v>
       </c>
       <c r="B17" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2222,43 +2232,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>441150</v>
+        <v>441301</v>
       </c>
       <c r="R17" t="n">
-        <v>6753623</v>
+        <v>6753376</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2317,10 +2322,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122567158</v>
+        <v>122567122</v>
       </c>
       <c r="B18" t="n">
-        <v>78411</v>
+        <v>78766</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2333,21 +2338,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2357,10 +2362,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>441248</v>
+        <v>441315</v>
       </c>
       <c r="R18" t="n">
-        <v>6753389</v>
+        <v>6753342</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2419,10 +2424,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122567111</v>
+        <v>122567035</v>
       </c>
       <c r="B19" t="n">
-        <v>78766</v>
+        <v>79384</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2435,21 +2440,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2459,7 +2464,7 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>441221</v>
+        <v>441158</v>
       </c>
       <c r="R19" t="n">
         <v>6753553</v>
@@ -2521,10 +2526,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122567104</v>
+        <v>122567046</v>
       </c>
       <c r="B20" t="n">
-        <v>78766</v>
+        <v>74863</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2537,21 +2542,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2561,10 +2566,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>441277</v>
+        <v>441304</v>
       </c>
       <c r="R20" t="n">
-        <v>6753396</v>
+        <v>6753366</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2623,10 +2628,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122567083</v>
+        <v>122567069</v>
       </c>
       <c r="B21" t="n">
-        <v>78503</v>
+        <v>8441</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2635,38 +2640,43 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>441348</v>
+        <v>441119</v>
       </c>
       <c r="R21" t="n">
-        <v>6753422</v>
+        <v>6753677</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2725,10 +2735,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122567095</v>
+        <v>122567072</v>
       </c>
       <c r="B22" t="n">
-        <v>78766</v>
+        <v>8441</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2737,38 +2747,43 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>441406</v>
+        <v>441255</v>
       </c>
       <c r="R22" t="n">
-        <v>6753439</v>
+        <v>6753382</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2827,10 +2842,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122567049</v>
+        <v>122567119</v>
       </c>
       <c r="B23" t="n">
-        <v>74863</v>
+        <v>78766</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2843,21 +2858,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2867,10 +2882,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>441299</v>
+        <v>441291</v>
       </c>
       <c r="R23" t="n">
-        <v>6753387</v>
+        <v>6753289</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2929,10 +2944,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122567034</v>
+        <v>122567111</v>
       </c>
       <c r="B24" t="n">
-        <v>79384</v>
+        <v>78766</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2945,21 +2960,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2969,10 +2984,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>441152</v>
+        <v>441221</v>
       </c>
       <c r="R24" t="n">
-        <v>6753562</v>
+        <v>6753553</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3031,7 +3046,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122567033</v>
+        <v>122567042</v>
       </c>
       <c r="B25" t="n">
         <v>79384</v>
@@ -3071,10 +3086,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>441194</v>
+        <v>441336</v>
       </c>
       <c r="R25" t="n">
-        <v>6753576</v>
+        <v>6753370</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3133,10 +3148,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122567070</v>
+        <v>122567158</v>
       </c>
       <c r="B26" t="n">
-        <v>8441</v>
+        <v>78411</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3145,43 +3160,38 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>106545</v>
+        <v>353</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>441158</v>
+        <v>441248</v>
       </c>
       <c r="R26" t="n">
-        <v>6753533</v>
+        <v>6753389</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3240,10 +3250,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122567119</v>
+        <v>122567070</v>
       </c>
       <c r="B27" t="n">
-        <v>78766</v>
+        <v>8441</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3252,38 +3262,43 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>441291</v>
+        <v>441158</v>
       </c>
       <c r="R27" t="n">
-        <v>6753289</v>
+        <v>6753533</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3342,10 +3357,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122567136</v>
+        <v>122567064</v>
       </c>
       <c r="B28" t="n">
-        <v>78766</v>
+        <v>8441</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3354,38 +3369,43 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>441345</v>
+        <v>441389</v>
       </c>
       <c r="R28" t="n">
-        <v>6753451</v>
+        <v>6753439</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3444,10 +3464,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122567127</v>
+        <v>122567043</v>
       </c>
       <c r="B29" t="n">
-        <v>78766</v>
+        <v>79384</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3460,21 +3480,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3484,10 +3504,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>441338</v>
+        <v>441348</v>
       </c>
       <c r="R29" t="n">
-        <v>6753386</v>
+        <v>6753422</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3546,10 +3566,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122567035</v>
+        <v>122567067</v>
       </c>
       <c r="B30" t="n">
-        <v>79384</v>
+        <v>8441</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3558,38 +3578,43 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>441158</v>
+        <v>441231</v>
       </c>
       <c r="R30" t="n">
-        <v>6753553</v>
+        <v>6753537</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3648,10 +3673,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122567044</v>
+        <v>122567077</v>
       </c>
       <c r="B31" t="n">
-        <v>79384</v>
+        <v>8441</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3660,38 +3685,43 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>441348</v>
+        <v>441381</v>
       </c>
       <c r="R31" t="n">
-        <v>6753445</v>
+        <v>6753451</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3750,10 +3780,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122567048</v>
+        <v>122567081</v>
       </c>
       <c r="B32" t="n">
-        <v>74863</v>
+        <v>78503</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3766,21 +3796,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6440</v>
+        <v>228912</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3790,10 +3820,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>441302</v>
+        <v>441344</v>
       </c>
       <c r="R32" t="n">
-        <v>6753380</v>
+        <v>6753341</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3852,10 +3882,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122567098</v>
+        <v>122567036</v>
       </c>
       <c r="B33" t="n">
-        <v>78766</v>
+        <v>79384</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3868,21 +3898,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3892,10 +3922,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>441329</v>
+        <v>441283</v>
       </c>
       <c r="R33" t="n">
-        <v>6753411</v>
+        <v>6753350</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3954,10 +3984,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122567064</v>
+        <v>122567091</v>
       </c>
       <c r="B34" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3966,43 +3996,38 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>441389</v>
+        <v>441420</v>
       </c>
       <c r="R34" t="n">
-        <v>6753439</v>
+        <v>6753456</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4061,10 +4086,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122567038</v>
+        <v>122567108</v>
       </c>
       <c r="B35" t="n">
-        <v>79384</v>
+        <v>78766</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4077,21 +4102,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4101,10 +4126,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>441336</v>
+        <v>441273</v>
       </c>
       <c r="R35" t="n">
-        <v>6753344</v>
+        <v>6753425</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4163,10 +4188,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122567059</v>
+        <v>122567096</v>
       </c>
       <c r="B36" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4175,43 +4200,38 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>441302</v>
+        <v>441319</v>
       </c>
       <c r="R36" t="n">
-        <v>6753294</v>
+        <v>6753442</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4270,10 +4290,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122567075</v>
+        <v>122567127</v>
       </c>
       <c r="B37" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4282,43 +4302,38 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>441291</v>
+        <v>441338</v>
       </c>
       <c r="R37" t="n">
-        <v>6753289</v>
+        <v>6753386</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4377,7 +4392,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122567117</v>
+        <v>122567116</v>
       </c>
       <c r="B38" t="n">
         <v>78766</v>
@@ -4417,10 +4432,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>441193</v>
+        <v>441199</v>
       </c>
       <c r="R38" t="n">
-        <v>6753577</v>
+        <v>6753562</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4479,7 +4494,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122567046</v>
+        <v>122567049</v>
       </c>
       <c r="B39" t="n">
         <v>74863</v>
@@ -4519,10 +4534,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>441304</v>
+        <v>441299</v>
       </c>
       <c r="R39" t="n">
-        <v>6753366</v>
+        <v>6753387</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4581,10 +4596,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122567088</v>
+        <v>122567056</v>
       </c>
       <c r="B40" t="n">
-        <v>56688</v>
+        <v>57494</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4593,31 +4608,31 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -4626,10 +4641,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>441262</v>
+        <v>441305</v>
       </c>
       <c r="R40" t="n">
-        <v>6753412</v>
+        <v>6753366</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4688,7 +4703,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122567077</v>
+        <v>122567068</v>
       </c>
       <c r="B41" t="n">
         <v>8441</v>
@@ -4733,10 +4748,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>441381</v>
+        <v>441150</v>
       </c>
       <c r="R41" t="n">
-        <v>6753451</v>
+        <v>6753623</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4795,10 +4810,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122567073</v>
+        <v>122567050</v>
       </c>
       <c r="B42" t="n">
-        <v>8441</v>
+        <v>74863</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4807,43 +4822,38 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>106545</v>
+        <v>6440</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>441269</v>
+        <v>441314</v>
       </c>
       <c r="R42" t="n">
-        <v>6753365</v>
+        <v>6753342</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4902,10 +4912,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122567071</v>
+        <v>122567132</v>
       </c>
       <c r="B43" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4914,43 +4924,38 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>441172</v>
+        <v>441329</v>
       </c>
       <c r="R43" t="n">
-        <v>6753515</v>
+        <v>6753438</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5009,10 +5014,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122567096</v>
+        <v>122567059</v>
       </c>
       <c r="B44" t="n">
-        <v>78766</v>
+        <v>8441</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5021,38 +5026,43 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>441319</v>
+        <v>441302</v>
       </c>
       <c r="R44" t="n">
-        <v>6753442</v>
+        <v>6753294</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5111,10 +5121,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122567051</v>
+        <v>122567074</v>
       </c>
       <c r="B45" t="n">
-        <v>74863</v>
+        <v>8441</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5123,38 +5133,43 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6440</v>
+        <v>106545</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>441352</v>
+        <v>441284</v>
       </c>
       <c r="R45" t="n">
-        <v>6753455</v>
+        <v>6753286</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5213,7 +5228,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122567091</v>
+        <v>122567113</v>
       </c>
       <c r="B46" t="n">
         <v>78766</v>
@@ -5253,10 +5268,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>441420</v>
+        <v>441207</v>
       </c>
       <c r="R46" t="n">
-        <v>6753456</v>
+        <v>6753568</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5315,7 +5330,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122567137</v>
+        <v>122567106</v>
       </c>
       <c r="B47" t="n">
         <v>78766</v>
@@ -5355,10 +5370,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>441348</v>
+        <v>441266</v>
       </c>
       <c r="R47" t="n">
-        <v>6753444</v>
+        <v>6753401</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5519,10 +5534,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122567101</v>
+        <v>122567038</v>
       </c>
       <c r="B49" t="n">
-        <v>78766</v>
+        <v>79384</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5535,21 +5550,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5559,10 +5574,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>441301</v>
+        <v>441336</v>
       </c>
       <c r="R49" t="n">
-        <v>6753376</v>
+        <v>6753344</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5621,10 +5636,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122567108</v>
+        <v>122567083</v>
       </c>
       <c r="B50" t="n">
-        <v>78766</v>
+        <v>78503</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5637,21 +5652,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5661,10 +5676,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>441273</v>
+        <v>441348</v>
       </c>
       <c r="R50" t="n">
-        <v>6753425</v>
+        <v>6753422</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5723,10 +5738,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122567056</v>
+        <v>122567102</v>
       </c>
       <c r="B51" t="n">
-        <v>57494</v>
+        <v>78766</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5739,29 +5754,24 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
@@ -5771,7 +5781,7 @@
         <v>441305</v>
       </c>
       <c r="R51" t="n">
-        <v>6753366</v>
+        <v>6753384</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5830,7 +5840,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122567125</v>
+        <v>122567114</v>
       </c>
       <c r="B52" t="n">
         <v>78766</v>
@@ -5870,10 +5880,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>441356</v>
+        <v>441206</v>
       </c>
       <c r="R52" t="n">
-        <v>6753361</v>
+        <v>6753562</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5932,10 +5942,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122567089</v>
+        <v>122567136</v>
       </c>
       <c r="B53" t="n">
-        <v>56688</v>
+        <v>78766</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5944,43 +5954,38 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>441283</v>
+        <v>441345</v>
       </c>
       <c r="R53" t="n">
-        <v>6753349</v>
+        <v>6753451</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6039,7 +6044,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122567102</v>
+        <v>122567103</v>
       </c>
       <c r="B54" t="n">
         <v>78766</v>
@@ -6079,10 +6084,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>441305</v>
+        <v>441287</v>
       </c>
       <c r="R54" t="n">
-        <v>6753384</v>
+        <v>6753389</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6141,7 +6146,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122567100</v>
+        <v>122567120</v>
       </c>
       <c r="B55" t="n">
         <v>78766</v>
@@ -6181,10 +6186,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>441332</v>
+        <v>441289</v>
       </c>
       <c r="R55" t="n">
-        <v>6753382</v>
+        <v>6753324</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6243,7 +6248,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122567139</v>
+        <v>122567117</v>
       </c>
       <c r="B56" t="n">
         <v>78766</v>
@@ -6283,10 +6288,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>441430</v>
+        <v>441193</v>
       </c>
       <c r="R56" t="n">
-        <v>6753445</v>
+        <v>6753577</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6345,7 +6350,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122567121</v>
+        <v>122567138</v>
       </c>
       <c r="B57" t="n">
         <v>78766</v>
@@ -6385,10 +6390,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>441306</v>
+        <v>441383</v>
       </c>
       <c r="R57" t="n">
-        <v>6753338</v>
+        <v>6753450</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6447,10 +6452,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122567036</v>
+        <v>122567139</v>
       </c>
       <c r="B58" t="n">
-        <v>79384</v>
+        <v>78766</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6463,21 +6468,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6487,10 +6492,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>441283</v>
+        <v>441430</v>
       </c>
       <c r="R58" t="n">
-        <v>6753350</v>
+        <v>6753445</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6549,10 +6554,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122567047</v>
+        <v>122567034</v>
       </c>
       <c r="B59" t="n">
-        <v>74863</v>
+        <v>79384</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6565,21 +6570,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6440</v>
+        <v>6453</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6589,10 +6594,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>441304</v>
+        <v>441152</v>
       </c>
       <c r="R59" t="n">
-        <v>6753377</v>
+        <v>6753562</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6651,7 +6656,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122567067</v>
+        <v>122567075</v>
       </c>
       <c r="B60" t="n">
         <v>8441</v>
@@ -6696,10 +6701,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>441231</v>
+        <v>441291</v>
       </c>
       <c r="R60" t="n">
-        <v>6753537</v>
+        <v>6753289</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6758,10 +6763,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122567097</v>
+        <v>122567088</v>
       </c>
       <c r="B61" t="n">
-        <v>78766</v>
+        <v>56688</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6770,38 +6775,43 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>441320</v>
+        <v>441262</v>
       </c>
       <c r="R61" t="n">
-        <v>6753429</v>
+        <v>6753412</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6860,7 +6870,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122567134</v>
+        <v>122567112</v>
       </c>
       <c r="B62" t="n">
         <v>78766</v>
@@ -6900,10 +6910,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>441320</v>
+        <v>441217</v>
       </c>
       <c r="R62" t="n">
-        <v>6753453</v>
+        <v>6753556</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6962,10 +6972,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122567066</v>
+        <v>122567137</v>
       </c>
       <c r="B63" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -6974,43 +6984,38 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>441258</v>
+        <v>441348</v>
       </c>
       <c r="R63" t="n">
-        <v>6753406</v>
+        <v>6753444</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7069,10 +7074,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122567116</v>
+        <v>122567053</v>
       </c>
       <c r="B64" t="n">
-        <v>78766</v>
+        <v>78800</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7085,21 +7090,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7109,10 +7114,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>441199</v>
+        <v>441420</v>
       </c>
       <c r="R64" t="n">
-        <v>6753562</v>
+        <v>6753456</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7171,10 +7176,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122567069</v>
+        <v>122567099</v>
       </c>
       <c r="B65" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7183,43 +7188,38 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>441119</v>
+        <v>441323</v>
       </c>
       <c r="R65" t="n">
-        <v>6753677</v>
+        <v>6753416</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7278,10 +7278,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122567053</v>
+        <v>122567041</v>
       </c>
       <c r="B66" t="n">
-        <v>78800</v>
+        <v>79384</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7294,21 +7294,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7318,10 +7318,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>441420</v>
+        <v>441357</v>
       </c>
       <c r="R66" t="n">
-        <v>6753456</v>
+        <v>6753361</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7380,10 +7380,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122567042</v>
+        <v>122567109</v>
       </c>
       <c r="B67" t="n">
-        <v>79384</v>
+        <v>78766</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7396,21 +7396,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7420,10 +7420,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>441336</v>
+        <v>441223</v>
       </c>
       <c r="R67" t="n">
-        <v>6753370</v>
+        <v>6753536</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7482,10 +7482,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122567081</v>
+        <v>122567126</v>
       </c>
       <c r="B68" t="n">
-        <v>78503</v>
+        <v>78766</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7498,21 +7498,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7525,7 +7525,7 @@
         <v>441344</v>
       </c>
       <c r="R68" t="n">
-        <v>6753341</v>
+        <v>6753362</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7584,7 +7584,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122567103</v>
+        <v>122567098</v>
       </c>
       <c r="B69" t="n">
         <v>78766</v>
@@ -7624,10 +7624,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>441287</v>
+        <v>441329</v>
       </c>
       <c r="R69" t="n">
-        <v>6753389</v>
+        <v>6753411</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7686,7 +7686,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122567133</v>
+        <v>122567125</v>
       </c>
       <c r="B70" t="n">
         <v>78766</v>
@@ -7726,10 +7726,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>441321</v>
+        <v>441356</v>
       </c>
       <c r="R70" t="n">
-        <v>6753447</v>
+        <v>6753361</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7788,10 +7788,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122567113</v>
+        <v>122567039</v>
       </c>
       <c r="B71" t="n">
-        <v>78766</v>
+        <v>79384</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7804,21 +7804,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7828,10 +7828,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>441207</v>
+        <v>441344</v>
       </c>
       <c r="R71" t="n">
-        <v>6753568</v>
+        <v>6753341</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7890,10 +7890,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122567131</v>
+        <v>122567048</v>
       </c>
       <c r="B72" t="n">
-        <v>78766</v>
+        <v>74863</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -7906,21 +7906,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7930,10 +7930,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>441347</v>
+        <v>441302</v>
       </c>
       <c r="R72" t="n">
-        <v>6753407</v>
+        <v>6753380</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7992,7 +7992,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>122567112</v>
+        <v>122567107</v>
       </c>
       <c r="B73" t="n">
         <v>78766</v>
@@ -8032,10 +8032,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>441217</v>
+        <v>441262</v>
       </c>
       <c r="R73" t="n">
-        <v>6753556</v>
+        <v>6753417</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8094,7 +8094,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>122567114</v>
+        <v>122567118</v>
       </c>
       <c r="B74" t="n">
         <v>78766</v>
@@ -8134,10 +8134,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>441206</v>
+        <v>441277</v>
       </c>
       <c r="R74" t="n">
-        <v>6753562</v>
+        <v>6753324</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8196,7 +8196,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>122567138</v>
+        <v>122567097</v>
       </c>
       <c r="B75" t="n">
         <v>78766</v>
@@ -8236,10 +8236,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>441383</v>
+        <v>441320</v>
       </c>
       <c r="R75" t="n">
-        <v>6753450</v>
+        <v>6753429</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8298,10 +8298,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>122567128</v>
+        <v>122567071</v>
       </c>
       <c r="B76" t="n">
-        <v>78766</v>
+        <v>8441</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8310,38 +8310,43 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>441350</v>
+        <v>441172</v>
       </c>
       <c r="R76" t="n">
-        <v>6753388</v>
+        <v>6753515</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8400,7 +8405,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>122567107</v>
+        <v>122567133</v>
       </c>
       <c r="B77" t="n">
         <v>78766</v>
@@ -8440,10 +8445,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>441262</v>
+        <v>441321</v>
       </c>
       <c r="R77" t="n">
-        <v>6753417</v>
+        <v>6753447</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8502,10 +8507,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>122567074</v>
+        <v>122567121</v>
       </c>
       <c r="B78" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8514,43 +8519,38 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>441284</v>
+        <v>441306</v>
       </c>
       <c r="R78" t="n">
-        <v>6753286</v>
+        <v>6753338</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>

--- a/artfynd/A 61943-2024 artfynd.xlsx
+++ b/artfynd/A 61943-2024 artfynd.xlsx
@@ -1608,10 +1608,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122567051</v>
+        <v>122567135</v>
       </c>
       <c r="B11" t="n">
-        <v>74863</v>
+        <v>78766</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1624,21 +1624,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1648,10 +1648,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>441352</v>
+        <v>441322</v>
       </c>
       <c r="R11" t="n">
-        <v>6753455</v>
+        <v>6753459</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1710,10 +1710,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122567044</v>
+        <v>122567051</v>
       </c>
       <c r="B12" t="n">
-        <v>79384</v>
+        <v>74863</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1726,21 +1726,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>6440</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1750,10 +1750,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>441348</v>
+        <v>441352</v>
       </c>
       <c r="R12" t="n">
-        <v>6753445</v>
+        <v>6753455</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1812,10 +1812,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122567047</v>
+        <v>122567044</v>
       </c>
       <c r="B13" t="n">
-        <v>74863</v>
+        <v>79384</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1828,21 +1828,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6440</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1852,10 +1852,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>441304</v>
+        <v>441348</v>
       </c>
       <c r="R13" t="n">
-        <v>6753377</v>
+        <v>6753445</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1914,10 +1914,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122567135</v>
+        <v>122567047</v>
       </c>
       <c r="B14" t="n">
-        <v>78766</v>
+        <v>74863</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1930,21 +1930,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1954,10 +1954,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>441322</v>
+        <v>441304</v>
       </c>
       <c r="R14" t="n">
-        <v>6753459</v>
+        <v>6753377</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2735,10 +2735,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122567072</v>
+        <v>122567119</v>
       </c>
       <c r="B22" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2747,43 +2747,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>441255</v>
+        <v>441291</v>
       </c>
       <c r="R22" t="n">
-        <v>6753382</v>
+        <v>6753289</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2842,7 +2837,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122567119</v>
+        <v>122567111</v>
       </c>
       <c r="B23" t="n">
         <v>78766</v>
@@ -2882,10 +2877,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>441291</v>
+        <v>441221</v>
       </c>
       <c r="R23" t="n">
-        <v>6753289</v>
+        <v>6753553</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2944,10 +2939,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122567111</v>
+        <v>122567042</v>
       </c>
       <c r="B24" t="n">
-        <v>78766</v>
+        <v>79384</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2960,21 +2955,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2984,10 +2979,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>441221</v>
+        <v>441336</v>
       </c>
       <c r="R24" t="n">
-        <v>6753553</v>
+        <v>6753370</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3046,10 +3041,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122567042</v>
+        <v>122567072</v>
       </c>
       <c r="B25" t="n">
-        <v>79384</v>
+        <v>8441</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3058,38 +3053,43 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>441336</v>
+        <v>441255</v>
       </c>
       <c r="R25" t="n">
-        <v>6753370</v>
+        <v>6753382</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3464,10 +3464,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122567043</v>
+        <v>122567067</v>
       </c>
       <c r="B29" t="n">
-        <v>79384</v>
+        <v>8441</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3476,38 +3476,43 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>441348</v>
+        <v>441231</v>
       </c>
       <c r="R29" t="n">
-        <v>6753422</v>
+        <v>6753537</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3566,7 +3571,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122567067</v>
+        <v>122567077</v>
       </c>
       <c r="B30" t="n">
         <v>8441</v>
@@ -3611,10 +3616,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>441231</v>
+        <v>441381</v>
       </c>
       <c r="R30" t="n">
-        <v>6753537</v>
+        <v>6753451</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3673,10 +3678,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122567077</v>
+        <v>122567043</v>
       </c>
       <c r="B31" t="n">
-        <v>8441</v>
+        <v>79384</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3685,43 +3690,38 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>441381</v>
+        <v>441348</v>
       </c>
       <c r="R31" t="n">
-        <v>6753451</v>
+        <v>6753422</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4188,7 +4188,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122567096</v>
+        <v>122567127</v>
       </c>
       <c r="B36" t="n">
         <v>78766</v>
@@ -4228,10 +4228,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>441319</v>
+        <v>441338</v>
       </c>
       <c r="R36" t="n">
-        <v>6753442</v>
+        <v>6753386</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4290,7 +4290,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122567127</v>
+        <v>122567096</v>
       </c>
       <c r="B37" t="n">
         <v>78766</v>
@@ -4330,10 +4330,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>441338</v>
+        <v>441319</v>
       </c>
       <c r="R37" t="n">
-        <v>6753386</v>
+        <v>6753442</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4810,10 +4810,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122567050</v>
+        <v>122567132</v>
       </c>
       <c r="B42" t="n">
-        <v>74863</v>
+        <v>78766</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4826,21 +4826,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4850,10 +4850,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>441314</v>
+        <v>441329</v>
       </c>
       <c r="R42" t="n">
-        <v>6753342</v>
+        <v>6753438</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4912,10 +4912,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122567132</v>
+        <v>122567059</v>
       </c>
       <c r="B43" t="n">
-        <v>78766</v>
+        <v>8441</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4924,38 +4924,43 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>441329</v>
+        <v>441302</v>
       </c>
       <c r="R43" t="n">
-        <v>6753438</v>
+        <v>6753294</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5014,7 +5019,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122567059</v>
+        <v>122567074</v>
       </c>
       <c r="B44" t="n">
         <v>8441</v>
@@ -5050,7 +5055,7 @@
       <c r="I44" t="inlineStr"/>
       <c r="M44" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -5059,10 +5064,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>441302</v>
+        <v>441284</v>
       </c>
       <c r="R44" t="n">
-        <v>6753294</v>
+        <v>6753286</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5121,10 +5126,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122567074</v>
+        <v>122567050</v>
       </c>
       <c r="B45" t="n">
-        <v>8441</v>
+        <v>74863</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5133,43 +5138,38 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>106545</v>
+        <v>6440</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>441284</v>
+        <v>441314</v>
       </c>
       <c r="R45" t="n">
-        <v>6753286</v>
+        <v>6753342</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5228,7 +5228,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122567113</v>
+        <v>122567106</v>
       </c>
       <c r="B46" t="n">
         <v>78766</v>
@@ -5268,10 +5268,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>441207</v>
+        <v>441266</v>
       </c>
       <c r="R46" t="n">
-        <v>6753568</v>
+        <v>6753401</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5330,10 +5330,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122567106</v>
+        <v>122567038</v>
       </c>
       <c r="B47" t="n">
-        <v>78766</v>
+        <v>79384</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5346,21 +5346,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5370,10 +5370,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>441266</v>
+        <v>441336</v>
       </c>
       <c r="R47" t="n">
-        <v>6753401</v>
+        <v>6753344</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5432,7 +5432,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122567123</v>
+        <v>122567113</v>
       </c>
       <c r="B48" t="n">
         <v>78766</v>
@@ -5472,10 +5472,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>441334</v>
+        <v>441207</v>
       </c>
       <c r="R48" t="n">
-        <v>6753341</v>
+        <v>6753568</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5534,10 +5534,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122567038</v>
+        <v>122567123</v>
       </c>
       <c r="B49" t="n">
-        <v>79384</v>
+        <v>78766</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5550,21 +5550,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5574,10 +5574,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>441336</v>
+        <v>441334</v>
       </c>
       <c r="R49" t="n">
-        <v>6753344</v>
+        <v>6753341</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6248,10 +6248,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122567117</v>
+        <v>122567034</v>
       </c>
       <c r="B56" t="n">
-        <v>78766</v>
+        <v>79384</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6264,21 +6264,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6288,10 +6288,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>441193</v>
+        <v>441152</v>
       </c>
       <c r="R56" t="n">
-        <v>6753577</v>
+        <v>6753562</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6350,7 +6350,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122567138</v>
+        <v>122567117</v>
       </c>
       <c r="B57" t="n">
         <v>78766</v>
@@ -6390,10 +6390,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>441383</v>
+        <v>441193</v>
       </c>
       <c r="R57" t="n">
-        <v>6753450</v>
+        <v>6753577</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6452,7 +6452,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122567139</v>
+        <v>122567138</v>
       </c>
       <c r="B58" t="n">
         <v>78766</v>
@@ -6492,10 +6492,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>441430</v>
+        <v>441383</v>
       </c>
       <c r="R58" t="n">
-        <v>6753445</v>
+        <v>6753450</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6554,10 +6554,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122567034</v>
+        <v>122567139</v>
       </c>
       <c r="B59" t="n">
-        <v>79384</v>
+        <v>78766</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6570,21 +6570,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6594,10 +6594,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>441152</v>
+        <v>441430</v>
       </c>
       <c r="R59" t="n">
-        <v>6753562</v>
+        <v>6753445</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6656,10 +6656,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122567075</v>
+        <v>122567088</v>
       </c>
       <c r="B60" t="n">
-        <v>8441</v>
+        <v>56688</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6672,27 +6672,27 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="M60" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
@@ -6701,10 +6701,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>441291</v>
+        <v>441262</v>
       </c>
       <c r="R60" t="n">
-        <v>6753289</v>
+        <v>6753412</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6763,10 +6763,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122567088</v>
+        <v>122567075</v>
       </c>
       <c r="B61" t="n">
-        <v>56688</v>
+        <v>8441</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6779,27 +6779,27 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100138</v>
+        <v>106545</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="M61" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
@@ -6808,10 +6808,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>441262</v>
+        <v>441291</v>
       </c>
       <c r="R61" t="n">
-        <v>6753412</v>
+        <v>6753289</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7074,10 +7074,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122567053</v>
+        <v>122567041</v>
       </c>
       <c r="B64" t="n">
-        <v>78800</v>
+        <v>79384</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7090,21 +7090,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7114,10 +7114,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>441420</v>
+        <v>441357</v>
       </c>
       <c r="R64" t="n">
-        <v>6753456</v>
+        <v>6753361</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7176,10 +7176,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122567099</v>
+        <v>122567053</v>
       </c>
       <c r="B65" t="n">
-        <v>78766</v>
+        <v>78800</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7192,21 +7192,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7216,10 +7216,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>441323</v>
+        <v>441420</v>
       </c>
       <c r="R65" t="n">
-        <v>6753416</v>
+        <v>6753456</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7278,10 +7278,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122567041</v>
+        <v>122567099</v>
       </c>
       <c r="B66" t="n">
-        <v>79384</v>
+        <v>78766</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7294,21 +7294,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7318,10 +7318,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>441357</v>
+        <v>441323</v>
       </c>
       <c r="R66" t="n">
-        <v>6753361</v>
+        <v>6753416</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8298,10 +8298,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>122567071</v>
+        <v>122567133</v>
       </c>
       <c r="B76" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8310,43 +8310,38 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>441172</v>
+        <v>441321</v>
       </c>
       <c r="R76" t="n">
-        <v>6753515</v>
+        <v>6753447</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8405,7 +8400,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>122567133</v>
+        <v>122567121</v>
       </c>
       <c r="B77" t="n">
         <v>78766</v>
@@ -8445,10 +8440,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>441321</v>
+        <v>441306</v>
       </c>
       <c r="R77" t="n">
-        <v>6753447</v>
+        <v>6753338</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8507,10 +8502,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>122567121</v>
+        <v>122567071</v>
       </c>
       <c r="B78" t="n">
-        <v>78766</v>
+        <v>8441</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8519,38 +8514,43 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>441306</v>
+        <v>441172</v>
       </c>
       <c r="R78" t="n">
-        <v>6753338</v>
+        <v>6753515</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>

--- a/artfynd/A 61943-2024 artfynd.xlsx
+++ b/artfynd/A 61943-2024 artfynd.xlsx
@@ -1608,10 +1608,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122567135</v>
+        <v>122567051</v>
       </c>
       <c r="B11" t="n">
-        <v>78766</v>
+        <v>74863</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1624,21 +1624,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1648,10 +1648,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>441322</v>
+        <v>441352</v>
       </c>
       <c r="R11" t="n">
-        <v>6753459</v>
+        <v>6753455</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1710,10 +1710,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122567051</v>
+        <v>122567044</v>
       </c>
       <c r="B12" t="n">
-        <v>74863</v>
+        <v>79384</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1726,21 +1726,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6440</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1750,10 +1750,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>441352</v>
+        <v>441348</v>
       </c>
       <c r="R12" t="n">
-        <v>6753455</v>
+        <v>6753445</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1812,10 +1812,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122567044</v>
+        <v>122567047</v>
       </c>
       <c r="B13" t="n">
-        <v>79384</v>
+        <v>74863</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1828,21 +1828,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>6440</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1852,10 +1852,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>441348</v>
+        <v>441304</v>
       </c>
       <c r="R13" t="n">
-        <v>6753445</v>
+        <v>6753377</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1914,10 +1914,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122567047</v>
+        <v>122567135</v>
       </c>
       <c r="B14" t="n">
-        <v>74863</v>
+        <v>78766</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1930,21 +1930,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1954,10 +1954,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>441304</v>
+        <v>441322</v>
       </c>
       <c r="R14" t="n">
-        <v>6753377</v>
+        <v>6753459</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2735,10 +2735,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122567119</v>
+        <v>122567072</v>
       </c>
       <c r="B22" t="n">
-        <v>78766</v>
+        <v>8441</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2747,38 +2747,43 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>441291</v>
+        <v>441255</v>
       </c>
       <c r="R22" t="n">
-        <v>6753289</v>
+        <v>6753382</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2837,7 +2842,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122567111</v>
+        <v>122567119</v>
       </c>
       <c r="B23" t="n">
         <v>78766</v>
@@ -2877,10 +2882,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>441221</v>
+        <v>441291</v>
       </c>
       <c r="R23" t="n">
-        <v>6753553</v>
+        <v>6753289</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2939,10 +2944,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122567042</v>
+        <v>122567111</v>
       </c>
       <c r="B24" t="n">
-        <v>79384</v>
+        <v>78766</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2955,21 +2960,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2979,10 +2984,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>441336</v>
+        <v>441221</v>
       </c>
       <c r="R24" t="n">
-        <v>6753370</v>
+        <v>6753553</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3041,10 +3046,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122567072</v>
+        <v>122567042</v>
       </c>
       <c r="B25" t="n">
-        <v>8441</v>
+        <v>79384</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3053,43 +3058,38 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>441255</v>
+        <v>441336</v>
       </c>
       <c r="R25" t="n">
-        <v>6753382</v>
+        <v>6753370</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -4392,10 +4392,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122567116</v>
+        <v>122567068</v>
       </c>
       <c r="B38" t="n">
-        <v>78766</v>
+        <v>8441</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4404,38 +4404,43 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>441199</v>
+        <v>441150</v>
       </c>
       <c r="R38" t="n">
-        <v>6753562</v>
+        <v>6753623</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4703,10 +4708,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122567068</v>
+        <v>122567116</v>
       </c>
       <c r="B41" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4715,43 +4720,38 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>441150</v>
+        <v>441199</v>
       </c>
       <c r="R41" t="n">
-        <v>6753623</v>
+        <v>6753562</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4810,10 +4810,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122567132</v>
+        <v>122567050</v>
       </c>
       <c r="B42" t="n">
-        <v>78766</v>
+        <v>74863</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4826,21 +4826,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4850,10 +4850,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>441329</v>
+        <v>441314</v>
       </c>
       <c r="R42" t="n">
-        <v>6753438</v>
+        <v>6753342</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4912,10 +4912,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122567059</v>
+        <v>122567132</v>
       </c>
       <c r="B43" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4924,43 +4924,38 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>441302</v>
+        <v>441329</v>
       </c>
       <c r="R43" t="n">
-        <v>6753294</v>
+        <v>6753438</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5019,7 +5014,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122567074</v>
+        <v>122567059</v>
       </c>
       <c r="B44" t="n">
         <v>8441</v>
@@ -5055,7 +5050,7 @@
       <c r="I44" t="inlineStr"/>
       <c r="M44" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -5064,10 +5059,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>441284</v>
+        <v>441302</v>
       </c>
       <c r="R44" t="n">
-        <v>6753286</v>
+        <v>6753294</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5126,10 +5121,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122567050</v>
+        <v>122567074</v>
       </c>
       <c r="B45" t="n">
-        <v>74863</v>
+        <v>8441</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5138,38 +5133,43 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6440</v>
+        <v>106545</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>441314</v>
+        <v>441284</v>
       </c>
       <c r="R45" t="n">
-        <v>6753342</v>
+        <v>6753286</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5228,7 +5228,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122567106</v>
+        <v>122567113</v>
       </c>
       <c r="B46" t="n">
         <v>78766</v>
@@ -5268,10 +5268,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>441266</v>
+        <v>441207</v>
       </c>
       <c r="R46" t="n">
-        <v>6753401</v>
+        <v>6753568</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5330,10 +5330,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122567038</v>
+        <v>122567106</v>
       </c>
       <c r="B47" t="n">
-        <v>79384</v>
+        <v>78766</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5346,21 +5346,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5370,10 +5370,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>441336</v>
+        <v>441266</v>
       </c>
       <c r="R47" t="n">
-        <v>6753344</v>
+        <v>6753401</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5432,7 +5432,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122567113</v>
+        <v>122567123</v>
       </c>
       <c r="B48" t="n">
         <v>78766</v>
@@ -5472,10 +5472,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>441207</v>
+        <v>441334</v>
       </c>
       <c r="R48" t="n">
-        <v>6753568</v>
+        <v>6753341</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5534,10 +5534,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122567123</v>
+        <v>122567038</v>
       </c>
       <c r="B49" t="n">
-        <v>78766</v>
+        <v>79384</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5550,21 +5550,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5574,10 +5574,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>441334</v>
+        <v>441336</v>
       </c>
       <c r="R49" t="n">
-        <v>6753341</v>
+        <v>6753344</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -7482,10 +7482,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122567126</v>
+        <v>122567039</v>
       </c>
       <c r="B68" t="n">
-        <v>78766</v>
+        <v>79384</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7498,21 +7498,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7525,7 +7525,7 @@
         <v>441344</v>
       </c>
       <c r="R68" t="n">
-        <v>6753362</v>
+        <v>6753341</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7584,10 +7584,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122567098</v>
+        <v>122567048</v>
       </c>
       <c r="B69" t="n">
-        <v>78766</v>
+        <v>74863</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7600,21 +7600,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7624,10 +7624,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>441329</v>
+        <v>441302</v>
       </c>
       <c r="R69" t="n">
-        <v>6753411</v>
+        <v>6753380</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7686,7 +7686,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122567125</v>
+        <v>122567126</v>
       </c>
       <c r="B70" t="n">
         <v>78766</v>
@@ -7726,10 +7726,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>441356</v>
+        <v>441344</v>
       </c>
       <c r="R70" t="n">
-        <v>6753361</v>
+        <v>6753362</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7788,10 +7788,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122567039</v>
+        <v>122567098</v>
       </c>
       <c r="B71" t="n">
-        <v>79384</v>
+        <v>78766</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7804,21 +7804,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7828,10 +7828,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>441344</v>
+        <v>441329</v>
       </c>
       <c r="R71" t="n">
-        <v>6753341</v>
+        <v>6753411</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7890,10 +7890,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122567048</v>
+        <v>122567125</v>
       </c>
       <c r="B72" t="n">
-        <v>74863</v>
+        <v>78766</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -7906,21 +7906,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7930,10 +7930,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>441302</v>
+        <v>441356</v>
       </c>
       <c r="R72" t="n">
-        <v>6753380</v>
+        <v>6753361</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8298,10 +8298,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>122567133</v>
+        <v>122567071</v>
       </c>
       <c r="B76" t="n">
-        <v>78766</v>
+        <v>8441</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8310,38 +8310,43 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>441321</v>
+        <v>441172</v>
       </c>
       <c r="R76" t="n">
-        <v>6753447</v>
+        <v>6753515</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8400,7 +8405,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>122567121</v>
+        <v>122567133</v>
       </c>
       <c r="B77" t="n">
         <v>78766</v>
@@ -8440,10 +8445,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>441306</v>
+        <v>441321</v>
       </c>
       <c r="R77" t="n">
-        <v>6753338</v>
+        <v>6753447</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8502,10 +8507,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>122567071</v>
+        <v>122567121</v>
       </c>
       <c r="B78" t="n">
-        <v>8441</v>
+        <v>78766</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8514,43 +8519,38 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>441172</v>
+        <v>441306</v>
       </c>
       <c r="R78" t="n">
-        <v>6753515</v>
+        <v>6753338</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>

--- a/artfynd/A 61943-2024 artfynd.xlsx
+++ b/artfynd/A 61943-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY78"/>
+  <dimension ref="A1:AY87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,55 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122567066</v>
+        <v>122567053</v>
       </c>
       <c r="B2" t="n">
-        <v>8441</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106545</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>441258</v>
+        <v>441420</v>
       </c>
       <c r="R2" t="n">
-        <v>6753406</v>
+        <v>6753456</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,55 +772,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122567073</v>
+        <v>122567158</v>
       </c>
       <c r="B3" t="n">
-        <v>8441</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106545</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>441269</v>
+        <v>441248</v>
       </c>
       <c r="R3" t="n">
-        <v>6753365</v>
+        <v>6753389</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,15 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122567100</v>
+        <v>122567054</v>
       </c>
       <c r="B4" t="n">
-        <v>78766</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -905,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>441332</v>
+        <v>441179</v>
       </c>
       <c r="R4" t="n">
-        <v>6753382</v>
+        <v>6753504</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -991,19 +966,14 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122567104</v>
+        <v>122567090</v>
       </c>
       <c r="B5" t="n">
-        <v>78766</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1031,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>441277</v>
+        <v>441179</v>
       </c>
       <c r="R5" t="n">
-        <v>6753396</v>
+        <v>6753505</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1093,19 +1063,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122567128</v>
+        <v>122567091</v>
       </c>
       <c r="B6" t="n">
-        <v>78766</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1133,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>441350</v>
+        <v>441420</v>
       </c>
       <c r="R6" t="n">
-        <v>6753388</v>
+        <v>6753456</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1195,37 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122567033</v>
+        <v>122567095</v>
       </c>
       <c r="B7" t="n">
-        <v>79384</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1235,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>441194</v>
+        <v>441406</v>
       </c>
       <c r="R7" t="n">
-        <v>6753576</v>
+        <v>6753439</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1297,55 +1257,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122567089</v>
+        <v>122567096</v>
       </c>
       <c r="B8" t="n">
-        <v>56688</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>441283</v>
+        <v>441319</v>
       </c>
       <c r="R8" t="n">
-        <v>6753349</v>
+        <v>6753442</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1404,19 +1354,14 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122567131</v>
+        <v>122567097</v>
       </c>
       <c r="B9" t="n">
-        <v>78766</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1444,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>441347</v>
+        <v>441320</v>
       </c>
       <c r="R9" t="n">
-        <v>6753407</v>
+        <v>6753429</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1506,19 +1451,14 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122567105</v>
+        <v>122567098</v>
       </c>
       <c r="B10" t="n">
-        <v>78766</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1546,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>441269</v>
+        <v>441329</v>
       </c>
       <c r="R10" t="n">
-        <v>6753398</v>
+        <v>6753411</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1608,37 +1548,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122567051</v>
+        <v>122567099</v>
       </c>
       <c r="B11" t="n">
-        <v>74863</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1648,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>441352</v>
+        <v>441323</v>
       </c>
       <c r="R11" t="n">
-        <v>6753455</v>
+        <v>6753416</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1710,37 +1645,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122567044</v>
+        <v>122567100</v>
       </c>
       <c r="B12" t="n">
-        <v>79384</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1750,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>441348</v>
+        <v>441332</v>
       </c>
       <c r="R12" t="n">
-        <v>6753445</v>
+        <v>6753382</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1812,37 +1742,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122567047</v>
+        <v>122567101</v>
       </c>
       <c r="B13" t="n">
-        <v>74863</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1852,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>441304</v>
+        <v>441301</v>
       </c>
       <c r="R13" t="n">
-        <v>6753377</v>
+        <v>6753376</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1914,19 +1839,14 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122567135</v>
+        <v>122567102</v>
       </c>
       <c r="B14" t="n">
-        <v>78766</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -1954,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>441322</v>
+        <v>441305</v>
       </c>
       <c r="R14" t="n">
-        <v>6753459</v>
+        <v>6753384</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2016,19 +1936,14 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122567095</v>
+        <v>122567103</v>
       </c>
       <c r="B15" t="n">
-        <v>78766</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -2056,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>441406</v>
+        <v>441287</v>
       </c>
       <c r="R15" t="n">
-        <v>6753439</v>
+        <v>6753389</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2118,19 +2033,14 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122567134</v>
+        <v>122567104</v>
       </c>
       <c r="B16" t="n">
-        <v>78766</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -2158,10 +2068,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>441320</v>
+        <v>441277</v>
       </c>
       <c r="R16" t="n">
-        <v>6753453</v>
+        <v>6753396</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2220,19 +2130,14 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122567101</v>
+        <v>122567105</v>
       </c>
       <c r="B17" t="n">
-        <v>78766</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -2260,10 +2165,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>441301</v>
+        <v>441269</v>
       </c>
       <c r="R17" t="n">
-        <v>6753376</v>
+        <v>6753398</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2322,19 +2227,14 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122567122</v>
+        <v>122567106</v>
       </c>
       <c r="B18" t="n">
-        <v>78766</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -2362,10 +2262,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>441315</v>
+        <v>441266</v>
       </c>
       <c r="R18" t="n">
-        <v>6753342</v>
+        <v>6753401</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2424,37 +2324,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122567035</v>
+        <v>122567107</v>
       </c>
       <c r="B19" t="n">
-        <v>79384</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2464,10 +2359,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>441158</v>
+        <v>441262</v>
       </c>
       <c r="R19" t="n">
-        <v>6753553</v>
+        <v>6753417</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2526,37 +2421,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122567046</v>
+        <v>122567108</v>
       </c>
       <c r="B20" t="n">
-        <v>74863</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2566,10 +2456,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>441304</v>
+        <v>441273</v>
       </c>
       <c r="R20" t="n">
-        <v>6753366</v>
+        <v>6753425</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2628,55 +2518,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122567069</v>
+        <v>122567109</v>
       </c>
       <c r="B21" t="n">
-        <v>8441</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>441119</v>
+        <v>441223</v>
       </c>
       <c r="R21" t="n">
-        <v>6753677</v>
+        <v>6753536</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2735,55 +2615,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122567072</v>
+        <v>122567111</v>
       </c>
       <c r="B22" t="n">
-        <v>8441</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>441255</v>
+        <v>441221</v>
       </c>
       <c r="R22" t="n">
-        <v>6753382</v>
+        <v>6753553</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2842,19 +2712,14 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122567119</v>
+        <v>122567112</v>
       </c>
       <c r="B23" t="n">
-        <v>78766</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -2882,10 +2747,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>441291</v>
+        <v>441217</v>
       </c>
       <c r="R23" t="n">
-        <v>6753289</v>
+        <v>6753556</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2944,19 +2809,14 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122567111</v>
+        <v>122567113</v>
       </c>
       <c r="B24" t="n">
-        <v>78766</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -2984,10 +2844,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>441221</v>
+        <v>441207</v>
       </c>
       <c r="R24" t="n">
-        <v>6753553</v>
+        <v>6753568</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3046,37 +2906,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122567042</v>
+        <v>122567114</v>
       </c>
       <c r="B25" t="n">
-        <v>79384</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3086,10 +2941,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>441336</v>
+        <v>441206</v>
       </c>
       <c r="R25" t="n">
-        <v>6753370</v>
+        <v>6753562</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3148,37 +3003,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122567158</v>
+        <v>122567116</v>
       </c>
       <c r="B26" t="n">
-        <v>78411</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3188,10 +3038,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>441248</v>
+        <v>441199</v>
       </c>
       <c r="R26" t="n">
-        <v>6753389</v>
+        <v>6753562</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3250,55 +3100,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122567070</v>
+        <v>122567117</v>
       </c>
       <c r="B27" t="n">
-        <v>8441</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>441158</v>
+        <v>441193</v>
       </c>
       <c r="R27" t="n">
-        <v>6753533</v>
+        <v>6753577</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3357,55 +3197,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122567064</v>
+        <v>122567118</v>
       </c>
       <c r="B28" t="n">
-        <v>8441</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>441389</v>
+        <v>441277</v>
       </c>
       <c r="R28" t="n">
-        <v>6753439</v>
+        <v>6753324</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3464,55 +3294,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122567067</v>
+        <v>122567119</v>
       </c>
       <c r="B29" t="n">
-        <v>8441</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>441231</v>
+        <v>441291</v>
       </c>
       <c r="R29" t="n">
-        <v>6753537</v>
+        <v>6753289</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3571,55 +3391,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122567077</v>
+        <v>122567120</v>
       </c>
       <c r="B30" t="n">
-        <v>8441</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>441381</v>
+        <v>441289</v>
       </c>
       <c r="R30" t="n">
-        <v>6753451</v>
+        <v>6753324</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3678,37 +3488,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122567043</v>
+        <v>122567121</v>
       </c>
       <c r="B31" t="n">
-        <v>79384</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3718,10 +3523,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>441348</v>
+        <v>441306</v>
       </c>
       <c r="R31" t="n">
-        <v>6753422</v>
+        <v>6753338</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3780,37 +3585,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122567081</v>
+        <v>122567122</v>
       </c>
       <c r="B32" t="n">
-        <v>78503</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3820,10 +3620,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>441344</v>
+        <v>441315</v>
       </c>
       <c r="R32" t="n">
-        <v>6753341</v>
+        <v>6753342</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3882,37 +3682,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122567036</v>
+        <v>122567123</v>
       </c>
       <c r="B33" t="n">
-        <v>79384</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3922,10 +3717,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>441283</v>
+        <v>441334</v>
       </c>
       <c r="R33" t="n">
-        <v>6753350</v>
+        <v>6753341</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3984,19 +3779,14 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122567091</v>
+        <v>122567124</v>
       </c>
       <c r="B34" t="n">
-        <v>78766</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
@@ -4024,10 +3814,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>441420</v>
+        <v>441359</v>
       </c>
       <c r="R34" t="n">
-        <v>6753456</v>
+        <v>6753344</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4086,19 +3876,14 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122567108</v>
+        <v>122567125</v>
       </c>
       <c r="B35" t="n">
-        <v>78766</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
@@ -4126,10 +3911,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>441273</v>
+        <v>441356</v>
       </c>
       <c r="R35" t="n">
-        <v>6753425</v>
+        <v>6753361</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4188,19 +3973,14 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122567127</v>
+        <v>122567126</v>
       </c>
       <c r="B36" t="n">
-        <v>78766</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
@@ -4228,10 +4008,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>441338</v>
+        <v>441344</v>
       </c>
       <c r="R36" t="n">
-        <v>6753386</v>
+        <v>6753362</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4290,19 +4070,14 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122567096</v>
+        <v>122567127</v>
       </c>
       <c r="B37" t="n">
-        <v>78766</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
@@ -4330,10 +4105,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>441319</v>
+        <v>441338</v>
       </c>
       <c r="R37" t="n">
-        <v>6753442</v>
+        <v>6753386</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4392,55 +4167,45 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122567068</v>
+        <v>122567128</v>
       </c>
       <c r="B38" t="n">
-        <v>8441</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>441150</v>
+        <v>441350</v>
       </c>
       <c r="R38" t="n">
-        <v>6753623</v>
+        <v>6753388</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4499,37 +4264,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122567049</v>
+        <v>122567129</v>
       </c>
       <c r="B39" t="n">
-        <v>74863</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4539,10 +4299,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>441299</v>
+        <v>441355</v>
       </c>
       <c r="R39" t="n">
-        <v>6753387</v>
+        <v>6753403</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4601,55 +4361,45 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122567056</v>
+        <v>122567130</v>
       </c>
       <c r="B40" t="n">
-        <v>57494</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>441305</v>
+        <v>441356</v>
       </c>
       <c r="R40" t="n">
-        <v>6753366</v>
+        <v>6753399</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4708,19 +4458,14 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122567116</v>
+        <v>122567131</v>
       </c>
       <c r="B41" t="n">
-        <v>78766</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
@@ -4748,10 +4493,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>441199</v>
+        <v>441347</v>
       </c>
       <c r="R41" t="n">
-        <v>6753562</v>
+        <v>6753407</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4810,37 +4555,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122567050</v>
+        <v>122567132</v>
       </c>
       <c r="B42" t="n">
-        <v>74863</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4850,10 +4590,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>441314</v>
+        <v>441329</v>
       </c>
       <c r="R42" t="n">
-        <v>6753342</v>
+        <v>6753438</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4912,19 +4652,14 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122567132</v>
+        <v>122567133</v>
       </c>
       <c r="B43" t="n">
-        <v>78766</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
@@ -4952,10 +4687,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>441329</v>
+        <v>441321</v>
       </c>
       <c r="R43" t="n">
-        <v>6753438</v>
+        <v>6753447</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5014,55 +4749,45 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122567059</v>
+        <v>122567134</v>
       </c>
       <c r="B44" t="n">
-        <v>8441</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>441302</v>
+        <v>441320</v>
       </c>
       <c r="R44" t="n">
-        <v>6753294</v>
+        <v>6753453</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5121,55 +4846,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122567074</v>
+        <v>122567135</v>
       </c>
       <c r="B45" t="n">
-        <v>8441</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>441284</v>
+        <v>441322</v>
       </c>
       <c r="R45" t="n">
-        <v>6753286</v>
+        <v>6753459</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5228,19 +4943,14 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122567113</v>
+        <v>122567136</v>
       </c>
       <c r="B46" t="n">
-        <v>78766</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
@@ -5268,10 +4978,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>441207</v>
+        <v>441345</v>
       </c>
       <c r="R46" t="n">
-        <v>6753568</v>
+        <v>6753451</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5330,19 +5040,14 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122567106</v>
+        <v>122567137</v>
       </c>
       <c r="B47" t="n">
-        <v>78766</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
@@ -5370,10 +5075,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>441266</v>
+        <v>441348</v>
       </c>
       <c r="R47" t="n">
-        <v>6753401</v>
+        <v>6753444</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5432,19 +5137,14 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122567123</v>
+        <v>122567138</v>
       </c>
       <c r="B48" t="n">
-        <v>78766</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
@@ -5472,10 +5172,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>441334</v>
+        <v>441383</v>
       </c>
       <c r="R48" t="n">
-        <v>6753341</v>
+        <v>6753450</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5534,37 +5234,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122567038</v>
+        <v>122567139</v>
       </c>
       <c r="B49" t="n">
-        <v>79384</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5574,10 +5269,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>441336</v>
+        <v>441430</v>
       </c>
       <c r="R49" t="n">
-        <v>6753344</v>
+        <v>6753445</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5636,37 +5331,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122567083</v>
+        <v>122567140</v>
       </c>
       <c r="B50" t="n">
-        <v>78503</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5676,10 +5366,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>441348</v>
+        <v>441433</v>
       </c>
       <c r="R50" t="n">
-        <v>6753422</v>
+        <v>6753436</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5738,15 +5428,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122567102</v>
+        <v>122567046</v>
       </c>
       <c r="B51" t="n">
-        <v>78766</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5754,21 +5439,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5778,10 +5463,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>441305</v>
+        <v>441304</v>
       </c>
       <c r="R51" t="n">
-        <v>6753384</v>
+        <v>6753366</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5840,15 +5525,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122567114</v>
+        <v>122567047</v>
       </c>
       <c r="B52" t="n">
-        <v>78766</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5856,21 +5536,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5880,10 +5560,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>441206</v>
+        <v>441304</v>
       </c>
       <c r="R52" t="n">
-        <v>6753562</v>
+        <v>6753377</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5942,15 +5622,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122567136</v>
+        <v>122567048</v>
       </c>
       <c r="B53" t="n">
-        <v>78766</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5958,21 +5633,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5982,10 +5657,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>441345</v>
+        <v>441302</v>
       </c>
       <c r="R53" t="n">
-        <v>6753451</v>
+        <v>6753380</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6044,15 +5719,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122567103</v>
+        <v>122567049</v>
       </c>
       <c r="B54" t="n">
-        <v>78766</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6060,21 +5730,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6084,10 +5754,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>441287</v>
+        <v>441299</v>
       </c>
       <c r="R54" t="n">
-        <v>6753389</v>
+        <v>6753387</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6146,15 +5816,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122567120</v>
+        <v>122567050</v>
       </c>
       <c r="B55" t="n">
-        <v>78766</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6162,21 +5827,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6186,10 +5851,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>441289</v>
+        <v>441314</v>
       </c>
       <c r="R55" t="n">
-        <v>6753324</v>
+        <v>6753342</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6248,15 +5913,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122567034</v>
+        <v>122567051</v>
       </c>
       <c r="B56" t="n">
-        <v>79384</v>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6264,21 +5924,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6453</v>
+        <v>6440</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6288,10 +5948,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>441152</v>
+        <v>441352</v>
       </c>
       <c r="R56" t="n">
-        <v>6753562</v>
+        <v>6753455</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6350,15 +6010,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122567117</v>
+        <v>122567033</v>
       </c>
       <c r="B57" t="n">
-        <v>78766</v>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6366,21 +6021,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6390,10 +6045,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>441193</v>
+        <v>441194</v>
       </c>
       <c r="R57" t="n">
-        <v>6753577</v>
+        <v>6753576</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6452,15 +6107,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122567138</v>
+        <v>122567034</v>
       </c>
       <c r="B58" t="n">
-        <v>78766</v>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6468,21 +6118,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6492,10 +6142,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>441383</v>
+        <v>441152</v>
       </c>
       <c r="R58" t="n">
-        <v>6753450</v>
+        <v>6753562</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6554,15 +6204,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122567139</v>
+        <v>122567035</v>
       </c>
       <c r="B59" t="n">
-        <v>78766</v>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6570,21 +6215,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6594,10 +6239,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>441430</v>
+        <v>441158</v>
       </c>
       <c r="R59" t="n">
-        <v>6753445</v>
+        <v>6753553</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6656,55 +6301,45 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122567088</v>
+        <v>122567036</v>
       </c>
       <c r="B60" t="n">
-        <v>56688</v>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>441262</v>
+        <v>441283</v>
       </c>
       <c r="R60" t="n">
-        <v>6753412</v>
+        <v>6753350</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6763,55 +6398,45 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122567075</v>
+        <v>122567038</v>
       </c>
       <c r="B61" t="n">
-        <v>8441</v>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>441291</v>
+        <v>441336</v>
       </c>
       <c r="R61" t="n">
-        <v>6753289</v>
+        <v>6753344</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6870,15 +6495,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122567112</v>
+        <v>122567039</v>
       </c>
       <c r="B62" t="n">
-        <v>78766</v>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6886,21 +6506,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6910,10 +6530,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>441217</v>
+        <v>441344</v>
       </c>
       <c r="R62" t="n">
-        <v>6753556</v>
+        <v>6753341</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6972,15 +6592,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122567137</v>
+        <v>122567040</v>
       </c>
       <c r="B63" t="n">
-        <v>78766</v>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6988,21 +6603,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7012,10 +6627,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>441348</v>
+        <v>441358</v>
       </c>
       <c r="R63" t="n">
-        <v>6753444</v>
+        <v>6753344</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7077,12 +6692,7 @@
         <v>122567041</v>
       </c>
       <c r="B64" t="n">
-        <v>79384</v>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7176,15 +6786,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122567053</v>
+        <v>122567042</v>
       </c>
       <c r="B65" t="n">
-        <v>78800</v>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7192,21 +6797,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7216,10 +6821,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>441420</v>
+        <v>441336</v>
       </c>
       <c r="R65" t="n">
-        <v>6753456</v>
+        <v>6753370</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7278,15 +6883,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122567099</v>
+        <v>122567043</v>
       </c>
       <c r="B66" t="n">
-        <v>78766</v>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7294,21 +6894,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7318,10 +6918,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>441323</v>
+        <v>441348</v>
       </c>
       <c r="R66" t="n">
-        <v>6753416</v>
+        <v>6753422</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7380,15 +6980,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122567109</v>
+        <v>122567044</v>
       </c>
       <c r="B67" t="n">
-        <v>78766</v>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7396,21 +6991,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7420,10 +7015,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>441223</v>
+        <v>441348</v>
       </c>
       <c r="R67" t="n">
-        <v>6753536</v>
+        <v>6753445</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7482,15 +7077,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122567039</v>
+        <v>122567086</v>
       </c>
       <c r="B68" t="n">
-        <v>79384</v>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7498,21 +7088,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6453</v>
+        <v>6458</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7522,10 +7112,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>441344</v>
+        <v>441429</v>
       </c>
       <c r="R68" t="n">
-        <v>6753341</v>
+        <v>6753456</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7584,50 +7174,50 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122567048</v>
+        <v>122567056</v>
       </c>
       <c r="B69" t="n">
-        <v>74863</v>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6440</v>
+        <v>100049</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>441302</v>
+        <v>441305</v>
       </c>
       <c r="R69" t="n">
-        <v>6753380</v>
+        <v>6753366</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7686,50 +7276,50 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122567126</v>
+        <v>122567088</v>
       </c>
       <c r="B70" t="n">
-        <v>78766</v>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>441344</v>
+        <v>441262</v>
       </c>
       <c r="R70" t="n">
-        <v>6753362</v>
+        <v>6753412</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7788,50 +7378,50 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122567098</v>
+        <v>122567089</v>
       </c>
       <c r="B71" t="n">
-        <v>78766</v>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>441329</v>
+        <v>441283</v>
       </c>
       <c r="R71" t="n">
-        <v>6753411</v>
+        <v>6753349</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7890,50 +7480,50 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122567125</v>
+        <v>122567058</v>
       </c>
       <c r="B72" t="n">
-        <v>78766</v>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8455</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>441356</v>
+        <v>441211</v>
       </c>
       <c r="R72" t="n">
-        <v>6753361</v>
+        <v>6753570</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7992,50 +7582,50 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>122567107</v>
+        <v>122567059</v>
       </c>
       <c r="B73" t="n">
-        <v>78766</v>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8455</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>441262</v>
+        <v>441302</v>
       </c>
       <c r="R73" t="n">
-        <v>6753417</v>
+        <v>6753294</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8094,50 +7684,50 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>122567118</v>
+        <v>122567064</v>
       </c>
       <c r="B74" t="n">
-        <v>78766</v>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8455</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>441277</v>
+        <v>441389</v>
       </c>
       <c r="R74" t="n">
-        <v>6753324</v>
+        <v>6753439</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8196,50 +7786,50 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>122567097</v>
+        <v>122567066</v>
       </c>
       <c r="B75" t="n">
-        <v>78766</v>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8455</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>441320</v>
+        <v>441258</v>
       </c>
       <c r="R75" t="n">
-        <v>6753429</v>
+        <v>6753406</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8298,15 +7888,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>122567071</v>
+        <v>122567067</v>
       </c>
       <c r="B76" t="n">
-        <v>8441</v>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8455</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8343,10 +7928,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>441172</v>
+        <v>441231</v>
       </c>
       <c r="R76" t="n">
-        <v>6753515</v>
+        <v>6753537</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8405,50 +7990,50 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>122567133</v>
+        <v>122567068</v>
       </c>
       <c r="B77" t="n">
-        <v>78766</v>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8455</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>441321</v>
+        <v>441150</v>
       </c>
       <c r="R77" t="n">
-        <v>6753447</v>
+        <v>6753623</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8507,50 +8092,50 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>122567121</v>
+        <v>122567069</v>
       </c>
       <c r="B78" t="n">
-        <v>78766</v>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8455</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Stormyren, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>441306</v>
+        <v>441119</v>
       </c>
       <c r="R78" t="n">
-        <v>6753338</v>
+        <v>6753677</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8606,6 +8191,914 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>122567070</v>
+      </c>
+      <c r="B79" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Stormyren, Dlr</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>441158</v>
+      </c>
+      <c r="R79" t="n">
+        <v>6753533</v>
+      </c>
+      <c r="S79" t="n">
+        <v>10</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>122567071</v>
+      </c>
+      <c r="B80" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Stormyren, Dlr</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>441172</v>
+      </c>
+      <c r="R80" t="n">
+        <v>6753515</v>
+      </c>
+      <c r="S80" t="n">
+        <v>10</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>122567072</v>
+      </c>
+      <c r="B81" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Stormyren, Dlr</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>441255</v>
+      </c>
+      <c r="R81" t="n">
+        <v>6753382</v>
+      </c>
+      <c r="S81" t="n">
+        <v>10</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>122567073</v>
+      </c>
+      <c r="B82" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Stormyren, Dlr</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>441269</v>
+      </c>
+      <c r="R82" t="n">
+        <v>6753365</v>
+      </c>
+      <c r="S82" t="n">
+        <v>10</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>122567074</v>
+      </c>
+      <c r="B83" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Stormyren, Dlr</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>441284</v>
+      </c>
+      <c r="R83" t="n">
+        <v>6753286</v>
+      </c>
+      <c r="S83" t="n">
+        <v>10</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>122567075</v>
+      </c>
+      <c r="B84" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Stormyren, Dlr</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>441291</v>
+      </c>
+      <c r="R84" t="n">
+        <v>6753289</v>
+      </c>
+      <c r="S84" t="n">
+        <v>10</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>122567077</v>
+      </c>
+      <c r="B85" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Stormyren, Dlr</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>441381</v>
+      </c>
+      <c r="R85" t="n">
+        <v>6753451</v>
+      </c>
+      <c r="S85" t="n">
+        <v>10</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>122567081</v>
+      </c>
+      <c r="B86" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Stormyren, Dlr</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>441344</v>
+      </c>
+      <c r="R86" t="n">
+        <v>6753341</v>
+      </c>
+      <c r="S86" t="n">
+        <v>10</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>122567083</v>
+      </c>
+      <c r="B87" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Stormyren, Dlr</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>441348</v>
+      </c>
+      <c r="R87" t="n">
+        <v>6753422</v>
+      </c>
+      <c r="S87" t="n">
+        <v>10</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 61943-2024 artfynd.xlsx
+++ b/artfynd/A 61943-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY87"/>
+  <dimension ref="A1:AZ87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122567053</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122567158</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122567054</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122567090</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122567091</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122567095</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122567096</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122567097</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122567098</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122567099</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1739,6 +1794,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122567100</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1836,6 +1896,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122567101</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1933,6 +1998,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122567102</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2030,6 +2100,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122567103</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2127,6 +2202,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122567104</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2224,6 +2304,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122567105</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2321,6 +2406,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122567106</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2418,6 +2508,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122567107</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2515,6 +2610,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122567108</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2612,6 +2712,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122567109</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2709,6 +2814,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122567111</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2806,6 +2916,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122567112</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2903,6 +3018,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122567113</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3000,6 +3120,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122567114</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3097,6 +3222,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122567116</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3194,6 +3324,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122567117</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3291,6 +3426,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122567118</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3388,6 +3528,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122567119</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3485,6 +3630,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122567120</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3582,6 +3732,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122567121</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3679,6 +3834,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122567122</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3776,6 +3936,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122567123</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3873,6 +4038,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122567124</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -3970,6 +4140,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122567125</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4067,6 +4242,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122567126</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4164,6 +4344,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122567127</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4261,6 +4446,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122567128</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4358,6 +4548,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122567129</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4455,6 +4650,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122567130</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4552,6 +4752,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122567131</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4649,6 +4854,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122567132</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4746,6 +4956,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122567133</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4843,6 +5058,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122567134</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -4940,6 +5160,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122567135</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5037,6 +5262,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122567136</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5134,6 +5364,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122567137</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5231,6 +5466,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122567138</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5328,6 +5568,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122567139</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5425,6 +5670,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122567140</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5522,6 +5772,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122567046</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5619,6 +5874,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122567047</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5716,6 +5976,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122567048</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -5813,6 +6078,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122567049</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -5910,6 +6180,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122567050</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6007,6 +6282,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122567051</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6104,6 +6384,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122567033</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6201,6 +6486,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122567034</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6298,6 +6588,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122567035</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6395,6 +6690,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122567036</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6492,6 +6792,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122567038</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6589,6 +6894,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122567039</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6686,6 +6996,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122567040</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -6783,6 +7098,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122567041</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -6880,6 +7200,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122567042</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -6977,6 +7302,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122567043</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7074,6 +7404,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122567044</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7171,6 +7506,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122567086</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7273,6 +7613,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122567056</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7375,6 +7720,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122567088</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7477,6 +7827,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122567089</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7579,6 +7934,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122567058</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -7681,6 +8041,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122567059</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -7783,6 +8148,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122567064</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -7885,6 +8255,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122567066</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -7987,6 +8362,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122567067</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8089,6 +8469,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122567068</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8191,6 +8576,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122567069</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8293,6 +8683,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122567070</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8395,6 +8790,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122567071</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8497,6 +8897,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122567072</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -8599,6 +9004,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122567073</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -8701,6 +9111,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122567074</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -8803,6 +9218,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122567075</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -8905,6 +9325,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122567077</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9002,6 +9427,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122567081</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9099,8 +9529,101 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122567083</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>